--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
@@ -5042,6 +5042,942 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TST_CGST_TC_1</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify the Class grade settings page launches from a class page</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#22 — Launch class grade setting page from a class page</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Positive</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A class is open (Classes tab -&gt; launch a class).</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. On the class page, open the Actions menu. 2. Click Class grade settings.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Class grade settings page opens (/class/.../grade-weighting) showing Grading Scale (+ Change), Score settings (teacher-override toggle), Score calculation (Best/First score), per-material Weightage %, Other grading categories (+ Add a grading category), Total grade: 100%, Save changes / Cancel.</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Destination the grading category/scale details pages link to (TST_GCAT_TC_7, TST_GSCL_TC_7).</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TST_CGST_TC_2</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify the grading scale can be changed for a class</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#22 — Launch class grade setting page from a class page</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Positive</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On the Class grade settings page.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. In Grading Scale, click Change. 2. Select a grading scale. 3. Click Save changes.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A grading scale (AutoTest Scale / Cambridge One grading scale)</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Class grading scale updates to the selected scale; the class then appears under that scale's details. [ASSUMED] confirm change-scale selector.</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Associates a scale with a class - resolves TST_GSCL_TC_7.</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TST_CGST_TC_3</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify a grading category can be added to a class</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#22 — Launch class grade setting page from a class page</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Positive</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On the Class grade settings page.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Click Add a grading category. 2. Select a grading category. 3. Set its Weightage %. 4. Click Save changes.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A grading category (some) + weightage</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grading category added to the class with a weightage; the class then appears under that category's details. [ASSUMED] confirm add-category selector.</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Associates a category with a class - resolves TST_GCAT_TC_7.</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TST_CGST_TC_4</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify the score calculation (Best / First score) can be changed</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#22 — Launch class grade setting page from a class page</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Positive</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On the Class grade settings page.</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open the Score calculation dropdown. 2. Select First score (or Best score). 3. Click Save changes.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Score type: First score</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Selected score type is saved as the score that counts toward students' progress.</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">73</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TST_CGST_TC_5</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify the teacher score-override setting can be toggled</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#22 — Launch class grade setting page from a class page</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Positive</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On the Class grade settings page.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Toggle Allow teachers to override and add scores to auto-marked activities. 2. Click Save changes.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The override setting is saved in the state it was toggled to.</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TST_CGST_TC_6</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify the total grade weightage must equal 100%</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#22 — Launch class grade setting page from a class page</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Edge</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On the Class grade settings page with &gt;=1 material/category weightage.</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Set weightages that do not add up to 100%. 2. Attempt to Save changes.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Weightages summing to != 100%</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saving is prevented / an error shown until Total grade equals 100%. [ASSUMED] confirm validation copy.</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page shows a running Total grade: 100%.</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">75</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TST_CLON_TC_1</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify a class can be cloned from an existing class</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#31 — Verify class clone functionality (Copy an Existing Class)</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Positive</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On the Create new classes form with &gt;=1 row selected; a source class exists.</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Click Copy an Existing Class. 2. Step 1: search and select the source class -&gt; Continue. 3. Step 2: on Choose what to copy from [source], select components -&gt; Continue.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Source class: SarthakTestClass1</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step 2 lists copyable components as checkboxes - Teachers, Course materials, Assignments, Locked content rules, Class grade settings - each with a count; selected components are copied from the source into the selected new row(s).</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distinct from Duplicate (TST_BCCF_TC_7).</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">76</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TST_CLON_TC_2</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify all components copy from a fully-populated source class</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#31 — Verify class clone functionality (Copy an Existing Class)</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Positive</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A source class that HAS a teacher, course materials, assignments, locked content rules (incl. an assignment-created lock rule), and class grade settings.</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Copy an Existing Class -&gt; select the populated source. 2. Select all available components. 3. Continue and create.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A fully-populated source class [ASSUMED]</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The cloned class contains the source's teacher, materials, assignments, locked content rules (incl. the assignment-created rule), and class grade settings. [ASSUMED] verify each component copies (tested sources had 0 of each).</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Requires a seeded source class.</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TST_CLON_TC_3</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify components with no items are not selectable when copying</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#31 — Verify class clone functionality (Copy an Existing Class)</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Edge</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A source class that has 0 of one or more components.</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Copy an Existing Class -&gt; select a source with empty components -&gt; Continue.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Source: SarthakTestClass1 (0 teachers/materials/assignments/rules)</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Components with a count of 0 are disabled/unselectable (e.g. Teachers [0] disabled; Class grade settings - Not available).</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observed live.</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TST_CTXC_TC_1</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify a context class can be created</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#32 — Verify Context class creation and view in teacher/admin/student login</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Positive</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Logged in as school admin. [ASSUMED] context-class creation path TBD.</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Create a context class via the (to-be-confirmed) context-class creation flow.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Context class details [ASSUMED]</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The context class is created successfully. [ASSUMED] confirm the creation entry point and any context-specific fields.</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Entry point not found in the admin bulk-create form; needs product clarification.</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TST_CTXC_TC_2</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify the context class appears in the admin login</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#32 — Verify Context class creation and view in teacher/admin/student login</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Positive</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A context class exists; logged in as school admin.</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open the school's Classes tab. 2. Locate the context class.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The created context class</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The context class is listed and behaves as expected in the admin view. [ASSUMED] confirm admin-specific behaviour.</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TST_CTXC_TC_3</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify the context class appears/behaves correctly in the teacher login</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#32 — Verify Context class creation and view in teacher/admin/student login</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Positive</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A context class exists; a teacher account associated with it.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Log in as the teacher. 2. Locate/open the context class.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teacher account [ASSUMED]</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The context class is visible and behaves correctly for the teacher role. [ASSUMED] needs a teacher test account.</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cross-role verification.</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TST_CTXC_TC_4</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify the context class appears/behaves correctly in the student login</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#32 — Verify Context class creation and view in teacher/admin/student login</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Positive</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A context class exists; a student account enrolled in it.</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Log in as the student. 2. Locate/open the context class.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Student account [ASSUMED]</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The context class is visible and behaves correctly for the student role. [ASSUMED] needs a student test account.</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cross-role verification.</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
@@ -1,29 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
+      <name val="Calibri"/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
       <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -44,5940 +54,5426 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N82"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7"/>
-    <col min="2" max="2" width="20"/>
-    <col min="3" max="3" width="52"/>
-    <col min="4" max="4" width="18"/>
-    <col min="5" max="5" width="10"/>
-    <col min="6" max="6" width="10"/>
-    <col min="7" max="7" width="30"/>
-    <col min="8" max="8" width="46"/>
-    <col min="9" max="9" width="30"/>
-    <col min="10" max="10" width="60"/>
-    <col min="11" max="11" width="34"/>
-    <col min="12" max="12" width="14"/>
-    <col min="13" max="13" width="10"/>
-    <col min="14" max="14" width="22"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">S.No.</t>
+          <t>S.No.</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Test Case ID</t>
+          <t>Test Case ID</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Title</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Linked Requirement</t>
+          <t>Linked Requirement</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Type</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Priority</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preconditions</t>
+          <t>Preconditions</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Test Steps</t>
+          <t>Test Steps</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Test Data</t>
+          <t>Test Data</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Expected Result</t>
+          <t>Expected Result</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remarks</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Actual Result</t>
+          <t>Actual Result</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Status</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comments / Defect ID</t>
+          <t>Comments / Defect ID</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_1</t>
+          <t>TST_CLST_TC_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the Classes tab loads with all expected components</t>
+          <t>Verify the Classes tab loads with all expected components</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">#1 — Verify class tab is loading</t>
+          <t>#1 — Verify class tab is loading</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">School opened from My school accounts.</t>
+          <t>School opened from My school accounts.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open school 3 July Test School 1. 2. Observe the Classes tab.</t>
+          <t>1. Open school 3 July Test School 1. 2. Observe the Classes tab.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classes tab loads: Active classes (N) heading, Search, Add class, Filter, User guide, select-all + disabled Delete, class table (Class name/Class key/Start date/End date/Student progress), and a separate Ended classes (N) section. Left nav: Classes/Students/Staff/Library/Reports.</t>
+          <t>Classes tab loads: Active classes (N) heading, Search, Add class, Filter, User guide, select-all + disabled Delete, class table (Class name/Class key/Start date/End date/Student progress), and a separate Ended classes (N) section. Left nav: Classes/Students/Staff/Library/Reports.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classes(N) in nav = Active + Ended.</t>
+          <t>Classes(N) in nav = Active + Ended.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>PASS. Classes tab loaded with every listed component: 'Active classes (15)' heading, search box, Add class, Filter, User guide toggle, select-all checkbox with a disabled Delete class button, all five column headers, a separate 'Ended classes (26)' section, and the five left-nav items.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Automated - adminClassesTab.test.js (npm run P1AdminClassesTab_Thor, thor). Last run 2026-08-17: 12/12 passing.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_2</t>
+          <t>TST_CLST_TC_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the Filter modal opens and shows all filter options</t>
+          <t>Verify the Filter modal opens and shows all filter options</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">#2 — Verify filter functionality is working fine</t>
+          <t>#2 — Verify filter functionality is working fine</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Classes tab.</t>
+          <t>On the Classes tab.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Filter. 2. Observe the modal.</t>
+          <t>1. Click Filter. 2. Observe the modal.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filter modal opens with Class status (Not started, Active, Ended, Expired, Deleted), Class labels (Find a label), Clear all and Apply.</t>
+          <t>Filter modal opens with Class status (Not started, Active, Ended, Expired, Deleted), Class labels (Find a label), Clear all and Apply.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filter is a modal dialog.</t>
+          <t>Filter is a modal dialog.</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>PASS. Filter modal opened showing all five Class status options (Not started / Active / Ended / Expired / Deleted), the 'Find a label' input, and the Clear all and Apply buttons.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Automated - adminClassesTab.test.js (npm run P1AdminClassesTab_Thor, thor). Last run 2026-08-17: 12/12 passing. PRODUCT NOTE: the panel's X close button is unreliable - a click reports success but the panel can stay open. Automation carries an authorised retry marked // WORKAROUND. App-side fix reported landed 2026-08-17; retry retained pending removal.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_3</t>
+          <t>TST_CLST_TC_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify filtering by Class status returns only classes of that status</t>
+          <t>Verify filtering by Class status returns only classes of that status</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">#2 — Verify filter functionality is working fine</t>
+          <t>#2 — Verify filter functionality is working fine</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Classes tab; Filter modal open.</t>
+          <t>On the Classes tab; Filter modal open.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Select Class status = Active. 2. Click Apply.</t>
+          <t>1. Select Class status = Active. 2. Click Apply.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Class status: Active</t>
+          <t>Class status: Active</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal closes; list shows only Active classes; count reflects filtered result.</t>
+          <t>Modal closes; list shows only Active classes; count reflects filtered result.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Repeat for Ended/Expired/Deleted/Not started.</t>
+          <t>Repeat for Ended/Expired/Deleted/Not started.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>PASS. Applying Class status = Active closed the modal and filtered the list; the page-level 'Clear' link appeared (the app's own signal that a filter is applied) and the visible rows were consistent with the 'Active classes (N)' heading.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Automated - adminClassesTab.test.js (npm run P1AdminClassesTab_Thor, thor). Last run 2026-08-17: 12/12 passing.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_4</t>
+          <t>TST_CLST_TC_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify filtering by a Class label returns only classes with that label</t>
+          <t>Verify filtering by a Class label returns only classes with that label</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">#2 — Verify filter functionality is working fine</t>
+          <t>#2 — Verify filter functionality is working fine</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">At least one class has a label applied.</t>
+          <t>At least one class has a label applied.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Filter. 2. In Class labels, type VM1 and select it. 3. Click Apply.</t>
+          <t>1. Click Filter. 2. In Class labels, type VM1 and select it. 3. Click Apply.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Label: VM1 (real label; others: A11y test, aditya)</t>
+          <t>Label: VM1 (real label; others: A11y test, aditya)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Only classes with the selected label are listed.</t>
+          <t>Only classes with the selected label are listed.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Label list confirmed live; confirm a class carries VM1 before running.</t>
+          <t>Label list confirmed live; confirm a class carries VM1 before running.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>PASS. The label filter was applied (confirmed via the 'Clear' link) and the list settled into exactly one valid state - populated with matching classes, or the empty state. NOTE: label VM1 matches no ACTIVE class on this school, so an Active + VM1 combination legitimately returns zero.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Automated - adminClassesTab.test.js (npm run P1AdminClassesTab_Thor, thor). Last run 2026-08-17: 12/12 passing.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_19</t>
+          <t>TST_CLST_TC_19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify Clear all resets the filter selections</t>
+          <t>Verify Clear all resets the filter selections</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">#2 — Verify filter functionality is working fine</t>
+          <t>#2 — Verify filter functionality is working fine</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edge</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filter modal open with selections.</t>
+          <t>Filter modal open with selections.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Select a status and/or label. 2. Click Clear all.</t>
+          <t>1. Select a status and/or label. 2. Click Clear all.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">All filter selections clear back to default within the modal.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>All filter selections clear back to default within the modal.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>PASS. Clear all cleared the selections and closed the panel, and the page-level 'Clear' link disappeared, confirming the applied filter was reset. NOTE: during the panel's ~3.6s close it still holds its pre-clear markup, so the reset must be verified at page level, not from the panel's own chips.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Automated - adminClassesTab.test.js (npm run P1AdminClassesTab_Thor, thor). Last run 2026-08-17: 12/12 passing.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_22</t>
+          <t>TST_CLST_TC_22</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a filter combination with no matches shows an empty state</t>
+          <t>Verify a filter combination with no matches shows an empty state</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">#2 — Verify filter functionality is working fine</t>
+          <t>#2 — Verify filter functionality is working fine</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negative</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Classes tab.</t>
+          <t>On the Classes tab.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Filter. 2. Select a status + label combo with zero matches. 3. Click Apply.</t>
+          <t>1. Open Filter. 2. Select a status + label combo with zero matches. 3. Click Apply.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zero-match status+label combo [ASSUMED]</t>
+          <t>Status: Deleted + Label: A11y test (a combination confirmed to match zero classes)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">List shows empty/no-matching state, no error. [ASSUMED] capture exact copy.</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>The list shows the empty/no-matching-classes state with no error, reading "No classes that are &lt;status&gt;, &lt;label&gt;" (e.g. "No classes that are Deleted, A11y test"). CONFIRMED live 2026-08-15.</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>PASS. Filtering Class status = Deleted together with label 'A11y test' matched no classes and showed the empty state, with no error.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Automated - adminClassesTab.test.js (npm run P1AdminClassesTab_Thor, thor). Last run 2026-08-17: 12/12 passing.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_5</t>
+          <t>TST_CLST_TC_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify search by class name returns the matching class</t>
+          <t>Verify search by class name returns the matching class</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">#9 — Verify search for class key and class name working fine</t>
+          <t>#9 — Verify search for class key and class name working fine</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">A class named SarthakTestClass1 exists.</t>
+          <t>A class named SarthakTestClass1 exists.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Type SarthakTestClass1 in Search. 2. Click Search.</t>
+          <t>1. Type SarthakTestClass1 in Search. 2. Click Search.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Class name: SarthakTestClass1</t>
+          <t>Class name: SarthakTestClass1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">List filtered to the class(es) matching the name.</t>
+          <t>List filtered to the class(es) matching the name.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Any existing active class name may be used.</t>
+          <t>Any existing active class name may be used.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>PASS. Searching 'SarthakTestClass1' returned that class, and every returned row matched the term.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Automated - adminClassesTab.test.js (npm run P1AdminClassesTab_Thor, thor). Last run 2026-08-17: 12/12 passing.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_6</t>
+          <t>TST_CLST_TC_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify search by class key returns the matching class</t>
+          <t>Verify search by class key returns the matching class</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">#9 — Verify search for class key and class name working fine</t>
+          <t>#9 — Verify search for class key and class name working fine</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Class key 97Cc-y7bs exists.</t>
+          <t>Class key 97Cc-y7bs exists.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Type 97Cc-y7bs in Search. 2. Click Search.</t>
+          <t>1. Type 97Cc-y7bs in Search. 2. Click Search.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Class key: 97Cc-y7bs</t>
+          <t>Class key: 97Cc-y7bs</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">List filtered to the single class with that key.</t>
+          <t>List filtered to the single class with that key.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Search accepts name and key.</t>
+          <t>Search accepts name and key.</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>PASS. Searching class key '97Cc-y7bs' returned exactly one class - SarthakTestClass1 - confirming search accepts a class key as well as a name.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Automated - adminClassesTab.test.js (npm run P1AdminClassesTab_Thor, thor). Last run 2026-08-17: 12/12 passing.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_18</t>
+          <t>TST_CLST_TC_18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify class search is case-insensitive and matches partial names</t>
+          <t>Verify class search is case-insensitive and matches partial names</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">#9 — Verify search for class key and class name working fine</t>
+          <t>#9 — Verify search for class key and class name working fine</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edge</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Class SarthakTestClass1 exists.</t>
+          <t>Class SarthakTestClass1 exists.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Search sarthak (lower, partial). 2. Click Search.</t>
+          <t>1. Search sarthak (lower, partial). 2. Click Search.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Search term: sarthak</t>
+          <t>Search term: sarthak</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">SarthakTestClass1 is returned. [ASSUMED] confirm partial/case behaviour.</t>
+          <t>SarthakTestClass1 is returned, confirming class search is case-insensitive and matches partial names. CONFIRMED live 2026-08-17.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Split if exact-match only.</t>
+          <t>Split if exact-match only.</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>PASS. The lower-case partial term 'sarthak' returned 'SarthakTestClass1'. CONFIRMED: class search IS case-insensitive and DOES match partial names - the previously ASSUMED behaviour is correct, so no split into separate positive/negative TCs is needed.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Automated - adminClassesTab.test.js (npm run P1AdminClassesTab_Thor, thor). Last run 2026-08-17: 12/12 passing.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_21</t>
+          <t>TST_CLST_TC_21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify searching for a non-existent class shows a no-results state</t>
+          <t>Verify searching for a non-existent class shows a no-results state</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">#9 — Verify search for class key and class name working fine</t>
+          <t>#9 — Verify search for class key and class name working fine</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negative</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Classes tab.</t>
+          <t>On the Classes tab.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Search zzz-no-such-class-9999. 2. Click Search.</t>
+          <t>1. Search zzz-no-such-class-9999. 2. Click Search.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Search term: zzz-no-such-class-9999</t>
+          <t>Search term: zzz-no-such-class-9999</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">No classes listed; empty/no-results state shown (no error). [ASSUMED] capture exact copy.</t>
+          <t>No classes are listed and the no-results state is shown (no error/crash), reading exactly: "No classes that match your search &lt;term&gt;" with the searched term echoed in bold. CONFIRMED live 2026-08-17.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Record no-results text for automation.</t>
+          <t>Record no-results text for automation.</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>PASS. Searching 'zzz-no-such-class-9999' returned 0 classes and displayed the no-results state with no error. CAPTURED COPY: 'No classes that match your search zzz-no-such-class-9999' - the searched term is echoed back in bold.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Automated - adminClassesTab.test.js (npm run P1AdminClassesTab_Thor, thor). Last run 2026-08-17: 12/12 passing.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_7</t>
+          <t>TST_CLST_TC_7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify sorting by Class name toggles ascending/descending</t>
+          <t>Verify sorting by Class name toggles ascending/descending</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">#27 — Verify Sort by class name/start date/end date</t>
+          <t>#27 — Verify Sort by class name/start date/end date</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classes tab with &gt;=2 active classes.</t>
+          <t>Classes tab with &gt;=2 active classes.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Class name header. 2. Observe. 3. Click again.</t>
+          <t>1. Click Class name header. 2. Observe. 3. Click again.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">First click sorts A-&gt;Z; second reverses to Z-&gt;A; indicator updates.</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>First click sorts A-&gt;Z; second reverses to Z-&gt;A; indicator updates.</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>PASS. The first click sorted by class name and the column reported 'sorted ascending'; the second click reported 'sorted descending' and the order was the exact reverse of the first. NOTE: the product sorts by CODE POINT, so uppercase names sort before lowercase ones (for example 'Test Class 14 Aug' before 'class_L_...').</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Automated - adminClassesTab.test.js (npm run P1AdminClassesTab_Thor, thor). Last run 2026-08-17: 12/12 passing.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_8</t>
+          <t>TST_CLST_TC_8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify sorting by Start date and End date</t>
+          <t>Verify sorting by Start date and End date</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">#27 — Verify Sort by class name/start date/end date</t>
+          <t>#27 — Verify Sort by class name/start date/end date</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classes tab with &gt;=2 active classes.</t>
+          <t>Classes tab with &gt;=2 active classes.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Start date header. 2. Click End date header. Toggle each again.</t>
+          <t>1. Click Start date header. 2. Click End date header. Toggle each again.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classes reorder chronologically by the chosen date column; each header toggles asc/desc.</t>
+          <t>Classes reorder chronologically by the chosen date column; each header toggles asc/desc.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sort headers exist in Active and Ended tables.</t>
+          <t>Sort headers exist in Active and Ended tables.</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>PASS. Start date and End date each reordered the list chronologically and toggled direction on the second click. NOTE: dates repeat (six active classes share Aug 14, 2026), so the order is monotonic rather than strictly increasing, and descending is not an exact reversal of ascending.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Automated - adminClassesTab.test.js (npm run P1AdminClassesTab_Thor, thor). Last run 2026-08-17: 12/12 passing.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_9</t>
+          <t>TST_CLST_TC_9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify expanding a class row shows the class details</t>
+          <t>Verify expanding a class row shows the class details</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">#18 — Verify expanding a class row</t>
+          <t>#18 — Verify expanding a class row</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classes tab with &gt;=1 active class.</t>
+          <t>Classes tab with &gt;=1 active class.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Show class details on a row.</t>
+          <t>1. Click Show class details on a row.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Row expands showing Course materials, Class labels, Students (count+Pending), Teachers (count+Pending); toggle becomes Hide class details.</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Row expands showing Course materials, Class labels, Students (count+Pending), Teachers (count+Pending); toggle becomes Hide class details.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_10</t>
+          <t>TST_CLST_TC_10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify collapsing an expanded class row hides the details</t>
+          <t>Verify collapsing an expanded class row hides the details</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">#18 — Verify expanding a class row</t>
+          <t>#18 — Verify expanding a class row</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">A class row is expanded.</t>
+          <t>A class row is expanded.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Hide class details.</t>
+          <t>1. Click Hide class details.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Details collapse; toggle returns to Show class details.</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Details collapse; toggle returns to Show class details.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_11</t>
+          <t>TST_CLST_TC_11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify expanding the user guide shows the help panel</t>
+          <t>Verify expanding the user guide shows the help panel</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">#17/#33 — Verify expanding user guide in classes tab (expand/collapse)</t>
+          <t>#17/#33 — Verify expanding user guide in classes tab (expand/collapse)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">User guide collapsed.</t>
+          <t>User guide collapsed.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click User guide (Open the user guide).</t>
+          <t>1. Click User guide (Open the user guide).</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Help panel appears (search by name/class code, deleted/restored refresh tip); toggle becomes Hide the user guide.</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Help panel appears (search by name/class code, deleted/restored refresh tip); toggle becomes Hide the user guide.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_12</t>
+          <t>TST_CLST_TC_12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify collapsing the user guide hides the help panel</t>
+          <t>Verify collapsing the user guide hides the help panel</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">#17/#33 — Verify expanding user guide in classes tab (expand/collapse)</t>
+          <t>#17/#33 — Verify expanding user guide in classes tab (expand/collapse)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">User guide expanded.</t>
+          <t>User guide expanded.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Hide the user guide.</t>
+          <t>1. Click Hide the user guide.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Help panel collapses; toggle returns to Open the user guide.</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Help panel collapses; toggle returns to Open the user guide.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_13</t>
+          <t>TST_CLST_TC_13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify launching an Active class opens the Class Page</t>
+          <t>Verify launching an Active class opens the Class Page</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">#19 — Launch a class from classes tab</t>
+          <t>#19 — Launch a class from classes tab</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classes tab with &gt;=1 active class.</t>
+          <t>Classes tab with &gt;=1 active class.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click a class name link in the Active list.</t>
+          <t>1. Click a class name link in the Active list.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Class: SarthakTestClass1</t>
+          <t>Class: SarthakTestClass1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Class Page opens (/class/teacher/org_&lt;slug&gt;/class/&lt;uuid&gt;/view, title Class Page).</t>
+          <t>Class Page opens (/class/teacher/org_&lt;slug&gt;/class/&lt;uuid&gt;/view, title Class Page).</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Opens in teacher/class view.</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Opens in teacher/class view.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_14</t>
+          <t>TST_CLST_TC_14</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify Active and Ended classes appear in separate sections with counts</t>
+          <t>Verify Active and Ended classes appear in separate sections with counts</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">#28 — Ended &amp; Active sections separate; Expand/Collapse Ended</t>
+          <t>#28 — Ended &amp; Active sections separate; Expand/Collapse Ended</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">School has active and ended classes.</t>
+          <t>School has active and ended classes.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Observe Active classes (N). 2. Scroll to Ended classes (M).</t>
+          <t>1. Observe Active classes (N). 2. Scroll to Ended classes (M).</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two distinct sections each with its own count; Ended notes auto-move of ended/deleted classes and has a Class status column.</t>
+          <t>Two distinct sections each with its own count; Ended notes auto-move of ended/deleted classes and has a Class status column.</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nav Classes(N)=Active+Ended.</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Nav Classes(N)=Active+Ended.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_15</t>
+          <t>TST_CLST_TC_15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify expanding and collapsing the Ended classes section</t>
+          <t>Verify expanding and collapsing the Ended classes section</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">#28 — Ended &amp; Active sections separate; Expand/Collapse Ended</t>
+          <t>#28 — Ended &amp; Active sections separate; Expand/Collapse Ended</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ended section present.</t>
+          <t>Ended section present.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Ended classes header (Open). 2. Click again (Close).</t>
+          <t>1. Click Ended classes header (Open). 2. Click again (Close).</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ended section expands to reveal its table on Open and collapses on Close; label toggles Open/Close.</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Ended section expands to reveal its table on Open and collapses on Close; label toggles Open/Close.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_16</t>
+          <t>TST_CLST_TC_16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify launching a class from the Ended section opens the Class Page</t>
+          <t>Verify launching a class from the Ended section opens the Class Page</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">#29 — Verify class launch from ended classes section</t>
+          <t>#29 — Verify class launch from ended classes section</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ended section expanded with &gt;=1 ended class.</t>
+          <t>Ended section expanded with &gt;=1 ended class.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click a class name in the Ended list.</t>
+          <t>1. Click a class name in the Ended list.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ended class: CQA Vimal (key y4G4-3iXC)</t>
+          <t>Ended class: CQA Vimal (key y4G4-3iXC)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Class Page opens for the ended class (same /view destination).</t>
+          <t>Class Page opens for the ended class (same /view destination).</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ended classes remain launchable.</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Ended classes remain launchable.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_17</t>
+          <t>TST_CLST_TC_17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify Load more loads additional classes in the Ended section</t>
+          <t>Verify Load more loads additional classes in the Ended section</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">#20 — Verify load more classes in classes tab</t>
+          <t>#20 — Verify load more classes in classes tab</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ended section has more classes than the page size.</t>
+          <t>Ended section has more classes than the page size.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Expand Ended. 2. Scroll to bottom. 3. Click Load more.</t>
+          <t>1. Expand Ended. 2. Scroll to bottom. 3. Click Load more.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Additional rows append without full reload; visible row count increases.</t>
+          <t>Additional rows append without full reload; visible row count increases.</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Load more is count-gated.</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Load more is count-gated.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_20</t>
+          <t>TST_CLST_TC_20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify Load more no longer appears once all classes are loaded</t>
+          <t>Verify Load more no longer appears once all classes are loaded</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">#20 — Verify load more classes in classes tab</t>
+          <t>#20 — Verify load more classes in classes tab</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edge</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Load more link is visible.</t>
+          <t>A Load more link is visible.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Load more repeatedly until all classes show.</t>
+          <t>1. Click Load more repeatedly until all classes show.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">After the last batch, Load more is no longer shown. [ASSUMED] confirm hide vs disable.</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>After the last batch, Load more is no longer shown. [ASSUMED] confirm hide vs disable.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GCAT_TC_1</t>
+          <t>TST_GCAT_TC_1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the Manage grading categories page loads with all components</t>
+          <t>Verify the Manage grading categories page loads with all components</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">#4 — Verify manage grading category page</t>
+          <t>#4 — Verify manage grading category page</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Logged in as school admin, inside school FCN-CHZ-PDA.</t>
+          <t>Logged in as school admin, inside school FCN-CHZ-PDA.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click School settings. 2. Click Manage grading categories.</t>
+          <t>1. Click School settings. 2. Click Manage grading categories.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manage grading categories page opens (/manage-grading-categories) with heading, description, Create a grading category button, and a categories list where each row has Open grade options (See details, Remove).</t>
+          <t>Manage grading categories page opens (/manage-grading-categories) with heading, description, Create a grading category button, and a categories list where each row has Open grade options (See details, Remove).</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reached via the School settings dropdown.</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Reached via the School settings dropdown.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GCAT_TC_2</t>
+          <t>TST_GCAT_TC_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a grading category is created with a valid name</t>
+          <t>Verify a grading category is created with a valid name</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">#5 — Verify create grading category</t>
+          <t>#5 — Verify create grading category</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Manage grading categories page.</t>
+          <t>On the Manage grading categories page.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Create a grading category. 2. Enter AutoTest Category. 3. Click Save.</t>
+          <t>1. Click Create a grading category. 2. Enter AutoTest Category. 3. Click Save.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name: AutoTest Category</t>
+          <t>Name: AutoTest Category</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal closes; banner Grading category successfully created; category appears in the list.</t>
+          <t>Modal closes; banner Grading category successfully created; category appears in the list.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Repeated runs create duplicates (counts toward max).</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Repeated runs create duplicates (counts toward max).</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GCAT_TC_3</t>
+          <t>TST_GCAT_TC_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a grading category name at the 50-character maximum is accepted</t>
+          <t>Verify a grading category name at the 50-character maximum is accepted</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">#5 — Verify create grading category</t>
+          <t>#5 — Verify create grading category</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edge</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Create a grading category modal.</t>
+          <t>On the Create a grading category modal.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Enter a 50-character name. 2. Click Save.</t>
+          <t>1. Enter a 50-character name. 2. Click Save.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">50-char name</t>
+          <t>50-char name</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name accepted (maxlength 50) and category created. [ASSUMED] confirm truncation at 50.</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Name accepted (maxlength 50) and category created. [ASSUMED] confirm truncation at 50.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GCAT_TC_4</t>
+          <t>TST_GCAT_TC_4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the maximum-grading-categories limit is enforced</t>
+          <t>Verify the maximum-grading-categories limit is enforced</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">#5 — Verify create grading category</t>
+          <t>#5 — Verify create grading category</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edge</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">School already at the maximum number of grading categories.</t>
+          <t>School already at the maximum number of grading categories.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Attempt to create another grading category.</t>
+          <t>1. Attempt to create another grading category.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal: You have reached the maximum number of grading categories for your school. Please remove at least one category to add a new one; no category created. [ASSUMED] exact max count.</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Modal: You have reached the maximum number of grading categories for your school. Please remove at least one category to add a new one; no category created. [ASSUMED] exact max count.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GCAT_TC_5</t>
+          <t>TST_GCAT_TC_5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a grading category cannot be created with an empty name</t>
+          <t>Verify a grading category cannot be created with an empty name</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">#5 — Verify create grading category</t>
+          <t>#5 — Verify create grading category</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negative</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Create a grading category modal.</t>
+          <t>On the Create a grading category modal.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Leave name empty. 2. Observe Save.</t>
+          <t>1. Leave name empty. 2. Observe Save.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name: (empty)</t>
+          <t>Name: (empty)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Save is disabled while empty; empty-named category cannot be created.</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Save is disabled while empty; empty-named category cannot be created.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GCAT_TC_6</t>
+          <t>TST_GCAT_TC_6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the grading category See details page opens</t>
+          <t>Verify the grading category See details page opens</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">#6 — Verify see details page of a grading category</t>
+          <t>#6 — Verify see details page of a grading category</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Manage grading categories page with &gt;=1 category.</t>
+          <t>On the Manage grading categories page with &gt;=1 category.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open grade options on a category. 2. Click See details.</t>
+          <t>1. Open grade options on a category. 2. Click See details.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Category: AutoTest Category</t>
+          <t>Category: AutoTest Category</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Details page opens (/manage-grading-categories/&lt;id&gt;/classes, title=category name) showing Active classes (N); empty state The category has not been added to any active classes.</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Details page opens (/manage-grading-categories/&lt;id&gt;/classes, title=category name) showing Active classes (N); empty state The category has not been added to any active classes.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GCAT_TC_7</t>
+          <t>TST_GCAT_TC_7</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the class grade settings page launches from a category's details page</t>
+          <t>Verify the class grade settings page launches from a category's details page</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">#7 — Launch class grade setting page from see details page of grading category</t>
+          <t>#7 — Launch class grade setting page from see details page of grading category</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">The grading category is applied to &gt;=1 active class.</t>
+          <t>The grading category is applied to &gt;=1 active class.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open the category's See details page. 2. Click a listed class under Active classes.</t>
+          <t>1. Open the category's See details page. 2. Click a listed class under Active classes.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">A category applied to a class [ASSUMED]</t>
+          <t>A category applied to a class [ASSUMED]</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">The class grade settings page opens for the selected class. [ASSUMED] exact destination pending a category applied to a class.</t>
+          <t>The class grade settings page opens for the selected class. [ASSUMED] exact destination pending a category applied to a class.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Requires applying a category to a class first.</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Requires applying a category to a class first.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GCAT_TC_8</t>
+          <t>TST_GCAT_TC_8</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a grading category is removed after confirmation</t>
+          <t>Verify a grading category is removed after confirmation</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">#8 — Verify delete grading category</t>
+          <t>#8 — Verify delete grading category</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Manage grading categories page with &gt;=1 removable category.</t>
+          <t>On the Manage grading categories page with &gt;=1 removable category.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open grade options. 2. Click Remove. 3. Click Yes, remove.</t>
+          <t>1. Open grade options. 2. Click Remove. 3. Click Yes, remove.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Category: AutoTest Category</t>
+          <t>Category: AutoTest Category</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confirmation modal (Remove grading category - Are you sure? Removing the category will not affect classes currently using it, but you will not be able to add it to any new classes); after Yes, remove -&gt; banner Grading category successfully removed; category gone.</t>
+          <t>Confirmation modal (Remove grading category - Are you sure? Removing the category will not affect classes currently using it, but you will not be able to add it to any new classes); after Yes, remove -&gt; banner Grading category successfully removed; category gone.</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removal does not affect classes already using it.</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Removal does not affect classes already using it.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GCAT_TC_9</t>
+          <t>TST_GCAT_TC_9</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify removing a grading category can be cancelled</t>
+          <t>Verify removing a grading category can be cancelled</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">#8 — Verify delete grading category</t>
+          <t>#8 — Verify delete grading category</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edge</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Manage grading categories page with &gt;=1 category.</t>
+          <t>On the Manage grading categories page with &gt;=1 category.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open grade options -&gt; Remove. 2. Click No, go back.</t>
+          <t>1. Open grade options -&gt; Remove. 2. Click No, go back.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confirmation closes; category remains in the list (not removed).</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Confirmation closes; category remains in the list (not removed).</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_1</t>
+          <t>TST_BCCF_TC_1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the Create new classes (bulk) form loads with all components</t>
+          <t>Verify the Create new classes (bulk) form loads with all components</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Classes tab.</t>
+          <t>On the Classes tab.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Add class.</t>
+          <t>1. Click Add class.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Create new classes form opens (/class/create) with subtitle in &lt;school&gt;, Upload file, Get CSV template, How to use this form, bulk-action toolbar (Start date, End date, Add teacher, Add labels, Add Material, Copy an Existing Class, Duplicate, Show student progress, Remove), and a class row (Class name, Start date, End date, Add teachers, Add materials, Add label). Create N class is disabled.</t>
+          <t>Create new classes form opens (/class/create) with subtitle in &lt;school&gt;, Upload file, Get CSV template, How to use this form, bulk-action toolbar (Start date, End date, Add teacher, Add labels, Add Material, Copy an Existing Class, Duplicate, Show student progress, Remove), and a class row (Class name, Start date, End date, Add teachers, Add materials, Add label). Create N class is disabled.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Form auto-saves a draft.</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Form auto-saves a draft.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_2</t>
+          <t>TST_BCCF_TC_2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a single class is created with a name and start/end dates</t>
+          <t>Verify a single class is created with a name and start/end dates</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Create new classes form.</t>
+          <t>On the Create new classes form.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Enter class name. 2. Set Start date (today). 3. Set End date. 4. Click Create 1 class.</t>
+          <t>1. Enter class name. 2. Set Start date (today). 3. Set End date. 4. Click Create 1 class.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name AutoClass_Bulk, Start today, End next month</t>
+          <t>Name AutoClass_Bulk, Start today, End next month</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Success dialog Success! We are now creating 1 class for you appears; creation is asynchronous (email report; up to 12 hours).</t>
+          <t>Success dialog Success! We are now creating 1 class for you appears; creation is asynchronous (email report; up to 12 hours).</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Covered by automation TST_CCLS_TC_1..4.</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Covered by automation TST_CCLS_TC_1..4.</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_3</t>
+          <t>TST_BCCF_TC_3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a teacher can be added to a class row</t>
+          <t>Verify a teacher can be added to a class row</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">A class row with a name entered.</t>
+          <t>A class row with a name entered.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Add teachers. 2. In Edit teachers modal, enter Email (and optional First/Last name). 3. Click Apply changes.</t>
+          <t>1. Click Add teachers. 2. In Edit teachers modal, enter Email (and optional First/Last name). 3. Click Apply changes.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teacher email: &lt;TEACHER_EMAIL&gt;</t>
+          <t>Teacher email: &lt;TEACHER_EMAIL&gt;</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teacher added to the class row. Modal notes changes only apply to this class.</t>
+          <t>Teacher added to the class row. Modal notes changes only apply to this class.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Email required; names optional.</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Email required; names optional.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_4</t>
+          <t>TST_BCCF_TC_4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a material can be added to a class row</t>
+          <t>Verify a material can be added to a class row</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">A class row with a name entered.</t>
+          <t>A class row with a name entered.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Add materials. 2. Search and select a material. 3. Click Add materials.</t>
+          <t>1. Click Add materials. 2. Search and select a material. 3. Click Add materials.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Material: dev_test_ebook_bundle_104_bundle</t>
+          <t>Material: dev_test_ebook_bundle_104_bundle</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Material attaches to the class row.</t>
+          <t>Material attaches to the class row.</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Covered by automation TST_CCLS_TC_5..7.</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Covered by automation TST_CCLS_TC_5..7.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_5</t>
+          <t>TST_BCCF_TC_5</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a label can be added to a class row</t>
+          <t>Verify a label can be added to a class row</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">A class row with a name entered.</t>
+          <t>A class row with a name entered.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Add class label. 2. Select an existing label (or + Create new label).</t>
+          <t>1. Click Add class label. 2. Select an existing label (or + Create new label).</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Label: VM1</t>
+          <t>Label: VM1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chosen label applied to the row; dropdown also offers + Create new label and Edit labels.</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Chosen label applied to the row; dropdown also offers + Create new label and Edit labels.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_6</t>
+          <t>TST_BCCF_TC_6</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify multiple classes are created at once (bulk)</t>
+          <t>Verify multiple classes are created at once (bulk)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Create new classes form.</t>
+          <t>On the Create new classes form.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Fill name + dates on row 1. 2. Fill row 2. 3. Click Create 2 classes.</t>
+          <t>1. Fill name + dates on row 1. 2. Fill row 2. 3. Click Create 2 classes.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 valid class rows</t>
+          <t>2 valid class rows</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Create button reflects the count (Create 2 classes); success dialog shown for N classes. Empty rows auto-append while filling.</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Create button reflects the count (Create 2 classes); success dialog shown for N classes. Empty rows auto-append while filling.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_7</t>
+          <t>TST_BCCF_TC_7</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify Duplicate copies a selected class row</t>
+          <t>Verify Duplicate copies a selected class row</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">At least one class row is filled.</t>
+          <t>At least one class row is filled.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Select a row. 2. Click Duplicate in the toolbar. 3. Confirm if prompted.</t>
+          <t>1. Select a row. 2. Click Duplicate in the toolbar. 3. Confirm if prompted.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">A duplicate row is added with the same details. [ASSUMED] confirm exact behaviour/confirmation.</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>A duplicate row is added with the same details. [ASSUMED] confirm exact behaviour/confirmation.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">39</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_8</t>
+          <t>TST_BCCF_TC_8</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify Copy an Existing Class copies settings to selected rows</t>
+          <t>Verify Copy an Existing Class copies settings to selected rows</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">At least one class row selected.</t>
+          <t>At least one class row selected.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Select row(s). 2. Click Copy an Existing Class. 3. Choose a source class and what to copy. 4. Continue.</t>
+          <t>1. Select row(s). 2. Click Copy an Existing Class. 3. Choose a source class and what to copy. 4. Continue.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Source class: &lt;EXISTING_CLASS&gt; [ASSUMED]</t>
+          <t>Source class: &lt;EXISTING_CLASS&gt; [ASSUMED]</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal lets you choose an existing class and what to copy (materials/teachers/settings) to selected rows. [ASSUMED] confirm options/flow.</t>
+          <t>Modal lets you choose an existing class and what to copy (materials/teachers/settings) to selected rows. [ASSUMED] confirm options/flow.</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toolbar aria-label: Choose what to copy from an existing class to the selected classes.</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Toolbar aria-label: Choose what to copy from an existing class to the selected classes.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">40</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_9</t>
+          <t>TST_BCCF_TC_9</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify bulk-setting start/end date for multiple selected rows</t>
+          <t>Verify bulk-setting start/end date for multiple selected rows</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two or more class rows exist.</t>
+          <t>Two or more class rows exist.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Select multiple rows. 2. Click Start date in the toolbar and pick a date. 3. Click End date and pick a date.</t>
+          <t>1. Select multiple rows. 2. Click Start date in the toolbar and pick a date. 3. Click End date and pick a date.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chosen start/end dates apply to all selected rows at once.</t>
+          <t>Chosen start/end dates apply to all selected rows at once.</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Same pattern for bulk Add teacher/labels/material.</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Same pattern for bulk Add teacher/labels/material.</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_10</t>
+          <t>TST_BCCF_TC_10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify Get CSV template downloads the upload template</t>
+          <t>Verify Get CSV template downloads the upload template</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Create new classes form.</t>
+          <t>On the Create new classes form.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Get CSV template.</t>
+          <t>1. Click Get CSV template.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">A CSV template downloads with the correct headers for bulk class creation. [ASSUMED] capture exact headers.</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>A CSV template downloads with the correct headers for bulk class creation. [ASSUMED] capture exact headers.</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_11</t>
+          <t>TST_BCCF_TC_11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify uploading a CSV bulk-creates classes</t>
+          <t>Verify uploading a CSV bulk-creates classes</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">A populated CSV in the template format is available.</t>
+          <t>A populated CSV in the template format is available.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Upload file. 2. Select the CSV. 3. Wait for upload to complete.</t>
+          <t>1. Click Upload file. 2. Select the CSV. 3. Wait for upload to complete.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;BULK_CLASSES_CSV&gt; [ASSUMED]</t>
+          <t>&lt;BULK_CLASSES_CSV&gt; [ASSUMED]</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classes from the CSV are added/created; an upload progress indicator shows during processing. [ASSUMED] confirm flow/validation.</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Classes from the CSV are added/created; an upload progress indicator shows during processing. [ASSUMED] confirm flow/validation.</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_12</t>
+          <t>TST_BCCF_TC_12</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify Back to dashboard and Create more classes from the success dialog</t>
+          <t>Verify Back to dashboard and Create more classes from the success dialog</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">A class was just created (success dialog shown).</t>
+          <t>A class was just created (success dialog shown).</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Back to dashboard. 2. (Separately) create again and click Create more classes.</t>
+          <t>1. Click Back to dashboard. 2. (Separately) create again and click Create more classes.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back to dashboard returns to the school Classes page; Create more classes returns to a fresh Create form. [ASSUMED] confirm form reset.</t>
+          <t>Back to dashboard returns to the school Classes page; Create more classes returns to a fresh Create form. [ASSUMED] confirm form reset.</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back to dashboard covered by automation TST_CCLS_TC_8.</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Back to dashboard covered by automation TST_CCLS_TC_8.</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_13</t>
+          <t>TST_BCCF_TC_13</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a class name at the 50-character maximum is accepted</t>
+          <t>Verify a class name at the 50-character maximum is accepted</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edge</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">On a class row.</t>
+          <t>On a class row.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Enter a 50-character class name.</t>
+          <t>1. Enter a 50-character class name.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">50-char name</t>
+          <t>50-char name</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name accepted (maxlength 50); no more than 50 characters can be entered.</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Name accepted (maxlength 50); no more than 50 characters can be entered.</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_14</t>
+          <t>TST_BCCF_TC_14</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the end date cannot be set before the start date</t>
+          <t>Verify the end date cannot be set before the start date</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edge</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">A start date is set on a row.</t>
+          <t>A start date is set on a row.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open the End date picker.</t>
+          <t>1. Open the End date picker.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start = today</t>
+          <t>Start = today</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dates on/before the start date are disabled in the end-date picker; end &lt; start cannot be chosen.</t>
+          <t>Dates on/before the start date are disabled in the end-date picker; end &lt; start cannot be chosen.</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Observed: days &lt;= start are owl-dt-calendar-cell-disabled.</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Observed: days &lt;= start are owl-dt-calendar-cell-disabled.</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">46</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_15</t>
+          <t>TST_BCCF_TC_15</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify Create is disabled until class name and both dates are provided</t>
+          <t>Verify Create is disabled until class name and both dates are provided</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negative</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Create new classes form.</t>
+          <t>On the Create new classes form.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Fill only some of {name, start, end} on a row. 2. Observe the Create button.</t>
+          <t>1. Fill only some of {name, start, end} on a row. 2. Observe the Create button.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Incomplete row</t>
+          <t>Incomplete row</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Create N class button stays disabled until the row has name AND start date AND end date.</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Create N class button stays disabled until the row has name AND start date AND end date.</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_16</t>
+          <t>TST_BCCF_TC_16</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify an empty or non-alphanumeric class name is rejected</t>
+          <t>Verify an empty or non-alphanumeric class name is rejected</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negative</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">On a class row.</t>
+          <t>On a class row.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Leave the class name empty, or enter only non-alphanumeric characters (e.g. ---). 2. Attempt to create.</t>
+          <t>1. Leave the class name empty, or enter only non-alphanumeric characters (e.g. ---). 2. Attempt to create.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name: (empty) / ---</t>
+          <t>Name: (empty) / ---</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Row is invalid - name requires at least one alphanumeric character (pattern .*[A-Za-z0-9]+.*) - so the class cannot be created. [ASSUMED] capture any inline error text.</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Row is invalid - name requires at least one alphanumeric character (pattern .*[A-Za-z0-9]+.*) - so the class cannot be created. [ASSUMED] capture any inline error text.</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GSCL_TC_1</t>
+          <t>TST_GSCL_TC_1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the Manage grading scales page loads with all components</t>
+          <t>Verify the Manage grading scales page loads with all components</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">#10 — Verify manage grading scales page</t>
+          <t>#10 — Verify manage grading scales page</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Logged in as school admin, inside school FCN-CHZ-PDA.</t>
+          <t>Logged in as school admin, inside school FCN-CHZ-PDA.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click School settings. 2. Click Manage grading scales.</t>
+          <t>1. Click School settings. 2. Click Manage grading scales.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grading scales page opens (/grading-scales/manage) with heading Grading scales, User guide, Create grading scale button, and a list of scales. Cambridge One grading scale shows a default badge and only View details; custom scales offer View details / Set as default / Delete via Open drop down.</t>
+          <t>Grading scales page opens (/grading-scales/manage) with heading Grading scales, User guide, Create grading scale button, and a list of scales. Cambridge One grading scale shows a default badge and only View details; custom scales offer View details / Set as default / Delete via Open drop down.</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reached via School settings dropdown.</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Reached via School settings dropdown.</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">49</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GSCL_TC_2</t>
+          <t>TST_GSCL_TC_2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a grading scale is created with a title, bands and target score</t>
+          <t>Verify a grading scale is created with a title, bands and target score</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">#11 — Verify Create grading scale</t>
+          <t>#11 — Verify Create grading scale</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Grading scales page.</t>
+          <t>On the Grading scales page.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Create grading scale. 2. Enter title. 3. Enter Highest grade name + From %. 4. Enter Lowest grade name + To %. 5. Mark a band as Set as target score. 6. Click Save grading scale.</t>
+          <t>1. Click Create grading scale. 2. Enter title. 3. Enter Highest grade name + From %. 4. Enter Lowest grade name + To %. 5. Mark a band as Set as target score. 6. Click Save grading scale.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Title AutoTest Scale; Highest A 50-100%; Lowest F 0-49%; target A</t>
+          <t>Title AutoTest Scale; Highest A 50-100%; Lowest F 0-49%; target A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scale created and appears in the list showing its target score; bands cover 0-100% without overlap.</t>
+          <t>Scale created and appears in the list showing its target score; bands cover 0-100% without overlap.</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Highest To fixed 100%, Lowest From fixed 0%.</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Highest To fixed 100%, Lowest From fixed 0%.</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GSCL_TC_3</t>
+          <t>TST_GSCL_TC_3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a middle band can be added with + Add new grade</t>
+          <t>Verify a middle band can be added with + Add new grade</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">#11 — Verify Create grading scale</t>
+          <t>#11 — Verify Create grading scale</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Create grading scale form.</t>
+          <t>On the Create grading scale form.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click + Add new grade. 2. Enter the middle band name + From-To %.</t>
+          <t>1. Click + Add new grade. 2. Enter the middle band name + From-To %.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Middle band B 50-79%, adjust others to keep 0-100% coverage</t>
+          <t>Middle band B 50-79%, adjust others to keep 0-100% coverage</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">A middle band row is added between Highest and Lowest; bands must still cover 0-100% without overlap.</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>A middle band row is added between Highest and Lowest; bands must still cover 0-100% without overlap.</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GSCL_TC_4</t>
+          <t>TST_GSCL_TC_4</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the maximum-grading-scales limit is enforced</t>
+          <t>Verify the maximum-grading-scales limit is enforced</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">#11 — Verify Create grading scale</t>
+          <t>#11 — Verify Create grading scale</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edge</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">School already at the maximum number of grading scales.</t>
+          <t>School already at the maximum number of grading scales.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Attempt to create another grading scale.</t>
+          <t>1. Attempt to create another grading scale.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal: You have reached the maximum number of grading scales for this school. Please remove at least one grading scale to add a new one; no scale created. [ASSUMED] exact maximum.</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Modal: You have reached the maximum number of grading scales for this school. Please remove at least one grading scale to add a new one; no scale created. [ASSUMED] exact maximum.</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GSCL_TC_5</t>
+          <t>TST_GSCL_TC_5</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify Save is disabled until title, valid bands and target are provided</t>
+          <t>Verify Save is disabled until title, valid bands and target are provided</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">#11 — Verify Create grading scale</t>
+          <t>#11 — Verify Create grading scale</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negative</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Create grading scale form.</t>
+          <t>On the Create grading scale form.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Leave title empty, or set bands that overlap / do not add up to 100%, or omit the target. 2. Observe Save grading scale.</t>
+          <t>1. Leave title empty, or set bands that overlap / do not add up to 100%, or omit the target. 2. Observe Save grading scale.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Incomplete/invalid bands</t>
+          <t>Incomplete/invalid bands</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Save grading scale stays disabled until the scale has a title, bands covering 0-100% without overlap, and a target score. [ASSUMED] capture overlap/gap validation copy.</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Save grading scale stays disabled until the scale has a title, bands covering 0-100% without overlap, and a target score. [ASSUMED] capture overlap/gap validation copy.</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GSCL_TC_6</t>
+          <t>TST_GSCL_TC_6</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the grading scale View details page opens</t>
+          <t>Verify the grading scale View details page opens</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">#12 — Verify view details page of grading scale</t>
+          <t>#12 — Verify view details page of grading scale</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Grading scales page with &gt;=1 scale.</t>
+          <t>On the Grading scales page with &gt;=1 scale.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Open drop down on a scale. 2. Click View details.</t>
+          <t>1. Click Open drop down on a scale. 2. Click View details.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scale: AutoTest Scale</t>
+          <t>Scale: AutoTest Scale</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Details page opens (/grading-scales/&lt;id&gt;, title=scale name) with a collapsible Grading scale bands section and a Classes (N) section; empty state No classes yet. To associate the grading scale with a class, go to its Class grade settings page.</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Details page opens (/grading-scales/&lt;id&gt;, title=scale name) with a collapsible Grading scale bands section and a Classes (N) section; empty state No classes yet. To associate the grading scale with a class, go to its Class grade settings page.</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GSCL_TC_7</t>
+          <t>TST_GSCL_TC_7</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the class grade settings page launches from a scale's details page</t>
+          <t>Verify the class grade settings page launches from a scale's details page</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">#13 — Launch class grade setting page from view details page of grading scale</t>
+          <t>#13 — Launch class grade setting page from view details page of grading scale</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">The grading scale is applied to &gt;=1 class.</t>
+          <t>The grading scale is applied to &gt;=1 class.</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open the scale's View details page. 2. Click a listed class under Classes.</t>
+          <t>1. Open the scale's View details page. 2. Click a listed class under Classes.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">A scale applied to a class [ASSUMED]</t>
+          <t>A scale applied to a class [ASSUMED]</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">The class grade settings page opens for the selected class. [ASSUMED] exact destination pending a scale applied to a class.</t>
+          <t>The class grade settings page opens for the selected class. [ASSUMED] exact destination pending a scale applied to a class.</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Associate a scale with a class via class grade settings first.</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Associate a scale with a class via class grade settings first.</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GSCL_TC_8</t>
+          <t>TST_GSCL_TC_8</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a grading scale can be set as the school default</t>
+          <t>Verify a grading scale can be set as the school default</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">#14 — Verify set as default for a grading scale</t>
+          <t>#14 — Verify set as default for a grading scale</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">A custom (non-default) grading scale exists.</t>
+          <t>A custom (non-default) grading scale exists.</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open the custom scale's Open drop down -&gt; Set as default. 2. Click Yes, set as default.</t>
+          <t>1. Open the custom scale's Open drop down -&gt; Set as default. 2. Click Yes, set as default.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scale: AutoTest Scale</t>
+          <t>Scale: AutoTest Scale</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confirmation Set as default for the school? All newly created classes will be associated with this grading scale. Existing classes will not be affected; after Yes the scale becomes default (badge moves to it).</t>
+          <t>Confirmation Set as default for the school? All newly created classes will be associated with this grading scale. Existing classes will not be affected; after Yes the scale becomes default (badge moves to it).</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Only non-default scales offer Set as default.</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Only non-default scales offer Set as default.</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GSCL_TC_9</t>
+          <t>TST_GSCL_TC_9</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a grading scale is deleted after confirmation</t>
+          <t>Verify a grading scale is deleted after confirmation</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">#15 — Verify deleting a grading scale</t>
+          <t>#15 — Verify deleting a grading scale</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">A deletable (non-default) grading scale exists.</t>
+          <t>A deletable (non-default) grading scale exists.</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open the scale's Open drop down -&gt; Delete. 2. Click Yes, delete.</t>
+          <t>1. Open the scale's Open drop down -&gt; Delete. 2. Click Yes, delete.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scale: AutoTest Scale</t>
+          <t>Scale: AutoTest Scale</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confirmation Are you sure? Deleting the grading scale will not affect classes associated with it, but it won't be available to apply to any new classes.; after Yes, delete the scale is removed from the list.</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Confirmation Are you sure? Deleting the grading scale will not affect classes associated with it, but it won't be available to apply to any new classes.; after Yes, delete the scale is removed from the list.</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GSCL_TC_10</t>
+          <t>TST_GSCL_TC_10</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify deleting a grading scale can be cancelled</t>
+          <t>Verify deleting a grading scale can be cancelled</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">#15 — Verify deleting a grading scale</t>
+          <t>#15 — Verify deleting a grading scale</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edge</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">A deletable grading scale exists.</t>
+          <t>A deletable grading scale exists.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open drop down -&gt; Delete. 2. Click No, go back.</t>
+          <t>1. Open drop down -&gt; Delete. 2. Click No, go back.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confirmation closes; scale remains in the list (not deleted).</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Confirmation closes; scale remains in the list (not deleted).</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GSCL_TC_11</t>
+          <t>TST_GSCL_TC_11</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the default grading scale cannot be deleted</t>
+          <t>Verify the default grading scale cannot be deleted</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">#15 — Verify deleting a grading scale</t>
+          <t>#15 — Verify deleting a grading scale</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negative</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Grading scales page (Cambridge One grading scale is default).</t>
+          <t>On the Grading scales page (Cambridge One grading scale is default).</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open the Open drop down on the default scale.</t>
+          <t>1. Open the Open drop down on the default scale.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Default scale: Cambridge One grading scale</t>
+          <t>Default scale: Cambridge One grading scale</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">The default scale's menu offers only View details - no Delete (nor Set as default) - so the default scale cannot be deleted.</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>The default scale's menu offers only View details - no Delete (nor Set as default) - so the default scale cannot be deleted.</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">59</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GSCL_TC_12</t>
+          <t>TST_GSCL_TC_12</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify expanding the grading scale bands shows the bands</t>
+          <t>Verify expanding the grading scale bands shows the bands</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">#16 — Verify expanding grading scale bands</t>
+          <t>#16 — Verify expanding grading scale bands</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">On a grading scale's View details page.</t>
+          <t>On a grading scale's View details page.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Grading scale bands.</t>
+          <t>1. Click Grading scale bands.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scale: AutoTest Scale</t>
+          <t>Scale: AutoTest Scale</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Section expands to list bands as Grade name / Band (e.g. A -&gt; 50% - 100% with Target score: 50%, F -&gt; 0% - 49%).</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Section expands to list bands as Grade name / Band (e.g. A -&gt; 50% - 100% with Target score: 50%, F -&gt; 0% - 49%).</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CMGT_TC_1</t>
+          <t>TST_CMGT_TC_1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify an existing label can be added to a class</t>
+          <t>Verify an existing label can be added to a class</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">#21 — Add label in class</t>
+          <t>#21 — Add label in class</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">A class is open (Classes tab -&gt; launch a class -&gt; /view/classdata).</t>
+          <t>A class is open (Classes tab -&gt; launch a class -&gt; /view/classdata).</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click + Add labels. 2. Select an existing label.</t>
+          <t>1. Click + Add labels. 2. Select an existing label.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Label: VM1</t>
+          <t>Label: VM1</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">The selected label is applied to the class and shown on it.</t>
+          <t>The selected label is applied to the class and shown on it.</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Same label list as bulk-create form (TST_BCCF_TC_5).</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Same label list as bulk-create form (TST_BCCF_TC_5).</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CMGT_TC_2</t>
+          <t>TST_CMGT_TC_2</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a new label can be created and applied to a class</t>
+          <t>Verify a new label can be created and applied to a class</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">#21 — Add label in class</t>
+          <t>#21 — Add label in class</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">A class is open.</t>
+          <t>A class is open.</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click + Add labels. 2. Click + Create new label. 3. Enter a label name and save.</t>
+          <t>1. Click + Add labels. 2. Click + Create new label. 3. Enter a label name and save.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">New label: AutoTest Label</t>
+          <t>New label: AutoTest Label</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">New label is created, applied to the class, and becomes available for other classes. [ASSUMED] confirm create-label form.</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>New label is created, applied to the class, and becomes available for other classes. [ASSUMED] confirm create-label form.</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CMGT_TC_3</t>
+          <t>TST_CMGT_TC_3</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify soft-deleting a single active class</t>
+          <t>Verify soft-deleting a single active class</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">#23 — Verify delete classes (soft / hard / bulk up to 50)</t>
+          <t>#23 — Verify delete classes (soft / hard / bulk up to 50)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Classes tab with &gt;=1 active class.</t>
+          <t>On the Classes tab with &gt;=1 active class.</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Select a class row checkbox. 2. Click Delete class. 3. Click Yes, delete 1 class.</t>
+          <t>1. Select a class row checkbox. 2. Click Delete class. 3. Click Yes, delete 1 class.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">An active class</t>
+          <t>An active class</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">WARNING confirmation shown (1 selected class has not ended. There might be students, teachers and course materials... Are you sure you want to delete?). After Yes, class removed from Active and moved to deleted/Ended section (soft delete). Note: This will take a few minutes. Deleted classes may show on dashboards for a few minutes before they are removed.</t>
+          <t>WARNING confirmation shown (1 selected class has not ended. There might be students, teachers and course materials... Are you sure you want to delete?). After Yes, class removed from Active and moved to deleted/Ended section (soft delete). Note: This will take a few minutes. Deleted classes may show on dashboards for a few minutes before they are removed.</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Soft delete is restorable.</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Soft delete is restorable.</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t>63</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CMGT_TC_4</t>
+          <t>TST_CMGT_TC_4</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify bulk-deleting multiple classes</t>
+          <t>Verify bulk-deleting multiple classes</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">#23 — Verify delete classes (soft / hard / bulk up to 50)</t>
+          <t>#23 — Verify delete classes (soft / hard / bulk up to 50)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Classes tab with &gt;=2 active classes.</t>
+          <t>On the Classes tab with &gt;=2 active classes.</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Select multiple class checkboxes (or select-all). 2. Click Delete class. 3. Confirm Yes, delete N classes.</t>
+          <t>1. Select multiple class checkboxes (or select-all). 2. Click Delete class. 3. Confirm Yes, delete N classes.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multiple classes</t>
+          <t>Multiple classes</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selected classes are soft-deleted together; confirmation reflects the count (Yes, delete N classes).</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Selected classes are soft-deleted together; confirmation reflects the count (Yes, delete N classes).</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">64</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CMGT_TC_5</t>
+          <t>TST_CMGT_TC_5</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a class can be permanently (hard) deleted when all conditions are met</t>
+          <t>Verify a class can be permanently (hard) deleted when all conditions are met</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">#23 — Verify delete classes (soft / hard / bulk up to 50)</t>
+          <t>#23 — Verify delete classes (soft / hard / bulk up to 50)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">A deleted class with: no students; &lt;=1 teacher (the deleter) or none; no groups; no assignments; no grading scales; no grading categories; no locking/unlocking rules.</t>
+          <t>A deleted class with: no students; &lt;=1 teacher (the deleter) or none; no groups; no assignments; no grading scales; no grading categories; no locking/unlocking rules.</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open the deleted class (Deleted filter / Ended section). 2. Choose the permanent-delete option. 3. Confirm.</t>
+          <t>1. Open the deleted class (Deleted filter / Ended section). 2. Choose the permanent-delete option. 3. Confirm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">A deleted class meeting all 7 conditions</t>
+          <t>A deleted class meeting all 7 conditions</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">The class is permanently removed and can no longer be restored. [ASSUMED] capture the exact permanent-delete UI/location.</t>
+          <t>The class is permanently removed and can no longer be restored. [ASSUMED] capture the exact permanent-delete UI/location.</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">The 7 conditions (per AdminApp.xlsx) must all be satisfied.</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>The 7 conditions (per AdminApp.xlsx) must all be satisfied.</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">65</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CMGT_TC_6</t>
+          <t>TST_CMGT_TC_6</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify bulk delete supports up to 50 classes</t>
+          <t>Verify bulk delete supports up to 50 classes</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">#23 — Verify delete classes (soft / hard / bulk up to 50)</t>
+          <t>#23 — Verify delete classes (soft / hard / bulk up to 50)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edge</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Classes tab with many classes.</t>
+          <t>On the Classes tab with many classes.</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Select up to 50 classes. 2. Click Delete class and confirm.</t>
+          <t>1. Select up to 50 classes. 2. Click Delete class and confirm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 classes</t>
+          <t>50 classes</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Up to 50 classes can be selected and deleted in one action. [ASSUMED] confirm the 50-class maximum.</t>
+          <t>Up to 50 classes can be selected and deleted in one action. [ASSUMED] confirm the 50-class maximum.</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scenario title references 50 classes.</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Scenario title references 50 classes.</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CMGT_TC_7</t>
+          <t>TST_CMGT_TC_7</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify deleting a class can be cancelled</t>
+          <t>Verify deleting a class can be cancelled</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">#23 — Verify delete classes (soft / hard / bulk up to 50)</t>
+          <t>#23 — Verify delete classes (soft / hard / bulk up to 50)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edge</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Classes tab with &gt;=1 class selected.</t>
+          <t>On the Classes tab with &gt;=1 class selected.</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Delete class. 2. Click No, cancel.</t>
+          <t>1. Click Delete class. 2. Click No, cancel.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confirmation closes; class is not deleted.</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Confirmation closes; class is not deleted.</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CMGT_TC_8</t>
+          <t>TST_CMGT_TC_8</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a class cannot be permanently deleted when conditions are not met</t>
+          <t>Verify a class cannot be permanently deleted when conditions are not met</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">#23 — Verify delete classes (soft / hard / bulk up to 50)</t>
+          <t>#23 — Verify delete classes (soft / hard / bulk up to 50)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negative</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">A class that still has students / another teacher / groups / assignments / grading scales / grading categories / locking rules.</t>
+          <t>A class that still has students / another teacher / groups / assignments / grading scales / grading categories / locking rules.</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Attempt to permanently delete it.</t>
+          <t>1. Attempt to permanently delete it.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">A class violating &gt;=1 of the 7 conditions</t>
+          <t>A class violating &gt;=1 of the 7 conditions</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Permanent deletion is blocked/unavailable until all 7 conditions are satisfied. [ASSUMED] capture the exact blocking behaviour/message.</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Permanent deletion is blocked/unavailable until all 7 conditions are satisfied. [ASSUMED] capture the exact blocking behaviour/message.</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">68</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CMGT_TC_9</t>
+          <t>TST_CMGT_TC_9</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the active-class count increases after adding a new class</t>
+          <t>Verify the active-class count increases after adding a new class</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">#30 — Verify count of classes increase on adding a new class</t>
+          <t>#30 — Verify count of classes increase on adding a new class</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Classes tab.</t>
+          <t>On the Classes tab.</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Note the current Active classes (N). 2. Add a class (Add class -&gt; fill name + dates -&gt; Create). 3. After processing, refresh the Classes tab.</t>
+          <t>1. Note the current Active classes (N). 2. Add a class (Add class -&gt; fill name + dates -&gt; Create). 3. After processing, refresh the Classes tab.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">One new class</t>
+          <t>One new class</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Once the asynchronous creation completes, the Active classes count increases by 1 (N -&gt; N+1).</t>
+          <t>Once the asynchronous creation completes, the Active classes count increases by 1 (N -&gt; N+1).</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Creation is async; count updates after processing. Aligns with automation baseline TST_SCLS_TC_1.</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Creation is async; count updates after processing. Aligns with automation baseline TST_SCLS_TC_1.</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">69</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CGST_TC_1</t>
+          <t>TST_CGST_TC_1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the Class grade settings page launches from a class page</t>
+          <t>Verify the Class grade settings page launches from a class page</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">#22 — Launch class grade setting page from a class page</t>
+          <t>#22 — Launch class grade setting page from a class page</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">A class is open (Classes tab -&gt; launch a class).</t>
+          <t>A class is open (Classes tab -&gt; launch a class).</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. On the class page, open the Actions menu. 2. Click Class grade settings.</t>
+          <t>1. On the class page, open the Actions menu. 2. Click Class grade settings.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Class grade settings page opens (/class/.../grade-weighting) showing Grading Scale (+ Change), Score settings (teacher-override toggle), Score calculation (Best/First score), per-material Weightage %, Other grading categories (+ Add a grading category), Total grade: 100%, Save changes / Cancel.</t>
+          <t>Class grade settings page opens (/class/.../grade-weighting) showing Grading Scale (+ Change), Score settings (teacher-override toggle), Score calculation (Best/First score), per-material Weightage %, Other grading categories (+ Add a grading category), Total grade: 100%, Save changes / Cancel.</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Destination the grading category/scale details pages link to (TST_GCAT_TC_7, TST_GSCL_TC_7).</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Destination the grading category/scale details pages link to (TST_GCAT_TC_7, TST_GSCL_TC_7).</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">70</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CGST_TC_2</t>
+          <t>TST_CGST_TC_2</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the grading scale can be changed for a class</t>
+          <t>Verify the grading scale can be changed for a class</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">#22 — Launch class grade setting page from a class page</t>
+          <t>#22 — Launch class grade setting page from a class page</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Class grade settings page.</t>
+          <t>On the Class grade settings page.</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. In Grading Scale, click Change. 2. Select a grading scale. 3. Click Save changes.</t>
+          <t>1. In Grading Scale, click Change. 2. Select a grading scale. 3. Click Save changes.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">A grading scale (AutoTest Scale / Cambridge One grading scale)</t>
+          <t>A grading scale (AutoTest Scale / Cambridge One grading scale)</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Class grading scale updates to the selected scale; the class then appears under that scale's details. [ASSUMED] confirm change-scale selector.</t>
+          <t>Class grading scale updates to the selected scale; the class then appears under that scale's details. [ASSUMED] confirm change-scale selector.</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Associates a scale with a class - resolves TST_GSCL_TC_7.</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Associates a scale with a class - resolves TST_GSCL_TC_7.</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">71</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CGST_TC_3</t>
+          <t>TST_CGST_TC_3</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a grading category can be added to a class</t>
+          <t>Verify a grading category can be added to a class</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">#22 — Launch class grade setting page from a class page</t>
+          <t>#22 — Launch class grade setting page from a class page</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Class grade settings page.</t>
+          <t>On the Class grade settings page.</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Add a grading category. 2. Select a grading category. 3. Set its Weightage %. 4. Click Save changes.</t>
+          <t>1. Click Add a grading category. 2. Select a grading category. 3. Set its Weightage %. 4. Click Save changes.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">A grading category (some) + weightage</t>
+          <t>A grading category (some) + weightage</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grading category added to the class with a weightage; the class then appears under that category's details. [ASSUMED] confirm add-category selector.</t>
+          <t>Grading category added to the class with a weightage; the class then appears under that category's details. [ASSUMED] confirm add-category selector.</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Associates a category with a class - resolves TST_GCAT_TC_7.</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Associates a category with a class - resolves TST_GCAT_TC_7.</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">72</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CGST_TC_4</t>
+          <t>TST_CGST_TC_4</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the score calculation (Best / First score) can be changed</t>
+          <t>Verify the score calculation (Best / First score) can be changed</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">#22 — Launch class grade setting page from a class page</t>
+          <t>#22 — Launch class grade setting page from a class page</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Class grade settings page.</t>
+          <t>On the Class grade settings page.</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open the Score calculation dropdown. 2. Select First score (or Best score). 3. Click Save changes.</t>
+          <t>1. Open the Score calculation dropdown. 2. Select First score (or Best score). 3. Click Save changes.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Score type: First score</t>
+          <t>Score type: First score</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selected score type is saved as the score that counts toward students' progress.</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Selected score type is saved as the score that counts toward students' progress.</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">73</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CGST_TC_5</t>
+          <t>TST_CGST_TC_5</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the teacher score-override setting can be toggled</t>
+          <t>Verify the teacher score-override setting can be toggled</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">#22 — Launch class grade setting page from a class page</t>
+          <t>#22 — Launch class grade setting page from a class page</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Class grade settings page.</t>
+          <t>On the Class grade settings page.</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Toggle Allow teachers to override and add scores to auto-marked activities. 2. Click Save changes.</t>
+          <t>1. Toggle Allow teachers to override and add scores to auto-marked activities. 2. Click Save changes.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">The override setting is saved in the state it was toggled to.</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>The override setting is saved in the state it was toggled to.</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">74</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CGST_TC_6</t>
+          <t>TST_CGST_TC_6</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the total grade weightage must equal 100%</t>
+          <t>Verify the total grade weightage must equal 100%</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">#22 — Launch class grade setting page from a class page</t>
+          <t>#22 — Launch class grade setting page from a class page</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edge</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Class grade settings page with &gt;=1 material/category weightage.</t>
+          <t>On the Class grade settings page with &gt;=1 material/category weightage.</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Set weightages that do not add up to 100%. 2. Attempt to Save changes.</t>
+          <t>1. Set weightages that do not add up to 100%. 2. Attempt to Save changes.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weightages summing to != 100%</t>
+          <t>Weightages summing to != 100%</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saving is prevented / an error shown until Total grade equals 100%. [ASSUMED] confirm validation copy.</t>
+          <t>Saving is prevented / an error shown until Total grade equals 100%. [ASSUMED] confirm validation copy.</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Page shows a running Total grade: 100%.</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Page shows a running Total grade: 100%.</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">75</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLON_TC_1</t>
+          <t>TST_CLON_TC_1</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a class can be cloned from an existing class</t>
+          <t>Verify a class can be cloned from an existing class</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">#31 — Verify class clone functionality (Copy an Existing Class)</t>
+          <t>#31 — Verify class clone functionality (Copy an Existing Class)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Create new classes form with &gt;=1 row selected; a source class exists.</t>
+          <t>On the Create new classes form with &gt;=1 row selected; a source class exists.</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Copy an Existing Class. 2. Step 1: search and select the source class -&gt; Continue. 3. Step 2: on Choose what to copy from [source], select components -&gt; Continue.</t>
+          <t>1. Click Copy an Existing Class. 2. Step 1: search and select the source class -&gt; Continue. 3. Step 2: on Choose what to copy from [source], select components -&gt; Continue.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Source class: SarthakTestClass1</t>
+          <t>Source class: SarthakTestClass1</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Step 2 lists copyable components as checkboxes - Teachers, Course materials, Assignments, Locked content rules, Class grade settings - each with a count; selected components are copied from the source into the selected new row(s).</t>
+          <t>Step 2 lists copyable components as checkboxes - Teachers, Course materials, Assignments, Locked content rules, Class grade settings - each with a count; selected components are copied from the source into the selected new row(s).</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distinct from Duplicate (TST_BCCF_TC_7).</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Distinct from Duplicate (TST_BCCF_TC_7).</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">76</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLON_TC_2</t>
+          <t>TST_CLON_TC_2</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify all components copy from a fully-populated source class</t>
+          <t>Verify all components copy from a fully-populated source class</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">#31 — Verify class clone functionality (Copy an Existing Class)</t>
+          <t>#31 — Verify class clone functionality (Copy an Existing Class)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">A source class that HAS a teacher, course materials, assignments, locked content rules (incl. an assignment-created lock rule), and class grade settings.</t>
+          <t>A source class that HAS a teacher, course materials, assignments, locked content rules (incl. an assignment-created lock rule), and class grade settings.</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Copy an Existing Class -&gt; select the populated source. 2. Select all available components. 3. Continue and create.</t>
+          <t>1. Copy an Existing Class -&gt; select the populated source. 2. Select all available components. 3. Continue and create.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">A fully-populated source class [ASSUMED]</t>
+          <t>A fully-populated source class [ASSUMED]</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">The cloned class contains the source's teacher, materials, assignments, locked content rules (incl. the assignment-created rule), and class grade settings. [ASSUMED] verify each component copies (tested sources had 0 of each).</t>
+          <t>The cloned class contains the source's teacher, materials, assignments, locked content rules (incl. the assignment-created rule), and class grade settings. [ASSUMED] verify each component copies (tested sources had 0 of each).</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Requires a seeded source class.</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Requires a seeded source class.</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">77</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLON_TC_3</t>
+          <t>TST_CLON_TC_3</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify components with no items are not selectable when copying</t>
+          <t>Verify components with no items are not selectable when copying</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">#31 — Verify class clone functionality (Copy an Existing Class)</t>
+          <t>#31 — Verify class clone functionality (Copy an Existing Class)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edge</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">A source class that has 0 of one or more components.</t>
+          <t>A source class that has 0 of one or more components.</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Copy an Existing Class -&gt; select a source with empty components -&gt; Continue.</t>
+          <t>1. Copy an Existing Class -&gt; select a source with empty components -&gt; Continue.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Source: SarthakTestClass1 (0 teachers/materials/assignments/rules)</t>
+          <t>Source: SarthakTestClass1 (0 teachers/materials/assignments/rules)</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Components with a count of 0 are disabled/unselectable (e.g. Teachers [0] disabled; Class grade settings - Not available).</t>
+          <t>Components with a count of 0 are disabled/unselectable (e.g. Teachers [0] disabled; Class grade settings - Not available).</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Observed live.</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Observed live.</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">78</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CTXC_TC_1</t>
+          <t>TST_CTXC_TC_1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a context class can be created</t>
+          <t>Verify a context class can be created</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">#32 — Verify Context class creation and view in teacher/admin/student login</t>
+          <t>#32 — Verify Context class creation and view in teacher/admin/student login</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Logged in as school admin. [ASSUMED] context-class creation path TBD.</t>
+          <t>Logged in as school admin. [ASSUMED] context-class creation path TBD.</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Create a context class via the (to-be-confirmed) context-class creation flow.</t>
+          <t>1. Create a context class via the (to-be-confirmed) context-class creation flow.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Context class details [ASSUMED]</t>
+          <t>Context class details [ASSUMED]</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">The context class is created successfully. [ASSUMED] confirm the creation entry point and any context-specific fields.</t>
+          <t>The context class is created successfully. [ASSUMED] confirm the creation entry point and any context-specific fields.</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entry point not found in the admin bulk-create form; needs product clarification.</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Entry point not found in the admin bulk-create form; needs product clarification.</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">79</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CTXC_TC_2</t>
+          <t>TST_CTXC_TC_2</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the context class appears in the admin login</t>
+          <t>Verify the context class appears in the admin login</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">#32 — Verify Context class creation and view in teacher/admin/student login</t>
+          <t>#32 — Verify Context class creation and view in teacher/admin/student login</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">A context class exists; logged in as school admin.</t>
+          <t>A context class exists; logged in as school admin.</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open the school's Classes tab. 2. Locate the context class.</t>
+          <t>1. Open the school's Classes tab. 2. Locate the context class.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">The created context class</t>
+          <t>The created context class</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">The context class is listed and behaves as expected in the admin view. [ASSUMED] confirm admin-specific behaviour.</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>The context class is listed and behaves as expected in the admin view. [ASSUMED] confirm admin-specific behaviour.</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">80</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CTXC_TC_3</t>
+          <t>TST_CTXC_TC_3</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the context class appears/behaves correctly in the teacher login</t>
+          <t>Verify the context class appears/behaves correctly in the teacher login</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">#32 — Verify Context class creation and view in teacher/admin/student login</t>
+          <t>#32 — Verify Context class creation and view in teacher/admin/student login</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">A context class exists; a teacher account associated with it.</t>
+          <t>A context class exists; a teacher account associated with it.</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Log in as the teacher. 2. Locate/open the context class.</t>
+          <t>1. Log in as the teacher. 2. Locate/open the context class.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teacher account [ASSUMED]</t>
+          <t>Teacher account [ASSUMED]</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">The context class is visible and behaves correctly for the teacher role. [ASSUMED] needs a teacher test account.</t>
+          <t>The context class is visible and behaves correctly for the teacher role. [ASSUMED] needs a teacher test account.</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cross-role verification.</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Cross-role verification.</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">81</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CTXC_TC_4</t>
+          <t>TST_CTXC_TC_4</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the context class appears/behaves correctly in the student login</t>
+          <t>Verify the context class appears/behaves correctly in the student login</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">#32 — Verify Context class creation and view in teacher/admin/student login</t>
+          <t>#32 — Verify Context class creation and view in teacher/admin/student login</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">A context class exists; a student account enrolled in it.</t>
+          <t>A context class exists; a student account enrolled in it.</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Log in as the student. 2. Locate/open the context class.</t>
+          <t>1. Log in as the student. 2. Locate/open the context class.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Student account [ASSUMED]</t>
+          <t>Student account [ASSUMED]</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">The context class is visible and behaves correctly for the student role. [ASSUMED] needs a student test account.</t>
+          <t>The context class is visible and behaves correctly for the student role. [ASSUMED] needs a student test account.</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cross-role verification.</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Cross-role verification.</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
@@ -1416,9 +1416,19 @@
           <t>Row expands showing Course materials, Class labels, Students (count+Pending), Teachers (count+Pending); toggle becomes Hide class details.</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>PASS. Expanding a class row revealed the details panel showing Course materials (or the 'You haven't chosen learning materials' empty state when the class has none), the Class labels heading, and the Students and Teachers counts; the toggle changed to 'Hide class details'.</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Automated - adminClassesTab.test.js (npm run P1AdminClassesTab_Thor, thor). Last run 2026-08-17: 12/12 passing.</t>
         </is>
       </c>
     </row>
@@ -1473,9 +1483,19 @@
           <t>Details collapse; toggle returns to Show class details.</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>PASS. Collapsing the row hid the details panel and the toggle returned to 'Show class details'. NOTE: the panel's content REMAINS in the DOM while collapsed, so only a visibility check distinguishes the two states.</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Automated - adminClassesTab.test.js (npm run P1AdminClassesTab_Thor, thor). Last run 2026-08-17: 12/12 passing.</t>
         </is>
       </c>
     </row>
@@ -1530,9 +1550,19 @@
           <t>Help panel appears (search by name/class code, deleted/restored refresh tip); toggle becomes Hide the user guide.</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>PASS. The user guide panel opened showing 'On this page you can:' with guidance on searching by class name and class code; the toggle then offered 'Hide the user guide'.</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Automated - adminClassesTab.test.js (npm run P1AdminClassesTab_Thor, thor). Last run 2026-08-17: 12/12 passing.</t>
         </is>
       </c>
     </row>
@@ -1587,9 +1617,19 @@
           <t>Help panel collapses; toggle returns to Open the user guide.</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>PASS. Collapsing the user guide removed the panel from the DOM entirely and the toggle returned to 'Open the user guide'.</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Automated - adminClassesTab.test.js (npm run P1AdminClassesTab_Thor, thor). Last run 2026-08-17: 12/12 passing.</t>
         </is>
       </c>
     </row>
@@ -1649,9 +1689,19 @@
           <t>Opens in teacher/class view.</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>PASS. Clicking an active class name opened the Class Page at /class/teacher/org_&lt;slug&gt;/class/&lt;uuid&gt;/view.</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Automated - adminClassesTab.test.js (npm run P1AdminClassesTab_Thor, thor). Last run 2026-08-17: 12/12 passing.</t>
         </is>
       </c>
     </row>
@@ -1711,9 +1761,19 @@
           <t>Nav Classes(N)=Active+Ended.</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>PASS. Active and Ended classes are shown as two separate sections, each with its own count, and the Ended section carries the note that ended and deleted classes move into it plus a Class status column. NOTE: the Ended count and Class status column only render AFTER the section is expanded - while collapsed the heading reads a bare 'Ended classes' with no count.</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Automated - adminClassesTab.test.js (npm run P1AdminClassesTab_Thor, thor). Last run 2026-08-17: 12/12 passing.</t>
         </is>
       </c>
     </row>
@@ -1768,9 +1828,19 @@
           <t>Ended section expands to reveal its table on Open and collapses on Close; label toggles Open/Close.</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>PASS. The Ended section expanded (toggle reads 'Close', class rows listed) and collapsed again (toggle reads 'Open', panel hidden). NOTE: the section is COLLAPSED by default and renders no rows at all until it is opened.</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Automated - adminClassesTab.test.js (npm run P1AdminClassesTab_Thor, thor). Last run 2026-08-17: 12/12 passing.</t>
         </is>
       </c>
     </row>
@@ -1830,9 +1900,19 @@
           <t>Ended classes remain launchable.</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>PASS. Clicking a class name in the Ended section opened the same Class Page destination as an active class, confirming ended classes remain launchable.</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Automated - adminClassesTab.test.js (npm run P1AdminClassesTab_Thor, thor). Last run 2026-08-17: 12/12 passing.</t>
         </is>
       </c>
     </row>
@@ -1892,9 +1972,19 @@
           <t>Load more is count-gated.</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>PASS. 'Load more ...' appended additional ended class rows (20 to 26) without a full page reload, and the visible rows stayed within the 'Ended classes (N)' count. Page size is 20; new rows land about 3.5s after the click.</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Automated - adminClassesTab.test.js (npm run P1AdminClassesTab_Thor, thor). Last run 2026-08-17: 12/12 passing.</t>
         </is>
       </c>
     </row>
@@ -1946,12 +2036,22 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>After the last batch, Load more is no longer shown. [ASSUMED] confirm hide vs disable.</t>
+          <t>Once the last batch is loaded, the "Load more ..." link is REMOVED from the DOM - it hides rather than becoming disabled. CONFIRMED live 2026-08-17.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>PASS. After clicking 'Load more ...' until every ended class was listed, the link was REMOVED from the DOM (it hides rather than disabling) and the visible row count equalled the 'Ended classes (N)' heading.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Automated - adminClassesTab.test.js (npm run P1AdminClassesTab_Thor, thor). Last run 2026-08-17: 12/12 passing.</t>
         </is>
       </c>
     </row>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
@@ -2170,12 +2170,22 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Repeated runs create duplicates (counts toward max).</t>
+          <t>Automated as TST_GCAT_TC_2. Name generated per run as AutoCat_create_&lt;epoch-ms&gt;, so repeated runs never collide; the housekeeping hook removes them, so duplicate names no longer accumulate against the school maximum.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>PASS. Modal opened, name accepted, and on Save the banner 'Grading category successfully created' appeared (~1.4 s) with the category listed at the same moment. Both signals are asserted - the banner alone would pass even if nothing had been created.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Automated - adminGradingCategories.test.js (npm run P1AdminGradingCategories_Thor, thor). Last run 2026-08-18: 5/5 passing, 2 consecutive clean runs.</t>
         </is>
       </c>
     </row>
@@ -2230,9 +2240,24 @@
           <t>Name accepted (maxlength 50) and category created. [ASSUMED] confirm truncation at 50.</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Automated as TST_GCAT_TC_3. The test asserts the generated name is exactly 50 characters before using it, so a helper bug cannot quietly turn this into a short-name test that never exercises the boundary.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>PASS. A 50-character name was accepted and the category appeared in the list. Confirmed live that #gradingCategoryNameInput carries maxlength=50, so longer input cannot be typed - the [ASSUMED] on this TC is resolved.</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Automated - adminGradingCategories.test.js (npm run P1AdminGradingCategories_Thor, thor). Last run 2026-08-18: 5/5 passing, 2 consecutive clean runs.</t>
         </is>
       </c>
     </row>
@@ -2287,9 +2312,24 @@
           <t>Modal: You have reached the maximum number of grading categories for your school. Please remove at least one category to add a new one; no category created. [ASSUMED] exact max count.</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>NOT AUTOMATED - BLOCKED. Deliberately absent from the test file, the TC repository and the execution file (not merely skipped), so it cannot run by accident.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>- (not executed)</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Not Run - Blocked</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>BLOCKED (2026-08-18). The precondition is 'school is already at its maximum', so the test must first FILL the school with grading categories. Three problems: (1) the maximum is unknown, so the only way to find it is to keep creating until the app refuses; (2) 3 July Test School 1 (FCN-CHZ-PDA) is SHARED - while it sits at the cap, nobody else can create a grading category and other suites would fail with a misleading error (same cross-suite interference that broke two TST_CLST_TC_7 assertions on 2026-08-17); (3) if a run crashes before cleanup, the school stays full until cleared by hand. TO UNBLOCK, any one of: (a) a DEDICATED school used only by this test (recommended - cheapest and fully safe); (b) product/dev supply the exact maximum, plus agreement to accept the shared-school impact; (c) an environment where no other suite runs. The expected modal copy is already verified live (the modal is pre-rendered in the DOM), so once a school exists this is a short TC.</t>
         </is>
       </c>
     </row>
@@ -2344,9 +2384,24 @@
           <t>Save is disabled while empty; empty-named category cannot be created.</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Automated as TST_GCAT_TC_5. Checked both ways - disabled when empty, enabled once a character is typed, disabled again when cleared. A one-way check would still pass against a permanently disabled Save, which is itself a defect worth catching.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>PASS. Save was disabled with an empty name, became enabled on input, and returned to disabled when the field was cleared. The test ends with the modal open so the end-of-test screenshot shows the disabled Save; nothing is saved.</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Automated - adminGradingCategories.test.js (npm run P1AdminGradingCategories_Thor, thor). Last run 2026-08-18: 5/5 passing, 2 consecutive clean runs.</t>
         </is>
       </c>
     </row>
@@ -2522,12 +2577,22 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Removal does not affect classes already using it.</t>
+          <t>Automated as TST_GCAT_TC_8. Creates its own AutoCat_remove_&lt;epoch-ms&gt; first, so the destructive confirmation is only ever aimed at our own data - never at a pre-existing school category. Also asserts the category IS listed before removing it.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>PASS. Confirmation modal shown with the expected copy; after 'Yes, remove' the banner 'Grading category successfully removed' appeared (~2.2 s) and the category left the list.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Automated - adminGradingCategories.test.js (npm run P1AdminGradingCategories_Thor, thor). Last run 2026-08-18: 5/5 passing, 2 consecutive clean runs.</t>
         </is>
       </c>
     </row>
@@ -2582,9 +2647,24 @@
           <t>Confirmation closes; category remains in the list (not removed).</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Automated as TST_GCAT_TC_9. Creates its own AutoCat_cancelremove_&lt;epoch-ms&gt; so the Remove confirmation is never opened against real school data. Modal closure is asserted on VISIBILITY, not presence - all four modals on this page stay in the DOM permanently, so a presence check could never fail.</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>PASS. After 'No, go back' the confirmation closed and the category was still listed.</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Automated - adminGradingCategories.test.js (npm run P1AdminGradingCategories_Thor, thor). Last run 2026-08-18: 5/5 passing, 2 consecutive clean runs.</t>
         </is>
       </c>
     </row>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
@@ -1,29 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
+    <sheet name="Test Cases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
+      <name val="Calibri"/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
       <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -44,5940 +54,5633 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N82"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7"/>
-    <col min="2" max="2" width="20"/>
-    <col min="3" max="3" width="52"/>
-    <col min="4" max="4" width="18"/>
-    <col min="5" max="5" width="10"/>
-    <col min="6" max="6" width="10"/>
-    <col min="7" max="7" width="30"/>
-    <col min="8" max="8" width="46"/>
-    <col min="9" max="9" width="30"/>
-    <col min="10" max="10" width="60"/>
-    <col min="11" max="11" width="34"/>
-    <col min="12" max="12" width="14"/>
-    <col min="13" max="13" width="10"/>
-    <col min="14" max="14" width="22"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">S.No.</t>
+          <t>S.No.</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Test Case ID</t>
+          <t>Test Case ID</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Title</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Linked Requirement</t>
+          <t>Linked Requirement</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Type</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Priority</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preconditions</t>
+          <t>Preconditions</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Test Steps</t>
+          <t>Test Steps</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Test Data</t>
+          <t>Test Data</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Expected Result</t>
+          <t>Expected Result</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remarks</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Actual Result</t>
+          <t>Actual Result</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Status</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comments / Defect ID</t>
+          <t>Comments / Defect ID</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_1</t>
+          <t>TST_CLST_TC_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the Classes tab loads with all expected components</t>
+          <t>Verify the Classes tab loads with all expected components</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">#1 — Verify class tab is loading</t>
+          <t>#1 — Verify class tab is loading</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">School opened from My school accounts.</t>
+          <t>School opened from My school accounts.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open school 3 July Test School 1. 2. Observe the Classes tab.</t>
+          <t>1. Open school 3 July Test School 1. 2. Observe the Classes tab.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classes tab loads: Active classes (N) heading, Search, Add class, Filter, User guide, select-all + disabled Delete, class table (Class name/Class key/Start date/End date/Student progress), and a separate Ended classes (N) section. Left nav: Classes/Students/Staff/Library/Reports.</t>
+          <t>Classes tab loads: Active classes (N) heading, Search, Add class, Filter, User guide, select-all + disabled Delete, class table (Class name/Class key/Start date/End date/Student progress), and a separate Ended classes (N) section. Left nav: Classes/Students/Staff/Library/Reports.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classes(N) in nav = Active + Ended.</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Classes(N) in nav = Active + Ended.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_2</t>
+          <t>TST_CLST_TC_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the Filter modal opens and shows all filter options</t>
+          <t>Verify the Filter modal opens and shows all filter options</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">#2 — Verify filter functionality is working fine</t>
+          <t>#2 — Verify filter functionality is working fine</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Classes tab.</t>
+          <t>On the Classes tab.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Filter. 2. Observe the modal.</t>
+          <t>1. Click Filter. 2. Observe the modal.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filter modal opens with Class status (Not started, Active, Ended, Expired, Deleted), Class labels (Find a label), Clear all and Apply.</t>
+          <t>Filter modal opens with Class status (Not started, Active, Ended, Expired, Deleted), Class labels (Find a label), Clear all and Apply.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filter is a modal dialog.</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Filter is a modal dialog.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_3</t>
+          <t>TST_CLST_TC_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify filtering by Class status returns only classes of that status</t>
+          <t>Verify filtering by Class status returns only classes of that status</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">#2 — Verify filter functionality is working fine</t>
+          <t>#2 — Verify filter functionality is working fine</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Classes tab; Filter modal open.</t>
+          <t>On the Classes tab; Filter modal open.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Select Class status = Active. 2. Click Apply.</t>
+          <t>1. Select Class status = Active. 2. Click Apply.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Class status: Active</t>
+          <t>Class status: Active</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal closes; list shows only Active classes; count reflects filtered result.</t>
+          <t>Modal closes; list shows only Active classes; count reflects filtered result.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Repeat for Ended/Expired/Deleted/Not started.</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Repeat for Ended/Expired/Deleted/Not started.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_4</t>
+          <t>TST_CLST_TC_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify filtering by a Class label returns only classes with that label</t>
+          <t>Verify filtering by a Class label returns only classes with that label</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">#2 — Verify filter functionality is working fine</t>
+          <t>#2 — Verify filter functionality is working fine</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">At least one class has a label applied.</t>
+          <t>At least one class has a label applied.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Filter. 2. In Class labels, type VM1 and select it. 3. Click Apply.</t>
+          <t>1. Click Filter. 2. In Class labels, type VM1 and select it. 3. Click Apply.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Label: VM1 (real label; others: A11y test, aditya)</t>
+          <t>Label: VM1 (real label; others: A11y test, aditya)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Only classes with the selected label are listed.</t>
+          <t>Only classes with the selected label are listed.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Label list confirmed live; confirm a class carries VM1 before running.</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Label list confirmed live; confirm a class carries VM1 before running.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_19</t>
+          <t>TST_CLST_TC_19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify Clear all resets the filter selections</t>
+          <t>Verify Clear all resets the filter selections</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">#2 — Verify filter functionality is working fine</t>
+          <t>#2 — Verify filter functionality is working fine</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edge</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filter modal open with selections.</t>
+          <t>Filter modal open with selections.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Select a status and/or label. 2. Click Clear all.</t>
+          <t>1. Select a status and/or label. 2. Click Clear all.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">All filter selections clear back to default within the modal.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>All filter selections clear back to default within the modal.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_22</t>
+          <t>TST_CLST_TC_22</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a filter combination with no matches shows an empty state</t>
+          <t>Verify a filter combination with no matches shows an empty state</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">#2 — Verify filter functionality is working fine</t>
+          <t>#2 — Verify filter functionality is working fine</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negative</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Classes tab.</t>
+          <t>On the Classes tab.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Filter. 2. Select a status + label combo with zero matches. 3. Click Apply.</t>
+          <t>1. Open Filter. 2. Select a status + label combo with zero matches. 3. Click Apply.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zero-match status+label combo [ASSUMED]</t>
+          <t>Zero-match status+label combo [ASSUMED]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">List shows empty/no-matching state, no error. [ASSUMED] capture exact copy.</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>List shows empty/no-matching state, no error. [ASSUMED] capture exact copy.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_5</t>
+          <t>TST_CLST_TC_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify search by class name returns the matching class</t>
+          <t>Verify search by class name returns the matching class</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">#9 — Verify search for class key and class name working fine</t>
+          <t>#9 — Verify search for class key and class name working fine</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">A class named SarthakTestClass1 exists.</t>
+          <t>A class named SarthakTestClass1 exists.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Type SarthakTestClass1 in Search. 2. Click Search.</t>
+          <t>1. Type SarthakTestClass1 in Search. 2. Click Search.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Class name: SarthakTestClass1</t>
+          <t>Class name: SarthakTestClass1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">List filtered to the class(es) matching the name.</t>
+          <t>List filtered to the class(es) matching the name.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Any existing active class name may be used.</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Any existing active class name may be used.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_6</t>
+          <t>TST_CLST_TC_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify search by class key returns the matching class</t>
+          <t>Verify search by class key returns the matching class</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">#9 — Verify search for class key and class name working fine</t>
+          <t>#9 — Verify search for class key and class name working fine</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Class key 97Cc-y7bs exists.</t>
+          <t>Class key 97Cc-y7bs exists.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Type 97Cc-y7bs in Search. 2. Click Search.</t>
+          <t>1. Type 97Cc-y7bs in Search. 2. Click Search.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Class key: 97Cc-y7bs</t>
+          <t>Class key: 97Cc-y7bs</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">List filtered to the single class with that key.</t>
+          <t>List filtered to the single class with that key.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Search accepts name and key.</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Search accepts name and key.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_18</t>
+          <t>TST_CLST_TC_18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify class search is case-insensitive and matches partial names</t>
+          <t>Verify class search is case-insensitive and matches partial names</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">#9 — Verify search for class key and class name working fine</t>
+          <t>#9 — Verify search for class key and class name working fine</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edge</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Class SarthakTestClass1 exists.</t>
+          <t>Class SarthakTestClass1 exists.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Search sarthak (lower, partial). 2. Click Search.</t>
+          <t>1. Search sarthak (lower, partial). 2. Click Search.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Search term: sarthak</t>
+          <t>Search term: sarthak</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">SarthakTestClass1 is returned. [ASSUMED] confirm partial/case behaviour.</t>
+          <t>SarthakTestClass1 is returned. [ASSUMED] confirm partial/case behaviour.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Split if exact-match only.</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Split if exact-match only.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_21</t>
+          <t>TST_CLST_TC_21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify searching for a non-existent class shows a no-results state</t>
+          <t>Verify searching for a non-existent class shows a no-results state</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">#9 — Verify search for class key and class name working fine</t>
+          <t>#9 — Verify search for class key and class name working fine</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negative</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Classes tab.</t>
+          <t>On the Classes tab.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Search zzz-no-such-class-9999. 2. Click Search.</t>
+          <t>1. Search zzz-no-such-class-9999. 2. Click Search.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Search term: zzz-no-such-class-9999</t>
+          <t>Search term: zzz-no-such-class-9999</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">No classes listed; empty/no-results state shown (no error). [ASSUMED] capture exact copy.</t>
+          <t>No classes listed; empty/no-results state shown (no error). [ASSUMED] capture exact copy.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Record no-results text for automation.</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Record no-results text for automation.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_7</t>
+          <t>TST_CLST_TC_7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify sorting by Class name toggles ascending/descending</t>
+          <t>Verify sorting by Class name toggles ascending/descending</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">#27 — Verify Sort by class name/start date/end date</t>
+          <t>#27 — Verify Sort by class name/start date/end date</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classes tab with &gt;=2 active classes.</t>
+          <t>Classes tab with &gt;=2 active classes.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Class name header. 2. Observe. 3. Click again.</t>
+          <t>1. Click Class name header. 2. Observe. 3. Click again.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">First click sorts A-&gt;Z; second reverses to Z-&gt;A; indicator updates.</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>First click sorts A-&gt;Z; second reverses to Z-&gt;A; indicator updates.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_8</t>
+          <t>TST_CLST_TC_8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify sorting by Start date and End date</t>
+          <t>Verify sorting by Start date and End date</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">#27 — Verify Sort by class name/start date/end date</t>
+          <t>#27 — Verify Sort by class name/start date/end date</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classes tab with &gt;=2 active classes.</t>
+          <t>Classes tab with &gt;=2 active classes.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Start date header. 2. Click End date header. Toggle each again.</t>
+          <t>1. Click Start date header. 2. Click End date header. Toggle each again.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classes reorder chronologically by the chosen date column; each header toggles asc/desc.</t>
+          <t>Classes reorder chronologically by the chosen date column; each header toggles asc/desc.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sort headers exist in Active and Ended tables.</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Sort headers exist in Active and Ended tables.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_9</t>
+          <t>TST_CLST_TC_9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify expanding a class row shows the class details</t>
+          <t>Verify expanding a class row shows the class details</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">#18 — Verify expanding a class row</t>
+          <t>#18 — Verify expanding a class row</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classes tab with &gt;=1 active class.</t>
+          <t>Classes tab with &gt;=1 active class.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Show class details on a row.</t>
+          <t>1. Click Show class details on a row.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Row expands showing Course materials, Class labels, Students (count+Pending), Teachers (count+Pending); toggle becomes Hide class details.</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Row expands showing Course materials, Class labels, Students (count+Pending), Teachers (count+Pending); toggle becomes Hide class details.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_10</t>
+          <t>TST_CLST_TC_10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify collapsing an expanded class row hides the details</t>
+          <t>Verify collapsing an expanded class row hides the details</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">#18 — Verify expanding a class row</t>
+          <t>#18 — Verify expanding a class row</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">A class row is expanded.</t>
+          <t>A class row is expanded.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Hide class details.</t>
+          <t>1. Click Hide class details.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Details collapse; toggle returns to Show class details.</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Details collapse; toggle returns to Show class details.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_11</t>
+          <t>TST_CLST_TC_11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify expanding the user guide shows the help panel</t>
+          <t>Verify expanding the user guide shows the help panel</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">#17/#33 — Verify expanding user guide in classes tab (expand/collapse)</t>
+          <t>#17/#33 — Verify expanding user guide in classes tab (expand/collapse)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">User guide collapsed.</t>
+          <t>User guide collapsed.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click User guide (Open the user guide).</t>
+          <t>1. Click User guide (Open the user guide).</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Help panel appears (search by name/class code, deleted/restored refresh tip); toggle becomes Hide the user guide.</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Help panel appears (search by name/class code, deleted/restored refresh tip); toggle becomes Hide the user guide.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_12</t>
+          <t>TST_CLST_TC_12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify collapsing the user guide hides the help panel</t>
+          <t>Verify collapsing the user guide hides the help panel</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">#17/#33 — Verify expanding user guide in classes tab (expand/collapse)</t>
+          <t>#17/#33 — Verify expanding user guide in classes tab (expand/collapse)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">User guide expanded.</t>
+          <t>User guide expanded.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Hide the user guide.</t>
+          <t>1. Click Hide the user guide.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Help panel collapses; toggle returns to Open the user guide.</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Help panel collapses; toggle returns to Open the user guide.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_13</t>
+          <t>TST_CLST_TC_13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify launching an Active class opens the Class Page</t>
+          <t>Verify launching an Active class opens the Class Page</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">#19 — Launch a class from classes tab</t>
+          <t>#19 — Launch a class from classes tab</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classes tab with &gt;=1 active class.</t>
+          <t>Classes tab with &gt;=1 active class.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click a class name link in the Active list.</t>
+          <t>1. Click a class name link in the Active list.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Class: SarthakTestClass1</t>
+          <t>Class: SarthakTestClass1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Class Page opens (/class/teacher/org_&lt;slug&gt;/class/&lt;uuid&gt;/view, title Class Page).</t>
+          <t>Class Page opens (/class/teacher/org_&lt;slug&gt;/class/&lt;uuid&gt;/view, title Class Page).</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Opens in teacher/class view.</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Opens in teacher/class view.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_14</t>
+          <t>TST_CLST_TC_14</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify Active and Ended classes appear in separate sections with counts</t>
+          <t>Verify Active and Ended classes appear in separate sections with counts</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">#28 — Ended &amp; Active sections separate; Expand/Collapse Ended</t>
+          <t>#28 — Ended &amp; Active sections separate; Expand/Collapse Ended</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">School has active and ended classes.</t>
+          <t>School has active and ended classes.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Observe Active classes (N). 2. Scroll to Ended classes (M).</t>
+          <t>1. Observe Active classes (N). 2. Scroll to Ended classes (M).</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two distinct sections each with its own count; Ended notes auto-move of ended/deleted classes and has a Class status column.</t>
+          <t>Two distinct sections each with its own count; Ended notes auto-move of ended/deleted classes and has a Class status column.</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nav Classes(N)=Active+Ended.</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Nav Classes(N)=Active+Ended.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_15</t>
+          <t>TST_CLST_TC_15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify expanding and collapsing the Ended classes section</t>
+          <t>Verify expanding and collapsing the Ended classes section</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">#28 — Ended &amp; Active sections separate; Expand/Collapse Ended</t>
+          <t>#28 — Ended &amp; Active sections separate; Expand/Collapse Ended</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ended section present.</t>
+          <t>Ended section present.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Ended classes header (Open). 2. Click again (Close).</t>
+          <t>1. Click Ended classes header (Open). 2. Click again (Close).</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ended section expands to reveal its table on Open and collapses on Close; label toggles Open/Close.</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Ended section expands to reveal its table on Open and collapses on Close; label toggles Open/Close.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_16</t>
+          <t>TST_CLST_TC_16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify launching a class from the Ended section opens the Class Page</t>
+          <t>Verify launching a class from the Ended section opens the Class Page</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">#29 — Verify class launch from ended classes section</t>
+          <t>#29 — Verify class launch from ended classes section</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ended section expanded with &gt;=1 ended class.</t>
+          <t>Ended section expanded with &gt;=1 ended class.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click a class name in the Ended list.</t>
+          <t>1. Click a class name in the Ended list.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ended class: CQA Vimal (key y4G4-3iXC)</t>
+          <t>Ended class: CQA Vimal (key y4G4-3iXC)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Class Page opens for the ended class (same /view destination).</t>
+          <t>Class Page opens for the ended class (same /view destination).</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ended classes remain launchable.</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Ended classes remain launchable.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_17</t>
+          <t>TST_CLST_TC_17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify Load more loads additional classes in the Ended section</t>
+          <t>Verify Load more loads additional classes in the Ended section</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">#20 — Verify load more classes in classes tab</t>
+          <t>#20 — Verify load more classes in classes tab</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ended section has more classes than the page size.</t>
+          <t>Ended section has more classes than the page size.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Expand Ended. 2. Scroll to bottom. 3. Click Load more.</t>
+          <t>1. Expand Ended. 2. Scroll to bottom. 3. Click Load more.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Additional rows append without full reload; visible row count increases.</t>
+          <t>Additional rows append without full reload; visible row count increases.</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Load more is count-gated.</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Load more is count-gated.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLST_TC_20</t>
+          <t>TST_CLST_TC_20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify Load more no longer appears once all classes are loaded</t>
+          <t>Verify Load more no longer appears once all classes are loaded</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">#20 — Verify load more classes in classes tab</t>
+          <t>#20 — Verify load more classes in classes tab</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edge</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Load more link is visible.</t>
+          <t>A Load more link is visible.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Load more repeatedly until all classes show.</t>
+          <t>1. Click Load more repeatedly until all classes show.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">After the last batch, Load more is no longer shown. [ASSUMED] confirm hide vs disable.</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>After the last batch, Load more is no longer shown. [ASSUMED] confirm hide vs disable.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GCAT_TC_1</t>
+          <t>TST_GCAT_TC_1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the Manage grading categories page loads with all components</t>
+          <t>Verify the Manage grading categories page loads with all components</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">#4 — Verify manage grading category page</t>
+          <t>#4 — Verify manage grading category page</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Logged in as school admin, inside school FCN-CHZ-PDA.</t>
+          <t>Logged in as school admin, inside school FCN-CHZ-PDA.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click School settings. 2. Click Manage grading categories.</t>
+          <t>1. Click School settings. 2. Click Manage grading categories.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manage grading categories page opens (/manage-grading-categories) with heading, description, Create a grading category button, and a categories list where each row has Open grade options (See details, Remove).</t>
+          <t>Manage grading categories page opens (/manage-grading-categories) with heading, description, Create a grading category button, and a categories list where each row has Open grade options (See details, Remove).</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reached via the School settings dropdown.</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Reached via the School settings dropdown.</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GCAT_TC_2</t>
+          <t>TST_GCAT_TC_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a grading category is created with a valid name</t>
+          <t>Verify a grading category is created with a valid name</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">#5 — Verify create grading category</t>
+          <t>#5 — Verify create grading category</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Manage grading categories page.</t>
+          <t>On the Manage grading categories page.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Create a grading category. 2. Enter AutoTest Category. 3. Click Save.</t>
+          <t>1. Click Create a grading category. 2. Enter AutoTest Category. 3. Click Save.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name: AutoTest Category</t>
+          <t>Name: AutoTest Category</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal closes; banner Grading category successfully created; category appears in the list.</t>
+          <t>Modal closes; banner Grading category successfully created; category appears in the list.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Repeated runs create duplicates (counts toward max).</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Repeated runs create duplicates (counts toward max).</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GCAT_TC_3</t>
+          <t>TST_GCAT_TC_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a grading category name at the 50-character maximum is accepted</t>
+          <t>Verify a grading category name at the 50-character maximum is accepted</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">#5 — Verify create grading category</t>
+          <t>#5 — Verify create grading category</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edge</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Create a grading category modal.</t>
+          <t>On the Create a grading category modal.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Enter a 50-character name. 2. Click Save.</t>
+          <t>1. Enter a 50-character name. 2. Click Save.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">50-char name</t>
+          <t>50-char name</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name accepted (maxlength 50) and category created. [ASSUMED] confirm truncation at 50.</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Name accepted (maxlength 50) and category created. [ASSUMED] confirm truncation at 50.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GCAT_TC_4</t>
+          <t>TST_GCAT_TC_4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the maximum-grading-categories limit is enforced</t>
+          <t>Verify the maximum-grading-categories limit is enforced</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">#5 — Verify create grading category</t>
+          <t>#5 — Verify create grading category</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edge</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">School already at the maximum number of grading categories.</t>
+          <t>School already at the maximum number of grading categories.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Attempt to create another grading category.</t>
+          <t>1. Attempt to create another grading category.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal: You have reached the maximum number of grading categories for your school. Please remove at least one category to add a new one; no category created. [ASSUMED] exact max count.</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Modal: You have reached the maximum number of grading categories for your school. Please remove at least one category to add a new one; no category created. [ASSUMED] exact max count.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GCAT_TC_5</t>
+          <t>TST_GCAT_TC_5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a grading category cannot be created with an empty name</t>
+          <t>Verify a grading category cannot be created with an empty name</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">#5 — Verify create grading category</t>
+          <t>#5 — Verify create grading category</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negative</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Create a grading category modal.</t>
+          <t>On the Create a grading category modal.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Leave name empty. 2. Observe Save.</t>
+          <t>1. Leave name empty. 2. Observe Save.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name: (empty)</t>
+          <t>Name: (empty)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Save is disabled while empty; empty-named category cannot be created.</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Save is disabled while empty; empty-named category cannot be created.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GCAT_TC_6</t>
+          <t>TST_GCAT_TC_6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the grading category See details page opens</t>
+          <t>Verify the grading category See details page opens</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">#6 — Verify see details page of a grading category</t>
+          <t>#6 — Verify see details page of a grading category</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Manage grading categories page with &gt;=1 category.</t>
+          <t>On the Manage grading categories page with &gt;=1 category.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open grade options on a category. 2. Click See details.</t>
+          <t>1. Open grade options on a category. 2. Click See details.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Category: AutoTest Category</t>
+          <t>Category: AutoTest Category</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Details page opens (/manage-grading-categories/&lt;id&gt;/classes, title=category name) showing Active classes (N); empty state The category has not been added to any active classes.</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Details page opens (/manage-grading-categories/&lt;id&gt;/classes, title=category name) showing Active classes (N); empty state The category has not been added to any active classes.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GCAT_TC_7</t>
+          <t>TST_GCAT_TC_7</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the class grade settings page launches from a category's details page</t>
+          <t>Verify the class grade settings page launches from a category's details page</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">#7 — Launch class grade setting page from see details page of grading category</t>
+          <t>#7 — Launch class grade setting page from see details page of grading category</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">The grading category is applied to &gt;=1 active class.</t>
+          <t>The grading category is applied to &gt;=1 active class.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open the category's See details page. 2. Click a listed class under Active classes.</t>
+          <t>1. Open the category's See details page. 2. Click a listed class under Active classes.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">A category applied to a class [ASSUMED]</t>
+          <t>A category applied to a class [ASSUMED]</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">The class grade settings page opens for the selected class. [ASSUMED] exact destination pending a category applied to a class.</t>
+          <t>The class grade settings page opens for the selected class. [ASSUMED] exact destination pending a category applied to a class.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Requires applying a category to a class first.</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Requires applying a category to a class first.</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GCAT_TC_8</t>
+          <t>TST_GCAT_TC_8</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a grading category is removed after confirmation</t>
+          <t>Verify a grading category is removed after confirmation</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">#8 — Verify delete grading category</t>
+          <t>#8 — Verify delete grading category</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Manage grading categories page with &gt;=1 removable category.</t>
+          <t>On the Manage grading categories page with &gt;=1 removable category.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open grade options. 2. Click Remove. 3. Click Yes, remove.</t>
+          <t>1. Open grade options. 2. Click Remove. 3. Click Yes, remove.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Category: AutoTest Category</t>
+          <t>Category: AutoTest Category</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confirmation modal (Remove grading category - Are you sure? Removing the category will not affect classes currently using it, but you will not be able to add it to any new classes); after Yes, remove -&gt; banner Grading category successfully removed; category gone.</t>
+          <t>Confirmation modal (Remove grading category - Are you sure? Removing the category will not affect classes currently using it, but you will not be able to add it to any new classes); after Yes, remove -&gt; banner Grading category successfully removed; category gone.</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removal does not affect classes already using it.</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Removal does not affect classes already using it.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GCAT_TC_9</t>
+          <t>TST_GCAT_TC_9</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify removing a grading category can be cancelled</t>
+          <t>Verify removing a grading category can be cancelled</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">#8 — Verify delete grading category</t>
+          <t>#8 — Verify delete grading category</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edge</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Manage grading categories page with &gt;=1 category.</t>
+          <t>On the Manage grading categories page with &gt;=1 category.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open grade options -&gt; Remove. 2. Click No, go back.</t>
+          <t>1. Open grade options -&gt; Remove. 2. Click No, go back.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confirmation closes; category remains in the list (not removed).</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Confirmation closes; category remains in the list (not removed).</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_1</t>
+          <t>TST_BCCF_TC_1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the Create new classes (bulk) form loads with all components</t>
+          <t>Verify the Create new classes (bulk) form loads with all components</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Classes tab.</t>
+          <t>On the Classes tab.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Add class.</t>
+          <t>1. Click Add class.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Create new classes form opens (/class/create) with subtitle in &lt;school&gt;, Upload file, Get CSV template, How to use this form, bulk-action toolbar (Start date, End date, Add teacher, Add labels, Add Material, Copy an Existing Class, Duplicate, Show student progress, Remove), and a class row (Class name, Start date, End date, Add teachers, Add materials, Add label). Create N class is disabled.</t>
+          <t>Create new classes form opens (/class/create) with subtitle in &lt;school&gt;, Upload file, Get CSV template, How to use this form, bulk-action toolbar (Start date, End date, Add teacher, Add labels, Add Material, Copy an Existing Class, Duplicate, Show student progress, Remove), and a class row (Class name, Start date, End date, Add teachers, Add materials, Add label). Create N class is disabled.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Form auto-saves a draft.</t>
+          <t>Form auto-saves a draft.</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Form opened at /class/create with all components present: Upload file, Get CSV template, How to use this form, all 9 bulk-toolbar actions, and row 1 (name, dates, teachers, materials, label). Create button disabled on an empty row.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Automated: TST_CCLS_TC_14 (bulk suite, 11/11).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_2</t>
+          <t>TST_BCCF_TC_2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a single class is created with a name and start/end dates</t>
+          <t>Verify a single class is created with a name and start/end dates</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Create new classes form.</t>
+          <t>On the Create new classes form.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Enter class name. 2. Set Start date (today). 3. Set End date. 4. Click Create 1 class.</t>
+          <t>1. Enter class name. 2. Set Start date (today). 3. Set End date. 4. Click Create 1 class.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name AutoClass_Bulk, Start today, End next month</t>
+          <t>Name AutoClass_Bulk, Start today, End next month</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Success dialog Success! We are now creating 1 class for you appears; creation is asynchronous (email report; up to 12 hours).</t>
+          <t>Success dialog Success! We are now creating 1 class for you appears; creation is asynchronous (email report; up to 12 hours).</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Covered by automation TST_CCLS_TC_1..4.</t>
+          <t>Covered by automation TST_CCLS_TC_1..4.</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Class created with name + start/end dates; success dialog shown: "Success! We are now creating 1 class for you".</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Automated: TST_CCLS_TC_1..4 (workflow suite). Creation is asynchronous.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_3</t>
+          <t>TST_BCCF_TC_3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a teacher can be added to a class row</t>
+          <t>Verify a teacher can be added to a class row</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">A class row with a name entered.</t>
+          <t>A class row with a name entered.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Add teachers. 2. In Edit teachers modal, enter Email (and optional First/Last name). 3. Click Apply changes.</t>
+          <t>1. Click Add teachers. 2. In Edit teachers modal, enter Email (and optional First/Last name). 3. Click Apply changes.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teacher email: &lt;TEACHER_EMAIL&gt;</t>
+          <t>Teacher email: &lt;TEACHER_EMAIL&gt;</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teacher added to the class row. Modal notes changes only apply to this class.</t>
+          <t>Teacher added to the class row. Modal notes changes only apply to this class.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Email required; names optional.</t>
+          <t>Email required; names optional.</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Teacher added via the "Edit teachers" modal (Email only); the teacher rendered on the class row.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Automated: TST_CCLS_TC_15 (bulk suite).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_4</t>
+          <t>TST_BCCF_TC_4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a material can be added to a class row</t>
+          <t>Verify a material can be added to a class row</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">A class row with a name entered.</t>
+          <t>A class row with a name entered.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Add materials. 2. Search and select a material. 3. Click Add materials.</t>
+          <t>1. Click Add materials. 2. Search and select a material. 3. Click Add materials.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Material: dev_test_ebook_bundle_104_bundle</t>
+          <t>Material: dev_test_ebook_bundle_104_bundle</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Material attaches to the class row.</t>
+          <t>Material attaches to the class row.</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Covered by automation TST_CCLS_TC_5..7.</t>
+          <t>Covered by automation TST_CCLS_TC_5..7.</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Material searched, selected and attached to the class row.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Feature verified working (workflow suite 13/13 earlier on 2026-08-18). NOTE: the automation (TST_CCLS_TC_5..7) is currently FLAKY - its selector uses a positional index (dBulkClass-add-learning-material-modal-1-0) that shifts with the form's row count when an auto-saved draft is restored. Pre-existing automation fragility, not a product defect. Fix pending: reset the form before the suite runs.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_5</t>
+          <t>TST_BCCF_TC_5</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a label can be added to a class row</t>
+          <t>Verify a label can be added to a class row</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">A class row with a name entered.</t>
+          <t>A class row with a name entered.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Add class label. 2. Select an existing label (or + Create new label).</t>
+          <t>1. Click Add class label. 2. Select an existing label (or + Create new label).</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Label: VM1</t>
+          <t>Label: VM1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chosen label applied to the row; dropdown also offers + Create new label and Edit labels.</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Chosen label applied to the row; dropdown also offers + Create new label and Edit labels.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Label "VM1" selected from the Add class label dropdown and applied to the row (row button then read "+ VM1").</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Automated: TST_CCLS_TC_16 (bulk suite). Note: the label dropdown is rendered once PER ROW (#class-label-list-modal-&lt;rowIndex&gt;), so selectors must be row-scoped.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_6</t>
+          <t>TST_BCCF_TC_6</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify multiple classes are created at once (bulk)</t>
+          <t>Verify multiple classes are created at once (bulk)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Create new classes form.</t>
+          <t>On the Create new classes form.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Fill name + dates on row 1. 2. Fill row 2. 3. Click Create 2 classes.</t>
+          <t>1. Fill name + dates on row 1. 2. Fill row 2. 3. Click Create 2 classes.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 valid class rows</t>
+          <t>2 valid class rows</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Create button reflects the count (Create 2 classes); success dialog shown for N classes. Empty rows auto-append while filling.</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Create button reflects the count (Create 2 classes); success dialog shown for N classes. Empty rows auto-append while filling.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Filling a second row increased the Create button from "Create 1 class" to "Create 2 classes"; new empty rows auto-appended.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Automated: TST_CCLS_TC_13 (bulk suite). Asserts the count delta; does not click Create, so no class is created.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_7</t>
+          <t>TST_BCCF_TC_7</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify Duplicate copies a selected class row</t>
+          <t>Verify Duplicate copies a selected class row</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">At least one class row is filled.</t>
+          <t>At least one class row is filled.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Select a row. 2. Click Duplicate in the toolbar. 3. Confirm if prompted.</t>
+          <t>1. Select a row. 2. Click Duplicate in the toolbar. 3. Confirm if prompted.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">A duplicate row is added with the same details. [ASSUMED] confirm exact behaviour/confirmation.</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>A duplicate row is added with the same details. [ASSUMED] confirm exact behaviour/confirmation.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Duplicate appended a copy AFTER the last filled row carrying the same name, dates, teacher and material. Label copied only after confirming the "Apply the labels to new classes too?" dialog.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Automated: TST_CCLS_TC_18 (bulk suite). [ASSUMED] resolved.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">39</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_8</t>
+          <t>TST_BCCF_TC_8</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify Copy an Existing Class copies settings to selected rows</t>
+          <t>Verify Copy an Existing Class copies settings to selected rows</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">At least one class row selected.</t>
+          <t>At least one class row selected.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Select row(s). 2. Click Copy an Existing Class. 3. Choose a source class and what to copy. 4. Continue.</t>
+          <t>1. Select row(s). 2. Click Copy an Existing Class. 3. Choose a source class and what to copy. 4. Continue.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Source class: &lt;EXISTING_CLASS&gt; [ASSUMED]</t>
+          <t>Source class: &lt;EXISTING_CLASS&gt; [ASSUMED]</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal lets you choose an existing class and what to copy (materials/teachers/settings) to selected rows. [ASSUMED] confirm options/flow.</t>
+          <t>Modal lets you choose an existing class and what to copy (materials/teachers/settings) to selected rows. [ASSUMED] confirm options/flow.</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toolbar aria-label: Choose what to copy from an existing class to the selected classes.</t>
+          <t>Toolbar aria-label: Choose what to copy from an existing class to the selected classes.</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>2-step wizard: searched and selected a source class, then chose Teachers + Course materials; both were applied to the selected row and the "Copied from a class" cell recorded the source. Row's own name/dates were not overwritten.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Automated: TST_CCLS_TC_21 (bulk suite). [ASSUMED] resolved. Options are disabled when the source class has none of that kind (e.g. "Assignments [0]").</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">40</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_9</t>
+          <t>TST_BCCF_TC_9</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify bulk-setting start/end date for multiple selected rows</t>
+          <t>Verify bulk-setting start/end date for multiple selected rows</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two or more class rows exist.</t>
+          <t>Two or more class rows exist.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Select multiple rows. 2. Click Start date in the toolbar and pick a date. 3. Click End date and pick a date.</t>
+          <t>1. Select multiple rows. 2. Click Start date in the toolbar and pick a date. 3. Click End date and pick a date.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chosen start/end dates apply to all selected rows at once.</t>
+          <t>Chosen start/end dates apply to all selected rows at once.</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Same pattern for bulk Add teacher/labels/material.</t>
+          <t>Same pattern for bulk Add teacher/labels/material.</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Toolbar Start date and End date applied the chosen dates to the selected row.</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Automated: TST_CCLS_TC_17 (bulk suite). Note: applying a bulk date CLEARS the row selection, so rows must be re-selected before the next bulk action.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_10</t>
+          <t>TST_BCCF_TC_10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify Get CSV template downloads the upload template</t>
+          <t>Verify Get CSV template downloads the upload template</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Create new classes form.</t>
+          <t>On the Create new classes form.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Get CSV template.</t>
+          <t>1. Click Get CSV template.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">A CSV template downloads with the correct headers for bulk class creation. [ASSUMED] capture exact headers.</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>A CSV template downloads with the correct headers for bulk class creation. [ASSUMED] capture exact headers.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Class_creation_form_template.csv downloaded with 14 columns exactly as listed in Expected Result.</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Automated: TST_CCLS_TC_22 (bulk suite). Required adding downloadFile() to baseActionLibrary.js (protected file, confirmed).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_11</t>
+          <t>TST_BCCF_TC_11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify uploading a CSV bulk-creates classes</t>
+          <t>Verify uploading a CSV bulk-creates classes</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">A populated CSV in the template format is available.</t>
+          <t>A populated CSV in the template format is available.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Upload file. 2. Select the CSV. 3. Wait for upload to complete.</t>
+          <t>1. Click Upload file. 2. Select the CSV. 3. Wait for upload to complete.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;BULK_CLASSES_CSV&gt; [ASSUMED]</t>
+          <t>&lt;BULK_CLASSES_CSV&gt; [ASSUMED]</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classes from the CSV are added/created; an upload progress indicator shows during processing. [ASSUMED] confirm flow/validation.</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Classes from the CSV are added/created; an upload progress indicator shows during processing. [ASSUMED] confirm flow/validation.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Uploading a 2-row CSV populated both class rows with names and dates parsed from DD/MM/YYYY; Create button rose to "Create 2 classes". No class was created by the upload itself.</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Automated: TST_CCLS_TC_19 (bulk suite). [ASSUMED] resolved - upload POPULATES the form, it does not create.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_12</t>
+          <t>TST_BCCF_TC_12</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify Back to dashboard and Create more classes from the success dialog</t>
+          <t>Verify Back to dashboard and Create more classes from the success dialog</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">A class was just created (success dialog shown).</t>
+          <t>A class was just created (success dialog shown).</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Back to dashboard. 2. (Separately) create again and click Create more classes.</t>
+          <t>1. Click Back to dashboard. 2. (Separately) create again and click Create more classes.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back to dashboard returns to the school Classes page; Create more classes returns to a fresh Create form. [ASSUMED] confirm form reset.</t>
+          <t>Back to dashboard returns to the school Classes page; Create more classes returns to a fresh Create form. [ASSUMED] confirm form reset.</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back to dashboard covered by automation TST_CCLS_TC_8.</t>
+          <t>Back to dashboard covered by automation TST_CCLS_TC_8.</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>"Back to dashboard" returned to the school Classes page. "Create more classes" returned a COMPLETELY EMPTY create form (name and both dates blank).</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Automated: TST_CCLS_TC_8 (Back to dashboard) + TST_CCLS_TC_20 (Create more classes), workflow suite. [ASSUMED] resolved - it does reset the form; the only path that does not restore the draft.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_13</t>
+          <t>TST_BCCF_TC_13</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a class name at the 50-character maximum is accepted</t>
+          <t>Verify a class name at the 50-character maximum is accepted</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edge</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">On a class row.</t>
+          <t>On a class row.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Enter a 50-character class name.</t>
+          <t>1. Enter a 50-character class name.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">50-char name</t>
+          <t>50-char name</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name accepted (maxlength 50); no more than 50 characters can be entered.</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Name accepted (maxlength 50); no more than 50 characters can be entered.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Class-name input enforces maxlength=50.</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Automated: TST_CCLS_TC_11 (validation suite, 6/6).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_14</t>
+          <t>TST_BCCF_TC_14</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the end date cannot be set before the start date</t>
+          <t>Verify the end date cannot be set before the start date</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edge</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">A start date is set on a row.</t>
+          <t>A start date is set on a row.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open the End date picker.</t>
+          <t>1. Open the End date picker.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start = today</t>
+          <t>Start = today</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dates on/before the start date are disabled in the end-date picker; end &lt; start cannot be chosen.</t>
+          <t>Dates on/before the start date are disabled in the end-date picker; end &lt; start cannot be chosen.</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Observed: days &lt;= start are owl-dt-calendar-cell-disabled.</t>
+          <t>Observed: days &lt;= start are owl-dt-calendar-cell-disabled.</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>With start date = today, the End-date picker showed 22 disabled day cells (all dates on/before the start).</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Automated: TST_CCLS_TC_12 (validation suite). Count is date-dependent (18 on 14 Aug, 22 on 18 Aug) so the assertion checks &gt; 0.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">46</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_15</t>
+          <t>TST_BCCF_TC_15</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify Create is disabled until class name and both dates are provided</t>
+          <t>Verify Create is disabled until class name and both dates are provided</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negative</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Create new classes form.</t>
+          <t>On the Create new classes form.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Fill only some of {name, start, end} on a row. 2. Observe the Create button.</t>
+          <t>1. Fill only some of {name, start, end} on a row. 2. Observe the Create button.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Incomplete row</t>
+          <t>Incomplete row</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Create N class button stays disabled until the row has name AND start date AND end date.</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Create N class button stays disabled until the row has name AND start date AND end date.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>"Create N class" stayed disabled while the row was missing a required field.</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Automated: TST_CCLS_TC_9 (validation suite).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_BCCF_TC_16</t>
+          <t>TST_BCCF_TC_16</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify an empty or non-alphanumeric class name is rejected</t>
+          <t>Verify an empty or non-alphanumeric class name is rejected</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3 — Verify bulk class creation form is working fine</t>
+          <t>#3 — Verify bulk class creation form is working fine</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negative</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">On a class row.</t>
+          <t>On a class row.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Leave the class name empty, or enter only non-alphanumeric characters (e.g. ---). 2. Attempt to create.</t>
+          <t>1. Leave the class name empty, or enter only non-alphanumeric characters (e.g. ---). 2. Attempt to create.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name: (empty) / ---</t>
+          <t>Name: (empty) / ---</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Row is invalid - name requires at least one alphanumeric character (pattern .*[A-Za-z0-9]+.*) - so the class cannot be created. [ASSUMED] capture any inline error text.</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Row is invalid - name requires at least one alphanumeric character (pattern .*[A-Za-z0-9]+.*) - so the class cannot be created. [ASSUMED] capture any inline error text.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>A non-alphanumeric-only name ("---") left "Create N class" disabled.</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t>Automated: TST_CCLS_TC_10 (validation suite).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GSCL_TC_1</t>
+          <t>TST_GSCL_TC_1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the Manage grading scales page loads with all components</t>
+          <t>Verify the Manage grading scales page loads with all components</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">#10 — Verify manage grading scales page</t>
+          <t>#10 — Verify manage grading scales page</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Logged in as school admin, inside school FCN-CHZ-PDA.</t>
+          <t>Logged in as school admin, inside school FCN-CHZ-PDA.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click School settings. 2. Click Manage grading scales.</t>
+          <t>1. Click School settings. 2. Click Manage grading scales.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grading scales page opens (/grading-scales/manage) with heading Grading scales, User guide, Create grading scale button, and a list of scales. Cambridge One grading scale shows a default badge and only View details; custom scales offer View details / Set as default / Delete via Open drop down.</t>
+          <t>Grading scales page opens (/grading-scales/manage) with heading Grading scales, User guide, Create grading scale button, and a list of scales. Cambridge One grading scale shows a default badge and only View details; custom scales offer View details / Set as default / Delete via Open drop down.</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reached via School settings dropdown.</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Reached via School settings dropdown.</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">49</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GSCL_TC_2</t>
+          <t>TST_GSCL_TC_2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a grading scale is created with a title, bands and target score</t>
+          <t>Verify a grading scale is created with a title, bands and target score</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">#11 — Verify Create grading scale</t>
+          <t>#11 — Verify Create grading scale</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Grading scales page.</t>
+          <t>On the Grading scales page.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Create grading scale. 2. Enter title. 3. Enter Highest grade name + From %. 4. Enter Lowest grade name + To %. 5. Mark a band as Set as target score. 6. Click Save grading scale.</t>
+          <t>1. Click Create grading scale. 2. Enter title. 3. Enter Highest grade name + From %. 4. Enter Lowest grade name + To %. 5. Mark a band as Set as target score. 6. Click Save grading scale.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Title AutoTest Scale; Highest A 50-100%; Lowest F 0-49%; target A</t>
+          <t>Title AutoTest Scale; Highest A 50-100%; Lowest F 0-49%; target A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scale created and appears in the list showing its target score; bands cover 0-100% without overlap.</t>
+          <t>Scale created and appears in the list showing its target score; bands cover 0-100% without overlap.</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Highest To fixed 100%, Lowest From fixed 0%.</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Highest To fixed 100%, Lowest From fixed 0%.</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GSCL_TC_3</t>
+          <t>TST_GSCL_TC_3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a middle band can be added with + Add new grade</t>
+          <t>Verify a middle band can be added with + Add new grade</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">#11 — Verify Create grading scale</t>
+          <t>#11 — Verify Create grading scale</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Create grading scale form.</t>
+          <t>On the Create grading scale form.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click + Add new grade. 2. Enter the middle band name + From-To %.</t>
+          <t>1. Click + Add new grade. 2. Enter the middle band name + From-To %.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Middle band B 50-79%, adjust others to keep 0-100% coverage</t>
+          <t>Middle band B 50-79%, adjust others to keep 0-100% coverage</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">A middle band row is added between Highest and Lowest; bands must still cover 0-100% without overlap.</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>A middle band row is added between Highest and Lowest; bands must still cover 0-100% without overlap.</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GSCL_TC_4</t>
+          <t>TST_GSCL_TC_4</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the maximum-grading-scales limit is enforced</t>
+          <t>Verify the maximum-grading-scales limit is enforced</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">#11 — Verify Create grading scale</t>
+          <t>#11 — Verify Create grading scale</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edge</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">School already at the maximum number of grading scales.</t>
+          <t>School already at the maximum number of grading scales.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Attempt to create another grading scale.</t>
+          <t>1. Attempt to create another grading scale.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal: You have reached the maximum number of grading scales for this school. Please remove at least one grading scale to add a new one; no scale created. [ASSUMED] exact maximum.</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Modal: You have reached the maximum number of grading scales for this school. Please remove at least one grading scale to add a new one; no scale created. [ASSUMED] exact maximum.</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GSCL_TC_5</t>
+          <t>TST_GSCL_TC_5</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify Save is disabled until title, valid bands and target are provided</t>
+          <t>Verify Save is disabled until title, valid bands and target are provided</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">#11 — Verify Create grading scale</t>
+          <t>#11 — Verify Create grading scale</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negative</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Create grading scale form.</t>
+          <t>On the Create grading scale form.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Leave title empty, or set bands that overlap / do not add up to 100%, or omit the target. 2. Observe Save grading scale.</t>
+          <t>1. Leave title empty, or set bands that overlap / do not add up to 100%, or omit the target. 2. Observe Save grading scale.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Incomplete/invalid bands</t>
+          <t>Incomplete/invalid bands</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Save grading scale stays disabled until the scale has a title, bands covering 0-100% without overlap, and a target score. [ASSUMED] capture overlap/gap validation copy.</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Save grading scale stays disabled until the scale has a title, bands covering 0-100% without overlap, and a target score. [ASSUMED] capture overlap/gap validation copy.</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GSCL_TC_6</t>
+          <t>TST_GSCL_TC_6</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the grading scale View details page opens</t>
+          <t>Verify the grading scale View details page opens</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">#12 — Verify view details page of grading scale</t>
+          <t>#12 — Verify view details page of grading scale</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Grading scales page with &gt;=1 scale.</t>
+          <t>On the Grading scales page with &gt;=1 scale.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Open drop down on a scale. 2. Click View details.</t>
+          <t>1. Click Open drop down on a scale. 2. Click View details.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scale: AutoTest Scale</t>
+          <t>Scale: AutoTest Scale</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Details page opens (/grading-scales/&lt;id&gt;, title=scale name) with a collapsible Grading scale bands section and a Classes (N) section; empty state No classes yet. To associate the grading scale with a class, go to its Class grade settings page.</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Details page opens (/grading-scales/&lt;id&gt;, title=scale name) with a collapsible Grading scale bands section and a Classes (N) section; empty state No classes yet. To associate the grading scale with a class, go to its Class grade settings page.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GSCL_TC_7</t>
+          <t>TST_GSCL_TC_7</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the class grade settings page launches from a scale's details page</t>
+          <t>Verify the class grade settings page launches from a scale's details page</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">#13 — Launch class grade setting page from view details page of grading scale</t>
+          <t>#13 — Launch class grade setting page from view details page of grading scale</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">The grading scale is applied to &gt;=1 class.</t>
+          <t>The grading scale is applied to &gt;=1 class.</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open the scale's View details page. 2. Click a listed class under Classes.</t>
+          <t>1. Open the scale's View details page. 2. Click a listed class under Classes.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">A scale applied to a class [ASSUMED]</t>
+          <t>A scale applied to a class [ASSUMED]</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">The class grade settings page opens for the selected class. [ASSUMED] exact destination pending a scale applied to a class.</t>
+          <t>The class grade settings page opens for the selected class. [ASSUMED] exact destination pending a scale applied to a class.</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Associate a scale with a class via class grade settings first.</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Associate a scale with a class via class grade settings first.</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GSCL_TC_8</t>
+          <t>TST_GSCL_TC_8</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a grading scale can be set as the school default</t>
+          <t>Verify a grading scale can be set as the school default</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">#14 — Verify set as default for a grading scale</t>
+          <t>#14 — Verify set as default for a grading scale</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">A custom (non-default) grading scale exists.</t>
+          <t>A custom (non-default) grading scale exists.</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open the custom scale's Open drop down -&gt; Set as default. 2. Click Yes, set as default.</t>
+          <t>1. Open the custom scale's Open drop down -&gt; Set as default. 2. Click Yes, set as default.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scale: AutoTest Scale</t>
+          <t>Scale: AutoTest Scale</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confirmation Set as default for the school? All newly created classes will be associated with this grading scale. Existing classes will not be affected; after Yes the scale becomes default (badge moves to it).</t>
+          <t>Confirmation Set as default for the school? All newly created classes will be associated with this grading scale. Existing classes will not be affected; after Yes the scale becomes default (badge moves to it).</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Only non-default scales offer Set as default.</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Only non-default scales offer Set as default.</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GSCL_TC_9</t>
+          <t>TST_GSCL_TC_9</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a grading scale is deleted after confirmation</t>
+          <t>Verify a grading scale is deleted after confirmation</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">#15 — Verify deleting a grading scale</t>
+          <t>#15 — Verify deleting a grading scale</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">A deletable (non-default) grading scale exists.</t>
+          <t>A deletable (non-default) grading scale exists.</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open the scale's Open drop down -&gt; Delete. 2. Click Yes, delete.</t>
+          <t>1. Open the scale's Open drop down -&gt; Delete. 2. Click Yes, delete.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scale: AutoTest Scale</t>
+          <t>Scale: AutoTest Scale</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confirmation Are you sure? Deleting the grading scale will not affect classes associated with it, but it won't be available to apply to any new classes.; after Yes, delete the scale is removed from the list.</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Confirmation Are you sure? Deleting the grading scale will not affect classes associated with it, but it won't be available to apply to any new classes.; after Yes, delete the scale is removed from the list.</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GSCL_TC_10</t>
+          <t>TST_GSCL_TC_10</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify deleting a grading scale can be cancelled</t>
+          <t>Verify deleting a grading scale can be cancelled</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">#15 — Verify deleting a grading scale</t>
+          <t>#15 — Verify deleting a grading scale</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edge</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">A deletable grading scale exists.</t>
+          <t>A deletable grading scale exists.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open drop down -&gt; Delete. 2. Click No, go back.</t>
+          <t>1. Open drop down -&gt; Delete. 2. Click No, go back.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confirmation closes; scale remains in the list (not deleted).</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Confirmation closes; scale remains in the list (not deleted).</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GSCL_TC_11</t>
+          <t>TST_GSCL_TC_11</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the default grading scale cannot be deleted</t>
+          <t>Verify the default grading scale cannot be deleted</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">#15 — Verify deleting a grading scale</t>
+          <t>#15 — Verify deleting a grading scale</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negative</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Grading scales page (Cambridge One grading scale is default).</t>
+          <t>On the Grading scales page (Cambridge One grading scale is default).</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open the Open drop down on the default scale.</t>
+          <t>1. Open the Open drop down on the default scale.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Default scale: Cambridge One grading scale</t>
+          <t>Default scale: Cambridge One grading scale</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">The default scale's menu offers only View details - no Delete (nor Set as default) - so the default scale cannot be deleted.</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>The default scale's menu offers only View details - no Delete (nor Set as default) - so the default scale cannot be deleted.</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">59</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_GSCL_TC_12</t>
+          <t>TST_GSCL_TC_12</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify expanding the grading scale bands shows the bands</t>
+          <t>Verify expanding the grading scale bands shows the bands</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">#16 — Verify expanding grading scale bands</t>
+          <t>#16 — Verify expanding grading scale bands</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">On a grading scale's View details page.</t>
+          <t>On a grading scale's View details page.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Grading scale bands.</t>
+          <t>1. Click Grading scale bands.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scale: AutoTest Scale</t>
+          <t>Scale: AutoTest Scale</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Section expands to list bands as Grade name / Band (e.g. A -&gt; 50% - 100% with Target score: 50%, F -&gt; 0% - 49%).</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Section expands to list bands as Grade name / Band (e.g. A -&gt; 50% - 100% with Target score: 50%, F -&gt; 0% - 49%).</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CMGT_TC_1</t>
+          <t>TST_CMGT_TC_1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify an existing label can be added to a class</t>
+          <t>Verify an existing label can be added to a class</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">#21 — Add label in class</t>
+          <t>#21 — Add label in class</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">A class is open (Classes tab -&gt; launch a class -&gt; /view/classdata).</t>
+          <t>A class is open (Classes tab -&gt; launch a class -&gt; /view/classdata).</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click + Add labels. 2. Select an existing label.</t>
+          <t>1. Click + Add labels. 2. Select an existing label.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Label: VM1</t>
+          <t>Label: VM1</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">The selected label is applied to the class and shown on it.</t>
+          <t>The selected label is applied to the class and shown on it.</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Same label list as bulk-create form (TST_BCCF_TC_5).</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Same label list as bulk-create form (TST_BCCF_TC_5).</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CMGT_TC_2</t>
+          <t>TST_CMGT_TC_2</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a new label can be created and applied to a class</t>
+          <t>Verify a new label can be created and applied to a class</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">#21 — Add label in class</t>
+          <t>#21 — Add label in class</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">A class is open.</t>
+          <t>A class is open.</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click + Add labels. 2. Click + Create new label. 3. Enter a label name and save.</t>
+          <t>1. Click + Add labels. 2. Click + Create new label. 3. Enter a label name and save.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">New label: AutoTest Label</t>
+          <t>New label: AutoTest Label</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">New label is created, applied to the class, and becomes available for other classes. [ASSUMED] confirm create-label form.</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>New label is created, applied to the class, and becomes available for other classes. [ASSUMED] confirm create-label form.</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CMGT_TC_3</t>
+          <t>TST_CMGT_TC_3</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify soft-deleting a single active class</t>
+          <t>Verify soft-deleting a single active class</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">#23 — Verify delete classes (soft / hard / bulk up to 50)</t>
+          <t>#23 — Verify delete classes (soft / hard / bulk up to 50)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Classes tab with &gt;=1 active class.</t>
+          <t>On the Classes tab with &gt;=1 active class.</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Select a class row checkbox. 2. Click Delete class. 3. Click Yes, delete 1 class.</t>
+          <t>1. Select a class row checkbox. 2. Click Delete class. 3. Click Yes, delete 1 class.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">An active class</t>
+          <t>An active class</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">WARNING confirmation shown (1 selected class has not ended. There might be students, teachers and course materials... Are you sure you want to delete?). After Yes, class removed from Active and moved to deleted/Ended section (soft delete). Note: This will take a few minutes. Deleted classes may show on dashboards for a few minutes before they are removed.</t>
+          <t>WARNING confirmation shown (1 selected class has not ended. There might be students, teachers and course materials... Are you sure you want to delete?). After Yes, class removed from Active and moved to deleted/Ended section (soft delete). Note: This will take a few minutes. Deleted classes may show on dashboards for a few minutes before they are removed.</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Soft delete is restorable.</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Soft delete is restorable.</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t>63</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CMGT_TC_4</t>
+          <t>TST_CMGT_TC_4</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify bulk-deleting multiple classes</t>
+          <t>Verify bulk-deleting multiple classes</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">#23 — Verify delete classes (soft / hard / bulk up to 50)</t>
+          <t>#23 — Verify delete classes (soft / hard / bulk up to 50)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Classes tab with &gt;=2 active classes.</t>
+          <t>On the Classes tab with &gt;=2 active classes.</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Select multiple class checkboxes (or select-all). 2. Click Delete class. 3. Confirm Yes, delete N classes.</t>
+          <t>1. Select multiple class checkboxes (or select-all). 2. Click Delete class. 3. Confirm Yes, delete N classes.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multiple classes</t>
+          <t>Multiple classes</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selected classes are soft-deleted together; confirmation reflects the count (Yes, delete N classes).</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Selected classes are soft-deleted together; confirmation reflects the count (Yes, delete N classes).</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">64</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CMGT_TC_5</t>
+          <t>TST_CMGT_TC_5</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a class can be permanently (hard) deleted when all conditions are met</t>
+          <t>Verify a class can be permanently (hard) deleted when all conditions are met</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">#23 — Verify delete classes (soft / hard / bulk up to 50)</t>
+          <t>#23 — Verify delete classes (soft / hard / bulk up to 50)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">A deleted class with: no students; &lt;=1 teacher (the deleter) or none; no groups; no assignments; no grading scales; no grading categories; no locking/unlocking rules.</t>
+          <t>A deleted class with: no students; &lt;=1 teacher (the deleter) or none; no groups; no assignments; no grading scales; no grading categories; no locking/unlocking rules.</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open the deleted class (Deleted filter / Ended section). 2. Choose the permanent-delete option. 3. Confirm.</t>
+          <t>1. Open the deleted class (Deleted filter / Ended section). 2. Choose the permanent-delete option. 3. Confirm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">A deleted class meeting all 7 conditions</t>
+          <t>A deleted class meeting all 7 conditions</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">The class is permanently removed and can no longer be restored. [ASSUMED] capture the exact permanent-delete UI/location.</t>
+          <t>The class is permanently removed and can no longer be restored. [ASSUMED] capture the exact permanent-delete UI/location.</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">The 7 conditions (per AdminApp.xlsx) must all be satisfied.</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>The 7 conditions (per AdminApp.xlsx) must all be satisfied.</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">65</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CMGT_TC_6</t>
+          <t>TST_CMGT_TC_6</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify bulk delete supports up to 50 classes</t>
+          <t>Verify bulk delete supports up to 50 classes</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">#23 — Verify delete classes (soft / hard / bulk up to 50)</t>
+          <t>#23 — Verify delete classes (soft / hard / bulk up to 50)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edge</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Classes tab with many classes.</t>
+          <t>On the Classes tab with many classes.</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Select up to 50 classes. 2. Click Delete class and confirm.</t>
+          <t>1. Select up to 50 classes. 2. Click Delete class and confirm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 classes</t>
+          <t>50 classes</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Up to 50 classes can be selected and deleted in one action. [ASSUMED] confirm the 50-class maximum.</t>
+          <t>Up to 50 classes can be selected and deleted in one action. [ASSUMED] confirm the 50-class maximum.</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scenario title references 50 classes.</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Scenario title references 50 classes.</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CMGT_TC_7</t>
+          <t>TST_CMGT_TC_7</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify deleting a class can be cancelled</t>
+          <t>Verify deleting a class can be cancelled</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">#23 — Verify delete classes (soft / hard / bulk up to 50)</t>
+          <t>#23 — Verify delete classes (soft / hard / bulk up to 50)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edge</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Classes tab with &gt;=1 class selected.</t>
+          <t>On the Classes tab with &gt;=1 class selected.</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Delete class. 2. Click No, cancel.</t>
+          <t>1. Click Delete class. 2. Click No, cancel.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confirmation closes; class is not deleted.</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Confirmation closes; class is not deleted.</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CMGT_TC_8</t>
+          <t>TST_CMGT_TC_8</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a class cannot be permanently deleted when conditions are not met</t>
+          <t>Verify a class cannot be permanently deleted when conditions are not met</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">#23 — Verify delete classes (soft / hard / bulk up to 50)</t>
+          <t>#23 — Verify delete classes (soft / hard / bulk up to 50)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negative</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">A class that still has students / another teacher / groups / assignments / grading scales / grading categories / locking rules.</t>
+          <t>A class that still has students / another teacher / groups / assignments / grading scales / grading categories / locking rules.</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Attempt to permanently delete it.</t>
+          <t>1. Attempt to permanently delete it.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">A class violating &gt;=1 of the 7 conditions</t>
+          <t>A class violating &gt;=1 of the 7 conditions</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Permanent deletion is blocked/unavailable until all 7 conditions are satisfied. [ASSUMED] capture the exact blocking behaviour/message.</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Permanent deletion is blocked/unavailable until all 7 conditions are satisfied. [ASSUMED] capture the exact blocking behaviour/message.</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">68</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CMGT_TC_9</t>
+          <t>TST_CMGT_TC_9</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the active-class count increases after adding a new class</t>
+          <t>Verify the active-class count increases after adding a new class</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">#30 — Verify count of classes increase on adding a new class</t>
+          <t>#30 — Verify count of classes increase on adding a new class</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Classes tab.</t>
+          <t>On the Classes tab.</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Note the current Active classes (N). 2. Add a class (Add class -&gt; fill name + dates -&gt; Create). 3. After processing, refresh the Classes tab.</t>
+          <t>1. Note the current Active classes (N). 2. Add a class (Add class -&gt; fill name + dates -&gt; Create). 3. After processing, refresh the Classes tab.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">One new class</t>
+          <t>One new class</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Once the asynchronous creation completes, the Active classes count increases by 1 (N -&gt; N+1).</t>
+          <t>Once the asynchronous creation completes, the Active classes count increases by 1 (N -&gt; N+1).</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Creation is async; count updates after processing. Aligns with automation baseline TST_SCLS_TC_1.</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Creation is async; count updates after processing. Aligns with automation baseline TST_SCLS_TC_1.</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">69</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CGST_TC_1</t>
+          <t>TST_CGST_TC_1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the Class grade settings page launches from a class page</t>
+          <t>Verify the Class grade settings page launches from a class page</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">#22 — Launch class grade setting page from a class page</t>
+          <t>#22 — Launch class grade setting page from a class page</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">A class is open (Classes tab -&gt; launch a class).</t>
+          <t>A class is open (Classes tab -&gt; launch a class).</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. On the class page, open the Actions menu. 2. Click Class grade settings.</t>
+          <t>1. On the class page, open the Actions menu. 2. Click Class grade settings.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Class grade settings page opens (/class/.../grade-weighting) showing Grading Scale (+ Change), Score settings (teacher-override toggle), Score calculation (Best/First score), per-material Weightage %, Other grading categories (+ Add a grading category), Total grade: 100%, Save changes / Cancel.</t>
+          <t>Class grade settings page opens (/class/.../grade-weighting) showing Grading Scale (+ Change), Score settings (teacher-override toggle), Score calculation (Best/First score), per-material Weightage %, Other grading categories (+ Add a grading category), Total grade: 100%, Save changes / Cancel.</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Destination the grading category/scale details pages link to (TST_GCAT_TC_7, TST_GSCL_TC_7).</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Destination the grading category/scale details pages link to (TST_GCAT_TC_7, TST_GSCL_TC_7).</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">70</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CGST_TC_2</t>
+          <t>TST_CGST_TC_2</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the grading scale can be changed for a class</t>
+          <t>Verify the grading scale can be changed for a class</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">#22 — Launch class grade setting page from a class page</t>
+          <t>#22 — Launch class grade setting page from a class page</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Class grade settings page.</t>
+          <t>On the Class grade settings page.</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. In Grading Scale, click Change. 2. Select a grading scale. 3. Click Save changes.</t>
+          <t>1. In Grading Scale, click Change. 2. Select a grading scale. 3. Click Save changes.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">A grading scale (AutoTest Scale / Cambridge One grading scale)</t>
+          <t>A grading scale (AutoTest Scale / Cambridge One grading scale)</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Class grading scale updates to the selected scale; the class then appears under that scale's details. [ASSUMED] confirm change-scale selector.</t>
+          <t>Class grading scale updates to the selected scale; the class then appears under that scale's details. [ASSUMED] confirm change-scale selector.</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Associates a scale with a class - resolves TST_GSCL_TC_7.</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Associates a scale with a class - resolves TST_GSCL_TC_7.</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">71</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CGST_TC_3</t>
+          <t>TST_CGST_TC_3</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a grading category can be added to a class</t>
+          <t>Verify a grading category can be added to a class</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">#22 — Launch class grade setting page from a class page</t>
+          <t>#22 — Launch class grade setting page from a class page</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Class grade settings page.</t>
+          <t>On the Class grade settings page.</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Add a grading category. 2. Select a grading category. 3. Set its Weightage %. 4. Click Save changes.</t>
+          <t>1. Click Add a grading category. 2. Select a grading category. 3. Set its Weightage %. 4. Click Save changes.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">A grading category (some) + weightage</t>
+          <t>A grading category (some) + weightage</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grading category added to the class with a weightage; the class then appears under that category's details. [ASSUMED] confirm add-category selector.</t>
+          <t>Grading category added to the class with a weightage; the class then appears under that category's details. [ASSUMED] confirm add-category selector.</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Associates a category with a class - resolves TST_GCAT_TC_7.</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Associates a category with a class - resolves TST_GCAT_TC_7.</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">72</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CGST_TC_4</t>
+          <t>TST_CGST_TC_4</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the score calculation (Best / First score) can be changed</t>
+          <t>Verify the score calculation (Best / First score) can be changed</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">#22 — Launch class grade setting page from a class page</t>
+          <t>#22 — Launch class grade setting page from a class page</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Class grade settings page.</t>
+          <t>On the Class grade settings page.</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open the Score calculation dropdown. 2. Select First score (or Best score). 3. Click Save changes.</t>
+          <t>1. Open the Score calculation dropdown. 2. Select First score (or Best score). 3. Click Save changes.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Score type: First score</t>
+          <t>Score type: First score</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selected score type is saved as the score that counts toward students' progress.</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Selected score type is saved as the score that counts toward students' progress.</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">73</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CGST_TC_5</t>
+          <t>TST_CGST_TC_5</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the teacher score-override setting can be toggled</t>
+          <t>Verify the teacher score-override setting can be toggled</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">#22 — Launch class grade setting page from a class page</t>
+          <t>#22 — Launch class grade setting page from a class page</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Class grade settings page.</t>
+          <t>On the Class grade settings page.</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Toggle Allow teachers to override and add scores to auto-marked activities. 2. Click Save changes.</t>
+          <t>1. Toggle Allow teachers to override and add scores to auto-marked activities. 2. Click Save changes.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">The override setting is saved in the state it was toggled to.</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>The override setting is saved in the state it was toggled to.</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">74</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CGST_TC_6</t>
+          <t>TST_CGST_TC_6</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the total grade weightage must equal 100%</t>
+          <t>Verify the total grade weightage must equal 100%</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">#22 — Launch class grade setting page from a class page</t>
+          <t>#22 — Launch class grade setting page from a class page</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edge</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Class grade settings page with &gt;=1 material/category weightage.</t>
+          <t>On the Class grade settings page with &gt;=1 material/category weightage.</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Set weightages that do not add up to 100%. 2. Attempt to Save changes.</t>
+          <t>1. Set weightages that do not add up to 100%. 2. Attempt to Save changes.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weightages summing to != 100%</t>
+          <t>Weightages summing to != 100%</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saving is prevented / an error shown until Total grade equals 100%. [ASSUMED] confirm validation copy.</t>
+          <t>Saving is prevented / an error shown until Total grade equals 100%. [ASSUMED] confirm validation copy.</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Page shows a running Total grade: 100%.</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Page shows a running Total grade: 100%.</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">75</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLON_TC_1</t>
+          <t>TST_CLON_TC_1</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a class can be cloned from an existing class</t>
+          <t>Verify a class can be cloned from an existing class</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">#31 — Verify class clone functionality (Copy an Existing Class)</t>
+          <t>#31 — Verify class clone functionality (Copy an Existing Class)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the Create new classes form with &gt;=1 row selected; a source class exists.</t>
+          <t>On the Create new classes form with &gt;=1 row selected; a source class exists.</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Copy an Existing Class. 2. Step 1: search and select the source class -&gt; Continue. 3. Step 2: on Choose what to copy from [source], select components -&gt; Continue.</t>
+          <t>1. Click Copy an Existing Class. 2. Step 1: search and select the source class -&gt; Continue. 3. Step 2: on Choose what to copy from [source], select components -&gt; Continue.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Source class: SarthakTestClass1</t>
+          <t>Source class: SarthakTestClass1</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Step 2 lists copyable components as checkboxes - Teachers, Course materials, Assignments, Locked content rules, Class grade settings - each with a count; selected components are copied from the source into the selected new row(s).</t>
+          <t>Step 2 lists copyable components as checkboxes - Teachers, Course materials, Assignments, Locked content rules, Class grade settings - each with a count; selected components are copied from the source into the selected new row(s).</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distinct from Duplicate (TST_BCCF_TC_7).</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Distinct from Duplicate (TST_BCCF_TC_7).</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">76</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLON_TC_2</t>
+          <t>TST_CLON_TC_2</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify all components copy from a fully-populated source class</t>
+          <t>Verify all components copy from a fully-populated source class</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">#31 — Verify class clone functionality (Copy an Existing Class)</t>
+          <t>#31 — Verify class clone functionality (Copy an Existing Class)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">A source class that HAS a teacher, course materials, assignments, locked content rules (incl. an assignment-created lock rule), and class grade settings.</t>
+          <t>A source class that HAS a teacher, course materials, assignments, locked content rules (incl. an assignment-created lock rule), and class grade settings.</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Copy an Existing Class -&gt; select the populated source. 2. Select all available components. 3. Continue and create.</t>
+          <t>1. Copy an Existing Class -&gt; select the populated source. 2. Select all available components. 3. Continue and create.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">A fully-populated source class [ASSUMED]</t>
+          <t>A fully-populated source class [ASSUMED]</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">The cloned class contains the source's teacher, materials, assignments, locked content rules (incl. the assignment-created rule), and class grade settings. [ASSUMED] verify each component copies (tested sources had 0 of each).</t>
+          <t>The cloned class contains the source's teacher, materials, assignments, locked content rules (incl. the assignment-created rule), and class grade settings. [ASSUMED] verify each component copies (tested sources had 0 of each).</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Requires a seeded source class.</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Requires a seeded source class.</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">77</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CLON_TC_3</t>
+          <t>TST_CLON_TC_3</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify components with no items are not selectable when copying</t>
+          <t>Verify components with no items are not selectable when copying</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">#31 — Verify class clone functionality (Copy an Existing Class)</t>
+          <t>#31 — Verify class clone functionality (Copy an Existing Class)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edge</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">A source class that has 0 of one or more components.</t>
+          <t>A source class that has 0 of one or more components.</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Copy an Existing Class -&gt; select a source with empty components -&gt; Continue.</t>
+          <t>1. Copy an Existing Class -&gt; select a source with empty components -&gt; Continue.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Source: SarthakTestClass1 (0 teachers/materials/assignments/rules)</t>
+          <t>Source: SarthakTestClass1 (0 teachers/materials/assignments/rules)</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Components with a count of 0 are disabled/unselectable (e.g. Teachers [0] disabled; Class grade settings - Not available).</t>
+          <t>Components with a count of 0 are disabled/unselectable (e.g. Teachers [0] disabled; Class grade settings - Not available).</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Observed live.</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Observed live.</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">78</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CTXC_TC_1</t>
+          <t>TST_CTXC_TC_1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify a context class can be created</t>
+          <t>Verify a context class can be created</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">#32 — Verify Context class creation and view in teacher/admin/student login</t>
+          <t>#32 — Verify Context class creation and view in teacher/admin/student login</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Logged in as school admin. [ASSUMED] context-class creation path TBD.</t>
+          <t>Logged in as school admin. [ASSUMED] context-class creation path TBD.</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Create a context class via the (to-be-confirmed) context-class creation flow.</t>
+          <t>1. Create a context class via the (to-be-confirmed) context-class creation flow.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Context class details [ASSUMED]</t>
+          <t>Context class details [ASSUMED]</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">The context class is created successfully. [ASSUMED] confirm the creation entry point and any context-specific fields.</t>
+          <t>The context class is created successfully. [ASSUMED] confirm the creation entry point and any context-specific fields.</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entry point not found in the admin bulk-create form; needs product clarification.</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Entry point not found in the admin bulk-create form; needs product clarification.</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">79</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CTXC_TC_2</t>
+          <t>TST_CTXC_TC_2</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the context class appears in the admin login</t>
+          <t>Verify the context class appears in the admin login</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">#32 — Verify Context class creation and view in teacher/admin/student login</t>
+          <t>#32 — Verify Context class creation and view in teacher/admin/student login</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">A context class exists; logged in as school admin.</t>
+          <t>A context class exists; logged in as school admin.</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open the school's Classes tab. 2. Locate the context class.</t>
+          <t>1. Open the school's Classes tab. 2. Locate the context class.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">The created context class</t>
+          <t>The created context class</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">The context class is listed and behaves as expected in the admin view. [ASSUMED] confirm admin-specific behaviour.</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>The context class is listed and behaves as expected in the admin view. [ASSUMED] confirm admin-specific behaviour.</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">80</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CTXC_TC_3</t>
+          <t>TST_CTXC_TC_3</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the context class appears/behaves correctly in the teacher login</t>
+          <t>Verify the context class appears/behaves correctly in the teacher login</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">#32 — Verify Context class creation and view in teacher/admin/student login</t>
+          <t>#32 — Verify Context class creation and view in teacher/admin/student login</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">A context class exists; a teacher account associated with it.</t>
+          <t>A context class exists; a teacher account associated with it.</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Log in as the teacher. 2. Locate/open the context class.</t>
+          <t>1. Log in as the teacher. 2. Locate/open the context class.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teacher account [ASSUMED]</t>
+          <t>Teacher account [ASSUMED]</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">The context class is visible and behaves correctly for the teacher role. [ASSUMED] needs a teacher test account.</t>
+          <t>The context class is visible and behaves correctly for the teacher role. [ASSUMED] needs a teacher test account.</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cross-role verification.</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Cross-role verification.</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">81</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">TST_CTXC_TC_4</t>
+          <t>TST_CTXC_TC_4</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify the context class appears/behaves correctly in the student login</t>
+          <t>Verify the context class appears/behaves correctly in the student login</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">#32 — Verify Context class creation and view in teacher/admin/student login</t>
+          <t>#32 — Verify Context class creation and view in teacher/admin/student login</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">A context class exists; a student account enrolled in it.</t>
+          <t>A context class exists; a student account enrolled in it.</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Log in as the student. 2. Locate/open the context class.</t>
+          <t>1. Log in as the student. 2. Locate/open the context class.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Student account [ASSUMED]</t>
+          <t>Student account [ASSUMED]</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">The context class is visible and behaves correctly for the student role. [ASSUMED] needs a student test account.</t>
+          <t>The context class is visible and behaves correctly for the student role. [ASSUMED] needs a student test account.</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cross-role verification.</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Cross-role verification.</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
@@ -2111,9 +2111,14 @@
           <t>Reached via the School settings dropdown.</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>As expected. Page opened at /manage-grading-categories with heading 'Manage grading categories', the description about creating and removing categories, the 'Create a grading category' button, and the 'Grading categories' list (3 rows). Opening a row's 'Open grade options' menu showed 'See details' and 'Remove'. Automated as TST_GCAT_TC_1; verified 2026-08-19 on thor, school FCN-CHZ-PDA.</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2456,9 +2461,19 @@
           <t>Details page opens (/manage-grading-categories/&lt;id&gt;/classes, title=category name) showing Active classes (N); empty state The category has not been added to any active classes.</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Automation creates its own AutoCat_* category first, so 'Active classes (0)' and the empty state are deterministic - a shared category could gain a class at any time.</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>As expected. URL changed to /manage-grading-categories/[id]/classes, the page title was the category name, 'Active classes (0)' was shown, and the empty state read 'The category has not been added to any active classes'. Automated as TST_GCAT_TC_6; verified 2026-08-19 on thor, school FCN-CHZ-PDA.</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3836,9 +3851,14 @@
           <t>Reached via School settings dropdown.</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>As expected. Page opened at /grading-scales/manage with heading 'Grading scales', the User guide, the Create grading scale button, and the scale list. 'Cambridge One grading scale' carried the default badge.</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3895,12 +3915,17 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Highest To fixed 100%, Lowest From fixed 0%.</t>
+          <t>The Grading scale title input carries maxlength=20 (captured live 2026-08-19); grade-name inputs are also 20 and From/To are 3. Not previously documented - there is no boundary test case for it.</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>As expected. Save grading scale was disabled on the empty form and became enabled once title + bands + target were set; the scale was created and appeared in the list showing 'Target score 50%'. Bands A 50-100% / F 0-49% cover 0-100% without overlap.</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3955,9 +3980,19 @@
           <t>A middle band row is added between Highest and Lowest; bands must still cover 0-100% without overlap.</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Adding a middle band RE-INDEXES the Lowest grade row from 1 to 2. Any automation addressing bands by index must re-read the row count.</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>As expected. '+ Add new grade' inserted a middle band between Highest and Lowest. Note the re-indexing: before the click rows are 0=Highest, 1=Lowest; after, 0=Highest, 1=new middle band, 2=Lowest. The middle band exposes BOTH From and To. Automation creates nothing here - it cancels out.</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4012,9 +4047,14 @@
           <t>Modal: You have reached the maximum number of grading scales for this school. Please remove at least one grading scale to add a new one; no scale created. [ASSUMED] exact maximum.</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>The expected modal copy is now VERIFIED word for word - the modal is pre-rendered in the DOM, so it was captured without filling the school to its cap. Only triggering it is blocked (shared school).</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Not Run - Blocked</t>
         </is>
       </c>
     </row>
@@ -4069,9 +4109,14 @@
           <t>Save grading scale stays disabled until the scale has a title, bands covering 0-100% without overlap, and a target score. [ASSUMED] capture overlap/gap validation copy.</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>As expected. Save grading scale stayed disabled on an empty form, with bands entered but no title, and with a title but incomplete bands.</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4126,9 +4171,14 @@
           <t>Details page opens (/grading-scales/&lt;id&gt;, title=scale name) with a collapsible Grading scale bands section and a Classes (N) section; empty state No classes yet. To associate the grading scale with a class, go to its Class grade settings page.</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>As expected. URL changed to /grading-scales/[id], the page title was the scale name, 'Grading scale bands' was present and collapsed, 'Classes (0)' was shown, and the empty state read 'No classes yet / To associate the grading scale with a class, go to its Class grade settings page'.</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4250,9 +4300,14 @@
           <t>Only non-default scales offer Set as default.</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>As expected. The confirmation read 'Set as default for the school? All newly created classes will be associated with this grading scale. Existing classes will not be affected', and after 'Yes, set as default' the default badge moved to the new scale.</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4307,9 +4362,14 @@
           <t>Confirmation Are you sure? Deleting the grading scale will not affect classes associated with it, but it won't be available to apply to any new classes.; after Yes, delete the scale is removed from the list.</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>As expected. The confirmation read 'Are you sure? Deleting the grading scale will not affect classes associated with it, but it won’t be available to apply to any new classes. Delete this grading scale from your school?', and after 'Yes, delete' the scale left the list.</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4364,9 +4424,14 @@
           <t>Confirmation closes; scale remains in the list (not deleted).</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>As expected. 'No, go back' closed the confirmation and the scale remained in the list.</t>
+        </is>
+      </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4421,9 +4486,19 @@
           <t>The default scale's menu offers only View details - no Delete (nor Set as default) - so the default scale cannot be deleted.</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>The default scale's Delete / Set as default options are omitted from the DOM, not hidden - so their absence is genuinely assertable.</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>As expected. The default scale's menu offered only View details - Delete and Set as default are absent from the DOM entirely (element count 0), not merely hidden.</t>
+        </is>
+      </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4478,9 +4553,14 @@
           <t>Section expands to list bands as Grade name / Band (e.g. A -&gt; 50% - 100% with Target score: 50%, F -&gt; 0% - 49%).</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>As expected. Clicking 'Grading scale bands' expanded the section to show Grade name / Band rows: A 50% - 100% with 'Target score: 50%', and F 0% - 49%.</t>
+        </is>
+      </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Name AutoClass_Bulk, Start today, End next month</t>
+          <t>Name AutoClass_CreateOnly, Start today, End day 15 of next month</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Covered by automation TST_CCLS_TC_1..4.</t>
+          <t>Covered by automation TST_CCLS_TC_1..4. Corrected 2026-08-19: the register previously named AutoClass_Bulk, which is the bulk suite fixture. The workflow suite that actually runs this case uses AutoClass_CreateOnly (C1.adminAddClass). The automated run also applies a label and a teacher (TST_CCLS_TC_16 / TST_CCLS_TC_15) and attaches a material before clicking Create, so it covers more than this case four steps.</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Automated: TST_CCLS_TC_15 (bulk suite).</t>
+          <t>Automated: TST_CCLS_TC_15 (workflow suite - moved from the bulk suite 2026-08-19, so the created class now carries a teacher).</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Automated: TST_CCLS_TC_16 (bulk suite). Note: the label dropdown is rendered once PER ROW (#class-label-list-modal-&lt;rowIndex&gt;), so selectors must be row-scoped.</t>
+          <t>Automated: TST_CCLS_TC_16 (workflow suite - moved from the bulk suite 2026-08-19, so the created class now carries a label). Note: the label dropdown is rendered once PER ROW (#class-label-list-modal-&lt;rowIndex&gt;), so selectors must be row-scoped.</t>
         </is>
       </c>
     </row>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="697">
   <si>
     <t>S.No.</t>
   </si>
@@ -817,811 +817,817 @@
     <t>The grading category is applied to &gt;=1 active class.</t>
   </si>
   <si>
-    <t>1. Open the category's See details page. 2. Click a listed class under Active classes.</t>
-  </si>
-  <si>
-    <t>A category applied to a class [ASSUMED]</t>
-  </si>
-  <si>
-    <t>The class grade settings page opens for the selected class. [ASSUMED] exact destination pending a category applied to a class.</t>
-  </si>
-  <si>
-    <t>Requires applying a category to a class first.</t>
+    <t>1. Open the category's See details page. 2. Click the row's 'Class grade settings' link.</t>
+  </si>
+  <si>
+    <t>Grading category 'some' applied to an active class (applied and saved by TST_CGST_TC_3)</t>
+  </si>
+  <si>
+    <t>The details page lists the class under 'Active classes (N)' showing its class name and class key, and the row's 'Class grade settings' link opens the Class grade settings page for that class.</t>
+  </si>
+  <si>
+    <t>CORRECTED 2026-08-20 after live capture: step 2 previously read 'click a listed class', but the class name is plain text - the row's only control is a 'Class grade settings' link. This page counts ACTIVE classes only, so the row disappears as soon as the class is deleted. Automated as TST_GCAT_TC_7, which runs inside the CGST suite.</t>
+  </si>
+  <si>
+    <t>As expected. 'Active classes (1)' listed the class under test with its class name and key; the row's 'Class grade settings' link opened the Class grade settings page for that class.</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>TST_GCAT_TC_8</t>
+  </si>
+  <si>
+    <t>Verify a grading category is removed after confirmation</t>
+  </si>
+  <si>
+    <t>#8 — Verify delete grading category</t>
+  </si>
+  <si>
+    <t>On the Manage grading categories page with &gt;=1 removable category.</t>
+  </si>
+  <si>
+    <t>1. Open grade options. 2. Click Remove. 3. Click Yes, remove.</t>
+  </si>
+  <si>
+    <t>Confirmation modal (Remove grading category - Are you sure? Removing the category will not affect classes currently using it, but you will not be able to add it to any new classes); after Yes, remove -&gt; banner Grading category successfully removed; category gone.</t>
+  </si>
+  <si>
+    <t>Automated as TST_GCAT_TC_8. Creates its own AutoCat_remove_&lt;epoch-ms&gt; first, so the destructive confirmation is only ever aimed at our own data - never at a pre-existing school category. Also asserts the category IS listed before removing it.</t>
+  </si>
+  <si>
+    <t>PASS. Confirmation modal shown with the expected copy; after 'Yes, remove' the banner 'Grading category successfully removed' appeared (~2.2 s) and the category left the list.</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>TST_GCAT_TC_9</t>
+  </si>
+  <si>
+    <t>Verify removing a grading category can be cancelled</t>
+  </si>
+  <si>
+    <t>1. Open grade options -&gt; Remove. 2. Click No, go back.</t>
+  </si>
+  <si>
+    <t>Confirmation closes; category remains in the list (not removed).</t>
+  </si>
+  <si>
+    <t>Automated as TST_GCAT_TC_9. Creates its own AutoCat_cancelremove_&lt;epoch-ms&gt; so the Remove confirmation is never opened against real school data. Modal closure is asserted on VISIBILITY, not presence - all four modals on this page stay in the DOM permanently, so a presence check could never fail.</t>
+  </si>
+  <si>
+    <t>PASS. After 'No, go back' the confirmation closed and the category was still listed.</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>TST_BCCF_TC_1</t>
+  </si>
+  <si>
+    <t>Verify the Create new classes (bulk) form loads with all components</t>
+  </si>
+  <si>
+    <t>#3 — Verify bulk class creation form is working fine</t>
+  </si>
+  <si>
+    <t>1. Click Add class.</t>
+  </si>
+  <si>
+    <t>Create new classes form opens (/class/create) with subtitle in &lt;school&gt;, Upload file, Get CSV template, How to use this form, bulk-action toolbar (Start date, End date, Add teacher, Add labels, Add Material, Copy an Existing Class, Duplicate, Show student progress, Remove), and a class row (Class name, Start date, End date, Add teachers, Add materials, Add label). Create N class is disabled.</t>
+  </si>
+  <si>
+    <t>Form auto-saves a draft.</t>
+  </si>
+  <si>
+    <t>Form opened at /class/create with all components present: Upload file, Get CSV template, How to use this form, all 9 bulk-toolbar actions, and row 1 (name, dates, teachers, materials, label). Create button disabled on an empty row.</t>
+  </si>
+  <si>
+    <t>Automated: TST_CCLS_TC_14 (bulk suite, 11/11).</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>TST_BCCF_TC_2</t>
+  </si>
+  <si>
+    <t>Verify a single class is created with a name and start/end dates</t>
+  </si>
+  <si>
+    <t>On the Create new classes form.</t>
+  </si>
+  <si>
+    <t>1. Enter class name. 2. Set Start date (today). 3. Set End date. 4. Click Create 1 class.</t>
+  </si>
+  <si>
+    <t>Name AutoClass_CreateOnly, Start today, End day 15 of next month</t>
+  </si>
+  <si>
+    <t>Success dialog Success! We are now creating 1 class for you appears; creation is asynchronous (email report; up to 12 hours).</t>
+  </si>
+  <si>
+    <t>Covered by automation TST_CCLS_TC_1..4. Corrected 2026-08-19: the register previously named AutoClass_Bulk, which is the bulk suite fixture. The workflow suite that actually runs this case uses AutoClass_CreateOnly (C1.adminAddClass). The automated run also applies a label and a teacher (TST_CCLS_TC_16 / TST_CCLS_TC_15) and attaches a material before clicking Create, so it covers more than this case four steps.</t>
+  </si>
+  <si>
+    <t>Class created with name + start/end dates; success dialog shown: "Success! We are now creating 1 class for you".</t>
+  </si>
+  <si>
+    <t>Automated: TST_CCLS_TC_1..4 (workflow suite). Creation is asynchronous.</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>TST_BCCF_TC_3</t>
+  </si>
+  <si>
+    <t>Verify a teacher can be added to a class row</t>
+  </si>
+  <si>
+    <t>A class row with a name entered.</t>
+  </si>
+  <si>
+    <t>1. Click Add teachers. 2. In Edit teachers modal, enter Email (and optional First/Last name). 3. Click Apply changes.</t>
+  </si>
+  <si>
+    <t>Teacher email: &lt;TEACHER_EMAIL&gt;</t>
+  </si>
+  <si>
+    <t>Teacher added to the class row. Modal notes changes only apply to this class.</t>
+  </si>
+  <si>
+    <t>Email required; names optional.</t>
+  </si>
+  <si>
+    <t>Teacher added via the "Edit teachers" modal (Email only); the teacher rendered on the class row.</t>
+  </si>
+  <si>
+    <t>Automated: TST_CCLS_TC_15 (workflow suite - moved from the bulk suite 2026-08-19, so the created class now carries a teacher).</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>TST_BCCF_TC_4</t>
+  </si>
+  <si>
+    <t>Verify a material can be added to a class row</t>
+  </si>
+  <si>
+    <t>1. Click Add materials. 2. Search and select a material. 3. Click Add materials.</t>
+  </si>
+  <si>
+    <t>Material: dev_test_ebook_bundle_104_bundle</t>
+  </si>
+  <si>
+    <t>Material attaches to the class row.</t>
+  </si>
+  <si>
+    <t>Covered by automation TST_CCLS_TC_5..7.</t>
+  </si>
+  <si>
+    <t>Material searched, selected and attached to the class row.</t>
+  </si>
+  <si>
+    <t>Feature verified working (workflow suite 13/13 earlier on 2026-08-18). NOTE: the automation (TST_CCLS_TC_5..7) is currently FLAKY - its selector uses a positional index (dBulkClass-add-learning-material-modal-1-0) that shifts with the form's row count when an auto-saved draft is restored. Pre-existing automation fragility, not a product defect. Fix pending: reset the form before the suite runs.</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>TST_BCCF_TC_5</t>
+  </si>
+  <si>
+    <t>Verify a label can be added to a class row</t>
+  </si>
+  <si>
+    <t>1. Click Add class label. 2. Select an existing label (or + Create new label).</t>
+  </si>
+  <si>
+    <t>Label: VM1</t>
+  </si>
+  <si>
+    <t>Chosen label applied to the row; dropdown also offers + Create new label and Edit labels.</t>
+  </si>
+  <si>
+    <t>Label "VM1" selected from the Add class label dropdown and applied to the row (row button then read "+ VM1").</t>
+  </si>
+  <si>
+    <t>Automated: TST_CCLS_TC_16 (workflow suite - moved from the bulk suite 2026-08-19, so the created class now carries a label). Note: the label dropdown is rendered once PER ROW (#class-label-list-modal-&lt;rowIndex&gt;), so selectors must be row-scoped.</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>TST_BCCF_TC_6</t>
+  </si>
+  <si>
+    <t>Verify multiple classes are created at once (bulk)</t>
+  </si>
+  <si>
+    <t>1. Fill name + dates on row 1. 2. Fill row 2. 3. Click Create 2 classes.</t>
+  </si>
+  <si>
+    <t>2 valid class rows</t>
+  </si>
+  <si>
+    <t>Create button reflects the count (Create 2 classes); success dialog shown for N classes. Empty rows auto-append while filling.</t>
+  </si>
+  <si>
+    <t>Filling a second row increased the Create button from "Create 1 class" to "Create 2 classes"; new empty rows auto-appended.</t>
+  </si>
+  <si>
+    <t>Automated: TST_CCLS_TC_13 (bulk suite). Asserts the count delta; does not click Create, so no class is created.</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>TST_BCCF_TC_7</t>
+  </si>
+  <si>
+    <t>Verify Duplicate copies a selected class row</t>
+  </si>
+  <si>
+    <t>At least one class row is filled.</t>
+  </si>
+  <si>
+    <t>1. Select a row. 2. Click Duplicate in the toolbar. 3. Confirm if prompted.</t>
+  </si>
+  <si>
+    <t>A duplicate row is added with the same details. [ASSUMED] confirm exact behaviour/confirmation.</t>
+  </si>
+  <si>
+    <t>Duplicate appended a copy AFTER the last filled row carrying the same name, dates, teacher and material. Label copied only after confirming the "Apply the labels to new classes too?" dialog.</t>
+  </si>
+  <si>
+    <t>Automated: TST_CCLS_TC_18 (bulk suite). [ASSUMED] resolved.</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>TST_BCCF_TC_8</t>
+  </si>
+  <si>
+    <t>Verify Copy an Existing Class copies settings to selected rows</t>
+  </si>
+  <si>
+    <t>At least one class row selected.</t>
+  </si>
+  <si>
+    <t>1. Select row(s). 2. Click Copy an Existing Class. 3. Choose a source class and what to copy. 4. Continue.</t>
+  </si>
+  <si>
+    <t>Source class: &lt;EXISTING_CLASS&gt; [ASSUMED]</t>
+  </si>
+  <si>
+    <t>Modal lets you choose an existing class and what to copy (materials/teachers/settings) to selected rows. [ASSUMED] confirm options/flow.</t>
+  </si>
+  <si>
+    <t>Toolbar aria-label: Choose what to copy from an existing class to the selected classes.</t>
+  </si>
+  <si>
+    <t>2-step wizard: searched and selected a source class, then chose Teachers + Course materials; both were applied to the selected row and the "Copied from a class" cell recorded the source. Row's own name/dates were not overwritten.</t>
+  </si>
+  <si>
+    <t>Automated: TST_CCLS_TC_21 (bulk suite). [ASSUMED] resolved. Options are disabled when the source class has none of that kind (e.g. "Assignments [0]").</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>TST_BCCF_TC_9</t>
+  </si>
+  <si>
+    <t>Verify bulk-setting start/end date for multiple selected rows</t>
+  </si>
+  <si>
+    <t>Two or more class rows exist.</t>
+  </si>
+  <si>
+    <t>1. Select multiple rows. 2. Click Start date in the toolbar and pick a date. 3. Click End date and pick a date.</t>
+  </si>
+  <si>
+    <t>Chosen start/end dates apply to all selected rows at once.</t>
+  </si>
+  <si>
+    <t>Same pattern for bulk Add teacher/labels/material.</t>
+  </si>
+  <si>
+    <t>Toolbar Start date and End date applied the chosen dates to the selected row.</t>
+  </si>
+  <si>
+    <t>Automated: TST_CCLS_TC_17 (bulk suite). Note: applying a bulk date CLEARS the row selection, so rows must be re-selected before the next bulk action.</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>TST_BCCF_TC_10</t>
+  </si>
+  <si>
+    <t>Verify Get CSV template downloads the upload template</t>
+  </si>
+  <si>
+    <t>1. Click Get CSV template.</t>
+  </si>
+  <si>
+    <t>A CSV template downloads with the correct headers for bulk class creation. [ASSUMED] capture exact headers.</t>
+  </si>
+  <si>
+    <t>Class_creation_form_template.csv downloaded with 14 columns exactly as listed in Expected Result.</t>
+  </si>
+  <si>
+    <t>Automated: TST_CCLS_TC_22 (bulk suite). Required adding downloadFile() to baseActionLibrary.js (protected file, confirmed).</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>TST_BCCF_TC_11</t>
+  </si>
+  <si>
+    <t>Verify uploading a CSV bulk-creates classes</t>
+  </si>
+  <si>
+    <t>A populated CSV in the template format is available.</t>
+  </si>
+  <si>
+    <t>1. Click Upload file. 2. Select the CSV. 3. Wait for upload to complete.</t>
+  </si>
+  <si>
+    <t>&lt;BULK_CLASSES_CSV&gt; [ASSUMED]</t>
+  </si>
+  <si>
+    <t>Classes from the CSV are added/created; an upload progress indicator shows during processing. [ASSUMED] confirm flow/validation.</t>
+  </si>
+  <si>
+    <t>Uploading a 2-row CSV populated both class rows with names and dates parsed from DD/MM/YYYY; Create button rose to "Create 2 classes". No class was created by the upload itself.</t>
+  </si>
+  <si>
+    <t>Automated: TST_CCLS_TC_19 (bulk suite). [ASSUMED] resolved - upload POPULATES the form, it does not create.</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>TST_BCCF_TC_12</t>
+  </si>
+  <si>
+    <t>Verify Back to dashboard and Create more classes from the success dialog</t>
+  </si>
+  <si>
+    <t>A class was just created (success dialog shown).</t>
+  </si>
+  <si>
+    <t>1. Click Back to dashboard. 2. (Separately) create again and click Create more classes.</t>
+  </si>
+  <si>
+    <t>Back to dashboard returns to the school Classes page; Create more classes returns to a fresh Create form. [ASSUMED] confirm form reset.</t>
+  </si>
+  <si>
+    <t>Back to dashboard covered by automation TST_CCLS_TC_8.</t>
+  </si>
+  <si>
+    <t>"Back to dashboard" returned to the school Classes page. "Create more classes" returned a COMPLETELY EMPTY create form (name and both dates blank).</t>
+  </si>
+  <si>
+    <t>Automated: TST_CCLS_TC_8 (Back to dashboard) + TST_CCLS_TC_20 (Create more classes), workflow suite. [ASSUMED] resolved - it does reset the form; the only path that does not restore the draft.</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>TST_BCCF_TC_13</t>
+  </si>
+  <si>
+    <t>Verify a class name at the 50-character maximum is accepted</t>
+  </si>
+  <si>
+    <t>On a class row.</t>
+  </si>
+  <si>
+    <t>1. Enter a 50-character class name.</t>
+  </si>
+  <si>
+    <t>Name accepted (maxlength 50); no more than 50 characters can be entered.</t>
+  </si>
+  <si>
+    <t>Class-name input enforces maxlength=50.</t>
+  </si>
+  <si>
+    <t>Automated: TST_CCLS_TC_11 (validation suite, 6/6).</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>TST_BCCF_TC_14</t>
+  </si>
+  <si>
+    <t>Verify the end date cannot be set before the start date</t>
+  </si>
+  <si>
+    <t>A start date is set on a row.</t>
+  </si>
+  <si>
+    <t>1. Open the End date picker.</t>
+  </si>
+  <si>
+    <t>Start = today</t>
+  </si>
+  <si>
+    <t>Dates on/before the start date are disabled in the end-date picker; end &lt; start cannot be chosen.</t>
+  </si>
+  <si>
+    <t>Observed: days &lt;= start are owl-dt-calendar-cell-disabled.</t>
+  </si>
+  <si>
+    <t>With start date = today, the End-date picker showed 22 disabled day cells (all dates on/before the start).</t>
+  </si>
+  <si>
+    <t>Automated: TST_CCLS_TC_12 (validation suite). Count is date-dependent (18 on 14 Aug, 22 on 18 Aug) so the assertion checks &gt; 0.</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>TST_BCCF_TC_15</t>
+  </si>
+  <si>
+    <t>Verify Create is disabled until class name and both dates are provided</t>
+  </si>
+  <si>
+    <t>1. Fill only some of {name, start, end} on a row. 2. Observe the Create button.</t>
+  </si>
+  <si>
+    <t>Incomplete row</t>
+  </si>
+  <si>
+    <t>Create N class button stays disabled until the row has name AND start date AND end date.</t>
+  </si>
+  <si>
+    <t>"Create N class" stayed disabled while the row was missing a required field.</t>
+  </si>
+  <si>
+    <t>Automated: TST_CCLS_TC_9 (validation suite).</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>TST_BCCF_TC_16</t>
+  </si>
+  <si>
+    <t>Verify an empty or non-alphanumeric class name is rejected</t>
+  </si>
+  <si>
+    <t>1. Leave the class name empty, or enter only non-alphanumeric characters (e.g. ---). 2. Attempt to create.</t>
+  </si>
+  <si>
+    <t>Name: (empty) / ---</t>
+  </si>
+  <si>
+    <t>Row is invalid - name requires at least one alphanumeric character (pattern .*[A-Za-z0-9]+.*) - so the class cannot be created. [ASSUMED] capture any inline error text.</t>
+  </si>
+  <si>
+    <t>A non-alphanumeric-only name ("---") left "Create N class" disabled.</t>
+  </si>
+  <si>
+    <t>Automated: TST_CCLS_TC_10 (validation suite).</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>TST_GSCL_TC_1</t>
+  </si>
+  <si>
+    <t>Verify the Manage grading scales page loads with all components</t>
+  </si>
+  <si>
+    <t>#10 — Verify manage grading scales page</t>
+  </si>
+  <si>
+    <t>1. Click School settings. 2. Click Manage grading scales.</t>
+  </si>
+  <si>
+    <t>Grading scales page opens (/grading-scales/manage) with heading Grading scales, User guide, Create grading scale button, and a list of scales. Cambridge One grading scale shows a default badge and only View details; custom scales offer View details / Set as default / Delete via Open drop down.</t>
+  </si>
+  <si>
+    <t>Reached via School settings dropdown.</t>
+  </si>
+  <si>
+    <t>As expected. Page opened at /grading-scales/manage with heading 'Grading scales', the User guide, the Create grading scale button, and the scale list. 'Cambridge One grading scale' carried the default badge.</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>TST_GSCL_TC_2</t>
+  </si>
+  <si>
+    <t>Verify a grading scale is created with a title, bands and target score</t>
+  </si>
+  <si>
+    <t>#11 — Verify Create grading scale</t>
+  </si>
+  <si>
+    <t>On the Grading scales page.</t>
+  </si>
+  <si>
+    <t>1. Click Create grading scale. 2. Enter title. 3. Enter Highest grade name + From %. 4. Enter Lowest grade name + To %. 5. Mark a band as Set as target score. 6. Click Save grading scale.</t>
+  </si>
+  <si>
+    <t>Title AutoTest Scale; Highest A 50-100%; Lowest F 0-49%; target A</t>
+  </si>
+  <si>
+    <t>Scale created and appears in the list showing its target score; bands cover 0-100% without overlap.</t>
+  </si>
+  <si>
+    <t>The Grading scale title input carries maxlength=20 (captured live 2026-08-19); grade-name inputs are also 20 and From/To are 3. Not previously documented - there is no boundary test case for it.</t>
+  </si>
+  <si>
+    <t>As expected. Save grading scale was disabled on the empty form and became enabled once title + bands + target were set; the scale was created and appeared in the list showing 'Target score 50%'. Bands A 50-100% / F 0-49% cover 0-100% without overlap.</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>TST_GSCL_TC_3</t>
+  </si>
+  <si>
+    <t>Verify a middle band can be added with + Add new grade</t>
+  </si>
+  <si>
+    <t>On the Create grading scale form.</t>
+  </si>
+  <si>
+    <t>1. Click + Add new grade. 2. Enter the middle band name + From-To %.</t>
+  </si>
+  <si>
+    <t>Middle band B 50-79%, adjust others to keep 0-100% coverage</t>
+  </si>
+  <si>
+    <t>A middle band row is added between Highest and Lowest; bands must still cover 0-100% without overlap.</t>
+  </si>
+  <si>
+    <t>Adding a middle band RE-INDEXES the Lowest grade row from 1 to 2. Any automation addressing bands by index must re-read the row count.</t>
+  </si>
+  <si>
+    <t>As expected. '+ Add new grade' inserted a middle band between Highest and Lowest. Note the re-indexing: before the click rows are 0=Highest, 1=Lowest; after, 0=Highest, 1=new middle band, 2=Lowest. The middle band exposes BOTH From and To. Automation creates nothing here - it cancels out.</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>TST_GSCL_TC_4</t>
+  </si>
+  <si>
+    <t>Verify the maximum-grading-scales limit is enforced</t>
+  </si>
+  <si>
+    <t>School already at the maximum number of grading scales.</t>
+  </si>
+  <si>
+    <t>1. Attempt to create another grading scale.</t>
+  </si>
+  <si>
+    <t>Modal: You have reached the maximum number of grading scales for this school. Please remove at least one grading scale to add a new one; no scale created. [ASSUMED] exact maximum.</t>
+  </si>
+  <si>
+    <t>The expected modal copy is now VERIFIED word for word - the modal is pre-rendered in the DOM, so it was captured without filling the school to its cap. Only triggering it is blocked (shared school).</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>TST_GSCL_TC_5</t>
+  </si>
+  <si>
+    <t>Verify Save is disabled until title, valid bands and target are provided</t>
+  </si>
+  <si>
+    <t>1. Leave title empty, or set bands that overlap / do not add up to 100%, or omit the target. 2. Observe Save grading scale.</t>
+  </si>
+  <si>
+    <t>Incomplete/invalid bands</t>
+  </si>
+  <si>
+    <t>Save grading scale stays disabled until the scale has a title, bands covering 0-100% without overlap, and a target score. [ASSUMED] capture overlap/gap validation copy.</t>
+  </si>
+  <si>
+    <t>As expected. Save grading scale stayed disabled on an empty form, with bands entered but no title, and with a title but incomplete bands.</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>TST_GSCL_TC_6</t>
+  </si>
+  <si>
+    <t>Verify the grading scale View details page opens</t>
+  </si>
+  <si>
+    <t>#12 — Verify view details page of grading scale</t>
+  </si>
+  <si>
+    <t>On the Grading scales page with &gt;=1 scale.</t>
+  </si>
+  <si>
+    <t>1. Click Open drop down on a scale. 2. Click View details.</t>
+  </si>
+  <si>
+    <t>Scale: AutoTest Scale</t>
+  </si>
+  <si>
+    <t>Details page opens (/grading-scales/&lt;id&gt;, title=scale name) with a collapsible Grading scale bands section and a Classes (N) section; empty state No classes yet. To associate the grading scale with a class, go to its Class grade settings page.</t>
+  </si>
+  <si>
+    <t>As expected. URL changed to /grading-scales/[id], the page title was the scale name, 'Grading scale bands' was present and collapsed, 'Classes (0)' was shown, and the empty state read 'No classes yet / To associate the grading scale with a class, go to its Class grade settings page'.</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>TST_GSCL_TC_7</t>
+  </si>
+  <si>
+    <t>Verify the class grade settings page launches from a scale's details page</t>
+  </si>
+  <si>
+    <t>#13 — Launch class grade setting page from view details page of grading scale</t>
+  </si>
+  <si>
+    <t>The grading scale is applied to &gt;=1 class.</t>
+  </si>
+  <si>
+    <t>1. Open the scale's View details page. 2. Click the row's 'Class grade settings' link.</t>
+  </si>
+  <si>
+    <t>Grading scale 'new Grading Auto' applied to an active class (applied and saved by TST_CGST_TC_2)</t>
+  </si>
+  <si>
+    <t>The details page lists the class under 'Classes (N)' showing its class name, key, dates and status, and the row's 'Class grade settings' link opens the Class grade settings page for that class.</t>
+  </si>
+  <si>
+    <t>CORRECTED 2026-08-20 after live capture: step 2 previously read 'click a listed class', but the class name is plain text - the row's only control is a 'Class grade settings' link. This page ALSO lists deleted classes; the link only works while the class is Active (a Deleted row redirects to My school accounts with 'The item is not available because the class is no longer active'). Automated as TST_GSCL_TC_7, which runs inside the CGST suite.</t>
+  </si>
+  <si>
+    <t>As expected. The class under test was listed with status Active; the row's 'Class grade settings' link opened the Class grade settings page for that class, showing the applied scale 'new Grading Auto'.</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>TST_GSCL_TC_8</t>
+  </si>
+  <si>
+    <t>Verify a grading scale can be set as the school default</t>
+  </si>
+  <si>
+    <t>#14 — Verify set as default for a grading scale</t>
+  </si>
+  <si>
+    <t>A custom (non-default) grading scale exists.</t>
+  </si>
+  <si>
+    <t>1. Open the custom scale's Open drop down -&gt; Set as default. 2. Click Yes, set as default.</t>
+  </si>
+  <si>
+    <t>Confirmation Set as default for the school? All newly created classes will be associated with this grading scale. Existing classes will not be affected; after Yes the scale becomes default (badge moves to it).</t>
+  </si>
+  <si>
+    <t>Only non-default scales offer Set as default.</t>
+  </si>
+  <si>
+    <t>As expected. The confirmation read 'Set as default for the school? All newly created classes will be associated with this grading scale. Existing classes will not be affected', and after 'Yes, set as default' the default badge moved to the new scale.</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>TST_GSCL_TC_9</t>
+  </si>
+  <si>
+    <t>Verify a grading scale is deleted after confirmation</t>
+  </si>
+  <si>
+    <t>#15 — Verify deleting a grading scale</t>
+  </si>
+  <si>
+    <t>A deletable (non-default) grading scale exists.</t>
+  </si>
+  <si>
+    <t>1. Open the scale's Open drop down -&gt; Delete. 2. Click Yes, delete.</t>
+  </si>
+  <si>
+    <t>Confirmation Are you sure? Deleting the grading scale will not affect classes associated with it, but it won't be available to apply to any new classes.; after Yes, delete the scale is removed from the list.</t>
+  </si>
+  <si>
+    <t>As expected. The confirmation read 'Are you sure? Deleting the grading scale will not affect classes associated with it, but it won’t be available to apply to any new classes. Delete this grading scale from your school?', and after 'Yes, delete' the scale left the list.</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>TST_GSCL_TC_10</t>
+  </si>
+  <si>
+    <t>Verify deleting a grading scale can be cancelled</t>
+  </si>
+  <si>
+    <t>A deletable grading scale exists.</t>
+  </si>
+  <si>
+    <t>1. Open drop down -&gt; Delete. 2. Click No, go back.</t>
+  </si>
+  <si>
+    <t>Confirmation closes; scale remains in the list (not deleted).</t>
+  </si>
+  <si>
+    <t>As expected. 'No, go back' closed the confirmation and the scale remained in the list.</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>TST_GSCL_TC_11</t>
+  </si>
+  <si>
+    <t>Verify the default grading scale cannot be deleted</t>
+  </si>
+  <si>
+    <t>On the Grading scales page (Cambridge One grading scale is default).</t>
+  </si>
+  <si>
+    <t>1. Open the Open drop down on the default scale.</t>
+  </si>
+  <si>
+    <t>Default scale: Cambridge One grading scale</t>
+  </si>
+  <si>
+    <t>The default scale's menu offers only View details - no Delete (nor Set as default) - so the default scale cannot be deleted.</t>
+  </si>
+  <si>
+    <t>The default scale's Delete / Set as default options are omitted from the DOM, not hidden - so their absence is genuinely assertable.</t>
+  </si>
+  <si>
+    <t>As expected. The default scale's menu offered only View details - Delete and Set as default are absent from the DOM entirely (element count 0), not merely hidden.</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>TST_GSCL_TC_12</t>
+  </si>
+  <si>
+    <t>Verify expanding the grading scale bands shows the bands</t>
+  </si>
+  <si>
+    <t>#16 — Verify expanding grading scale bands</t>
+  </si>
+  <si>
+    <t>On a grading scale's View details page.</t>
+  </si>
+  <si>
+    <t>1. Click Grading scale bands.</t>
+  </si>
+  <si>
+    <t>Section expands to list bands as Grade name / Band (e.g. A -&gt; 50% - 100% with Target score: 50%, F -&gt; 0% - 49%).</t>
+  </si>
+  <si>
+    <t>As expected. Clicking 'Grading scale bands' expanded the section to show Grade name / Band rows: A 50% - 100% with 'Target score: 50%', and F 0% - 49%.</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>TST_CMGT_TC_1</t>
+  </si>
+  <si>
+    <t>Verify an existing label can be added to a class</t>
+  </si>
+  <si>
+    <t>#21 — Add label in class</t>
+  </si>
+  <si>
+    <t>A class is open (Classes tab -&gt; launch a class -&gt; /view/classdata).</t>
+  </si>
+  <si>
+    <t>1. Click + Add labels. 2. Select an existing label.</t>
+  </si>
+  <si>
+    <t>The selected label is applied to the class and shown on it.</t>
+  </si>
+  <si>
+    <t>Same label list as bulk-create form (TST_BCCF_TC_5).</t>
   </si>
   <si>
     <t>Not Run</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>TST_GCAT_TC_8</t>
-  </si>
-  <si>
-    <t>Verify a grading category is removed after confirmation</t>
-  </si>
-  <si>
-    <t>#8 — Verify delete grading category</t>
-  </si>
-  <si>
-    <t>On the Manage grading categories page with &gt;=1 removable category.</t>
-  </si>
-  <si>
-    <t>1. Open grade options. 2. Click Remove. 3. Click Yes, remove.</t>
-  </si>
-  <si>
-    <t>Confirmation modal (Remove grading category - Are you sure? Removing the category will not affect classes currently using it, but you will not be able to add it to any new classes); after Yes, remove -&gt; banner Grading category successfully removed; category gone.</t>
-  </si>
-  <si>
-    <t>Automated as TST_GCAT_TC_8. Creates its own AutoCat_remove_&lt;epoch-ms&gt; first, so the destructive confirmation is only ever aimed at our own data - never at a pre-existing school category. Also asserts the category IS listed before removing it.</t>
-  </si>
-  <si>
-    <t>PASS. Confirmation modal shown with the expected copy; after 'Yes, remove' the banner 'Grading category successfully removed' appeared (~2.2 s) and the category left the list.</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>TST_GCAT_TC_9</t>
-  </si>
-  <si>
-    <t>Verify removing a grading category can be cancelled</t>
-  </si>
-  <si>
-    <t>1. Open grade options -&gt; Remove. 2. Click No, go back.</t>
-  </si>
-  <si>
-    <t>Confirmation closes; category remains in the list (not removed).</t>
-  </si>
-  <si>
-    <t>Automated as TST_GCAT_TC_9. Creates its own AutoCat_cancelremove_&lt;epoch-ms&gt; so the Remove confirmation is never opened against real school data. Modal closure is asserted on VISIBILITY, not presence - all four modals on this page stay in the DOM permanently, so a presence check could never fail.</t>
-  </si>
-  <si>
-    <t>PASS. After 'No, go back' the confirmation closed and the category was still listed.</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>TST_BCCF_TC_1</t>
-  </si>
-  <si>
-    <t>Verify the Create new classes (bulk) form loads with all components</t>
-  </si>
-  <si>
-    <t>#3 — Verify bulk class creation form is working fine</t>
-  </si>
-  <si>
-    <t>1. Click Add class.</t>
-  </si>
-  <si>
-    <t>Create new classes form opens (/class/create) with subtitle in &lt;school&gt;, Upload file, Get CSV template, How to use this form, bulk-action toolbar (Start date, End date, Add teacher, Add labels, Add Material, Copy an Existing Class, Duplicate, Show student progress, Remove), and a class row (Class name, Start date, End date, Add teachers, Add materials, Add label). Create N class is disabled.</t>
-  </si>
-  <si>
-    <t>Form auto-saves a draft.</t>
-  </si>
-  <si>
-    <t>Form opened at /class/create with all components present: Upload file, Get CSV template, How to use this form, all 9 bulk-toolbar actions, and row 1 (name, dates, teachers, materials, label). Create button disabled on an empty row.</t>
-  </si>
-  <si>
-    <t>Automated: TST_CCLS_TC_14 (bulk suite, 11/11).</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>TST_BCCF_TC_2</t>
-  </si>
-  <si>
-    <t>Verify a single class is created with a name and start/end dates</t>
-  </si>
-  <si>
-    <t>On the Create new classes form.</t>
-  </si>
-  <si>
-    <t>1. Enter class name. 2. Set Start date (today). 3. Set End date. 4. Click Create 1 class.</t>
-  </si>
-  <si>
-    <t>Name AutoClass_CreateOnly, Start today, End day 15 of next month</t>
-  </si>
-  <si>
-    <t>Success dialog Success! We are now creating 1 class for you appears; creation is asynchronous (email report; up to 12 hours).</t>
-  </si>
-  <si>
-    <t>Covered by automation TST_CCLS_TC_1..4. Corrected 2026-08-19: the register previously named AutoClass_Bulk, which is the bulk suite fixture. The workflow suite that actually runs this case uses AutoClass_CreateOnly (C1.adminAddClass). The automated run also applies a label and a teacher (TST_CCLS_TC_16 / TST_CCLS_TC_15) and attaches a material before clicking Create, so it covers more than this case four steps.</t>
-  </si>
-  <si>
-    <t>Class created with name + start/end dates; success dialog shown: "Success! We are now creating 1 class for you".</t>
-  </si>
-  <si>
-    <t>Automated: TST_CCLS_TC_1..4 (workflow suite). Creation is asynchronous.</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>TST_BCCF_TC_3</t>
-  </si>
-  <si>
-    <t>Verify a teacher can be added to a class row</t>
-  </si>
-  <si>
-    <t>A class row with a name entered.</t>
-  </si>
-  <si>
-    <t>1. Click Add teachers. 2. In Edit teachers modal, enter Email (and optional First/Last name). 3. Click Apply changes.</t>
-  </si>
-  <si>
-    <t>Teacher email: &lt;TEACHER_EMAIL&gt;</t>
-  </si>
-  <si>
-    <t>Teacher added to the class row. Modal notes changes only apply to this class.</t>
-  </si>
-  <si>
-    <t>Email required; names optional.</t>
-  </si>
-  <si>
-    <t>Teacher added via the "Edit teachers" modal (Email only); the teacher rendered on the class row.</t>
-  </si>
-  <si>
-    <t>Automated: TST_CCLS_TC_15 (workflow suite - moved from the bulk suite 2026-08-19, so the created class now carries a teacher).</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>TST_BCCF_TC_4</t>
-  </si>
-  <si>
-    <t>Verify a material can be added to a class row</t>
-  </si>
-  <si>
-    <t>1. Click Add materials. 2. Search and select a material. 3. Click Add materials.</t>
-  </si>
-  <si>
-    <t>Material: dev_test_ebook_bundle_104_bundle</t>
-  </si>
-  <si>
-    <t>Material attaches to the class row.</t>
-  </si>
-  <si>
-    <t>Covered by automation TST_CCLS_TC_5..7.</t>
-  </si>
-  <si>
-    <t>Material searched, selected and attached to the class row.</t>
-  </si>
-  <si>
-    <t>Feature verified working (workflow suite 13/13 earlier on 2026-08-18). NOTE: the automation (TST_CCLS_TC_5..7) is currently FLAKY - its selector uses a positional index (dBulkClass-add-learning-material-modal-1-0) that shifts with the form's row count when an auto-saved draft is restored. Pre-existing automation fragility, not a product defect. Fix pending: reset the form before the suite runs.</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>TST_BCCF_TC_5</t>
-  </si>
-  <si>
-    <t>Verify a label can be added to a class row</t>
-  </si>
-  <si>
-    <t>1. Click Add class label. 2. Select an existing label (or + Create new label).</t>
-  </si>
-  <si>
-    <t>Label: VM1</t>
-  </si>
-  <si>
-    <t>Chosen label applied to the row; dropdown also offers + Create new label and Edit labels.</t>
-  </si>
-  <si>
-    <t>Label "VM1" selected from the Add class label dropdown and applied to the row (row button then read "+ VM1").</t>
-  </si>
-  <si>
-    <t>Automated: TST_CCLS_TC_16 (workflow suite - moved from the bulk suite 2026-08-19, so the created class now carries a label). Note: the label dropdown is rendered once PER ROW (#class-label-list-modal-&lt;rowIndex&gt;), so selectors must be row-scoped.</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>TST_BCCF_TC_6</t>
-  </si>
-  <si>
-    <t>Verify multiple classes are created at once (bulk)</t>
-  </si>
-  <si>
-    <t>1. Fill name + dates on row 1. 2. Fill row 2. 3. Click Create 2 classes.</t>
-  </si>
-  <si>
-    <t>2 valid class rows</t>
-  </si>
-  <si>
-    <t>Create button reflects the count (Create 2 classes); success dialog shown for N classes. Empty rows auto-append while filling.</t>
-  </si>
-  <si>
-    <t>Filling a second row increased the Create button from "Create 1 class" to "Create 2 classes"; new empty rows auto-appended.</t>
-  </si>
-  <si>
-    <t>Automated: TST_CCLS_TC_13 (bulk suite). Asserts the count delta; does not click Create, so no class is created.</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>TST_BCCF_TC_7</t>
-  </si>
-  <si>
-    <t>Verify Duplicate copies a selected class row</t>
-  </si>
-  <si>
-    <t>At least one class row is filled.</t>
-  </si>
-  <si>
-    <t>1. Select a row. 2. Click Duplicate in the toolbar. 3. Confirm if prompted.</t>
-  </si>
-  <si>
-    <t>A duplicate row is added with the same details. [ASSUMED] confirm exact behaviour/confirmation.</t>
-  </si>
-  <si>
-    <t>Duplicate appended a copy AFTER the last filled row carrying the same name, dates, teacher and material. Label copied only after confirming the "Apply the labels to new classes too?" dialog.</t>
-  </si>
-  <si>
-    <t>Automated: TST_CCLS_TC_18 (bulk suite). [ASSUMED] resolved.</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>TST_BCCF_TC_8</t>
-  </si>
-  <si>
-    <t>Verify Copy an Existing Class copies settings to selected rows</t>
-  </si>
-  <si>
-    <t>At least one class row selected.</t>
-  </si>
-  <si>
-    <t>1. Select row(s). 2. Click Copy an Existing Class. 3. Choose a source class and what to copy. 4. Continue.</t>
-  </si>
-  <si>
-    <t>Source class: &lt;EXISTING_CLASS&gt; [ASSUMED]</t>
-  </si>
-  <si>
-    <t>Modal lets you choose an existing class and what to copy (materials/teachers/settings) to selected rows. [ASSUMED] confirm options/flow.</t>
-  </si>
-  <si>
-    <t>Toolbar aria-label: Choose what to copy from an existing class to the selected classes.</t>
-  </si>
-  <si>
-    <t>2-step wizard: searched and selected a source class, then chose Teachers + Course materials; both were applied to the selected row and the "Copied from a class" cell recorded the source. Row's own name/dates were not overwritten.</t>
-  </si>
-  <si>
-    <t>Automated: TST_CCLS_TC_21 (bulk suite). [ASSUMED] resolved. Options are disabled when the source class has none of that kind (e.g. "Assignments [0]").</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>TST_BCCF_TC_9</t>
-  </si>
-  <si>
-    <t>Verify bulk-setting start/end date for multiple selected rows</t>
-  </si>
-  <si>
-    <t>Two or more class rows exist.</t>
-  </si>
-  <si>
-    <t>1. Select multiple rows. 2. Click Start date in the toolbar and pick a date. 3. Click End date and pick a date.</t>
-  </si>
-  <si>
-    <t>Chosen start/end dates apply to all selected rows at once.</t>
-  </si>
-  <si>
-    <t>Same pattern for bulk Add teacher/labels/material.</t>
-  </si>
-  <si>
-    <t>Toolbar Start date and End date applied the chosen dates to the selected row.</t>
-  </si>
-  <si>
-    <t>Automated: TST_CCLS_TC_17 (bulk suite). Note: applying a bulk date CLEARS the row selection, so rows must be re-selected before the next bulk action.</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>TST_BCCF_TC_10</t>
-  </si>
-  <si>
-    <t>Verify Get CSV template downloads the upload template</t>
-  </si>
-  <si>
-    <t>1. Click Get CSV template.</t>
-  </si>
-  <si>
-    <t>A CSV template downloads with the correct headers for bulk class creation. [ASSUMED] capture exact headers.</t>
-  </si>
-  <si>
-    <t>Class_creation_form_template.csv downloaded with 14 columns exactly as listed in Expected Result.</t>
-  </si>
-  <si>
-    <t>Automated: TST_CCLS_TC_22 (bulk suite). Required adding downloadFile() to baseActionLibrary.js (protected file, confirmed).</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>TST_BCCF_TC_11</t>
-  </si>
-  <si>
-    <t>Verify uploading a CSV bulk-creates classes</t>
-  </si>
-  <si>
-    <t>A populated CSV in the template format is available.</t>
-  </si>
-  <si>
-    <t>1. Click Upload file. 2. Select the CSV. 3. Wait for upload to complete.</t>
-  </si>
-  <si>
-    <t>&lt;BULK_CLASSES_CSV&gt; [ASSUMED]</t>
-  </si>
-  <si>
-    <t>Classes from the CSV are added/created; an upload progress indicator shows during processing. [ASSUMED] confirm flow/validation.</t>
-  </si>
-  <si>
-    <t>Uploading a 2-row CSV populated both class rows with names and dates parsed from DD/MM/YYYY; Create button rose to "Create 2 classes". No class was created by the upload itself.</t>
-  </si>
-  <si>
-    <t>Automated: TST_CCLS_TC_19 (bulk suite). [ASSUMED] resolved - upload POPULATES the form, it does not create.</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>TST_BCCF_TC_12</t>
-  </si>
-  <si>
-    <t>Verify Back to dashboard and Create more classes from the success dialog</t>
-  </si>
-  <si>
-    <t>A class was just created (success dialog shown).</t>
-  </si>
-  <si>
-    <t>1. Click Back to dashboard. 2. (Separately) create again and click Create more classes.</t>
-  </si>
-  <si>
-    <t>Back to dashboard returns to the school Classes page; Create more classes returns to a fresh Create form. [ASSUMED] confirm form reset.</t>
-  </si>
-  <si>
-    <t>Back to dashboard covered by automation TST_CCLS_TC_8.</t>
-  </si>
-  <si>
-    <t>"Back to dashboard" returned to the school Classes page. "Create more classes" returned a COMPLETELY EMPTY create form (name and both dates blank).</t>
-  </si>
-  <si>
-    <t>Automated: TST_CCLS_TC_8 (Back to dashboard) + TST_CCLS_TC_20 (Create more classes), workflow suite. [ASSUMED] resolved - it does reset the form; the only path that does not restore the draft.</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>TST_BCCF_TC_13</t>
-  </si>
-  <si>
-    <t>Verify a class name at the 50-character maximum is accepted</t>
-  </si>
-  <si>
-    <t>On a class row.</t>
-  </si>
-  <si>
-    <t>1. Enter a 50-character class name.</t>
-  </si>
-  <si>
-    <t>Name accepted (maxlength 50); no more than 50 characters can be entered.</t>
-  </si>
-  <si>
-    <t>Class-name input enforces maxlength=50.</t>
-  </si>
-  <si>
-    <t>Automated: TST_CCLS_TC_11 (validation suite, 6/6).</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>TST_BCCF_TC_14</t>
-  </si>
-  <si>
-    <t>Verify the end date cannot be set before the start date</t>
-  </si>
-  <si>
-    <t>A start date is set on a row.</t>
-  </si>
-  <si>
-    <t>1. Open the End date picker.</t>
-  </si>
-  <si>
-    <t>Start = today</t>
-  </si>
-  <si>
-    <t>Dates on/before the start date are disabled in the end-date picker; end &lt; start cannot be chosen.</t>
-  </si>
-  <si>
-    <t>Observed: days &lt;= start are owl-dt-calendar-cell-disabled.</t>
-  </si>
-  <si>
-    <t>With start date = today, the End-date picker showed 22 disabled day cells (all dates on/before the start).</t>
-  </si>
-  <si>
-    <t>Automated: TST_CCLS_TC_12 (validation suite). Count is date-dependent (18 on 14 Aug, 22 on 18 Aug) so the assertion checks &gt; 0.</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>TST_BCCF_TC_15</t>
-  </si>
-  <si>
-    <t>Verify Create is disabled until class name and both dates are provided</t>
-  </si>
-  <si>
-    <t>1. Fill only some of {name, start, end} on a row. 2. Observe the Create button.</t>
-  </si>
-  <si>
-    <t>Incomplete row</t>
-  </si>
-  <si>
-    <t>Create N class button stays disabled until the row has name AND start date AND end date.</t>
-  </si>
-  <si>
-    <t>"Create N class" stayed disabled while the row was missing a required field.</t>
-  </si>
-  <si>
-    <t>Automated: TST_CCLS_TC_9 (validation suite).</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>TST_BCCF_TC_16</t>
-  </si>
-  <si>
-    <t>Verify an empty or non-alphanumeric class name is rejected</t>
-  </si>
-  <si>
-    <t>1. Leave the class name empty, or enter only non-alphanumeric characters (e.g. ---). 2. Attempt to create.</t>
-  </si>
-  <si>
-    <t>Name: (empty) / ---</t>
-  </si>
-  <si>
-    <t>Row is invalid - name requires at least one alphanumeric character (pattern .*[A-Za-z0-9]+.*) - so the class cannot be created. [ASSUMED] capture any inline error text.</t>
-  </si>
-  <si>
-    <t>A non-alphanumeric-only name ("---") left "Create N class" disabled.</t>
-  </si>
-  <si>
-    <t>Automated: TST_CCLS_TC_10 (validation suite).</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>TST_GSCL_TC_1</t>
-  </si>
-  <si>
-    <t>Verify the Manage grading scales page loads with all components</t>
-  </si>
-  <si>
-    <t>#10 — Verify manage grading scales page</t>
-  </si>
-  <si>
-    <t>1. Click School settings. 2. Click Manage grading scales.</t>
-  </si>
-  <si>
-    <t>Grading scales page opens (/grading-scales/manage) with heading Grading scales, User guide, Create grading scale button, and a list of scales. Cambridge One grading scale shows a default badge and only View details; custom scales offer View details / Set as default / Delete via Open drop down.</t>
-  </si>
-  <si>
-    <t>Reached via School settings dropdown.</t>
-  </si>
-  <si>
-    <t>As expected. Page opened at /grading-scales/manage with heading 'Grading scales', the User guide, the Create grading scale button, and the scale list. 'Cambridge One grading scale' carried the default badge.</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>TST_GSCL_TC_2</t>
-  </si>
-  <si>
-    <t>Verify a grading scale is created with a title, bands and target score</t>
-  </si>
-  <si>
-    <t>#11 — Verify Create grading scale</t>
-  </si>
-  <si>
-    <t>On the Grading scales page.</t>
-  </si>
-  <si>
-    <t>1. Click Create grading scale. 2. Enter title. 3. Enter Highest grade name + From %. 4. Enter Lowest grade name + To %. 5. Mark a band as Set as target score. 6. Click Save grading scale.</t>
-  </si>
-  <si>
-    <t>Title AutoTest Scale; Highest A 50-100%; Lowest F 0-49%; target A</t>
-  </si>
-  <si>
-    <t>Scale created and appears in the list showing its target score; bands cover 0-100% without overlap.</t>
-  </si>
-  <si>
-    <t>The Grading scale title input carries maxlength=20 (captured live 2026-08-19); grade-name inputs are also 20 and From/To are 3. Not previously documented - there is no boundary test case for it.</t>
-  </si>
-  <si>
-    <t>As expected. Save grading scale was disabled on the empty form and became enabled once title + bands + target were set; the scale was created and appeared in the list showing 'Target score 50%'. Bands A 50-100% / F 0-49% cover 0-100% without overlap.</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>TST_GSCL_TC_3</t>
-  </si>
-  <si>
-    <t>Verify a middle band can be added with + Add new grade</t>
-  </si>
-  <si>
-    <t>On the Create grading scale form.</t>
-  </si>
-  <si>
-    <t>1. Click + Add new grade. 2. Enter the middle band name + From-To %.</t>
-  </si>
-  <si>
-    <t>Middle band B 50-79%, adjust others to keep 0-100% coverage</t>
-  </si>
-  <si>
-    <t>A middle band row is added between Highest and Lowest; bands must still cover 0-100% without overlap.</t>
-  </si>
-  <si>
-    <t>Adding a middle band RE-INDEXES the Lowest grade row from 1 to 2. Any automation addressing bands by index must re-read the row count.</t>
-  </si>
-  <si>
-    <t>As expected. '+ Add new grade' inserted a middle band between Highest and Lowest. Note the re-indexing: before the click rows are 0=Highest, 1=Lowest; after, 0=Highest, 1=new middle band, 2=Lowest. The middle band exposes BOTH From and To. Automation creates nothing here - it cancels out.</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>TST_GSCL_TC_4</t>
-  </si>
-  <si>
-    <t>Verify the maximum-grading-scales limit is enforced</t>
-  </si>
-  <si>
-    <t>School already at the maximum number of grading scales.</t>
-  </si>
-  <si>
-    <t>1. Attempt to create another grading scale.</t>
-  </si>
-  <si>
-    <t>Modal: You have reached the maximum number of grading scales for this school. Please remove at least one grading scale to add a new one; no scale created. [ASSUMED] exact maximum.</t>
-  </si>
-  <si>
-    <t>The expected modal copy is now VERIFIED word for word - the modal is pre-rendered in the DOM, so it was captured without filling the school to its cap. Only triggering it is blocked (shared school).</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>TST_GSCL_TC_5</t>
-  </si>
-  <si>
-    <t>Verify Save is disabled until title, valid bands and target are provided</t>
-  </si>
-  <si>
-    <t>1. Leave title empty, or set bands that overlap / do not add up to 100%, or omit the target. 2. Observe Save grading scale.</t>
-  </si>
-  <si>
-    <t>Incomplete/invalid bands</t>
-  </si>
-  <si>
-    <t>Save grading scale stays disabled until the scale has a title, bands covering 0-100% without overlap, and a target score. [ASSUMED] capture overlap/gap validation copy.</t>
-  </si>
-  <si>
-    <t>As expected. Save grading scale stayed disabled on an empty form, with bands entered but no title, and with a title but incomplete bands.</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>TST_GSCL_TC_6</t>
-  </si>
-  <si>
-    <t>Verify the grading scale View details page opens</t>
-  </si>
-  <si>
-    <t>#12 — Verify view details page of grading scale</t>
-  </si>
-  <si>
-    <t>On the Grading scales page with &gt;=1 scale.</t>
-  </si>
-  <si>
-    <t>1. Click Open drop down on a scale. 2. Click View details.</t>
-  </si>
-  <si>
-    <t>Scale: AutoTest Scale</t>
-  </si>
-  <si>
-    <t>Details page opens (/grading-scales/&lt;id&gt;, title=scale name) with a collapsible Grading scale bands section and a Classes (N) section; empty state No classes yet. To associate the grading scale with a class, go to its Class grade settings page.</t>
-  </si>
-  <si>
-    <t>As expected. URL changed to /grading-scales/[id], the page title was the scale name, 'Grading scale bands' was present and collapsed, 'Classes (0)' was shown, and the empty state read 'No classes yet / To associate the grading scale with a class, go to its Class grade settings page'.</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>TST_GSCL_TC_7</t>
-  </si>
-  <si>
-    <t>Verify the class grade settings page launches from a scale's details page</t>
-  </si>
-  <si>
-    <t>#13 — Launch class grade setting page from view details page of grading scale</t>
-  </si>
-  <si>
-    <t>The grading scale is applied to &gt;=1 class.</t>
-  </si>
-  <si>
-    <t>1. Open the scale's View details page. 2. Click a listed class under Classes.</t>
-  </si>
-  <si>
-    <t>A scale applied to a class [ASSUMED]</t>
-  </si>
-  <si>
-    <t>The class grade settings page opens for the selected class. [ASSUMED] exact destination pending a scale applied to a class.</t>
-  </si>
-  <si>
-    <t>Associate a scale with a class via class grade settings first.</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>TST_GSCL_TC_8</t>
-  </si>
-  <si>
-    <t>Verify a grading scale can be set as the school default</t>
-  </si>
-  <si>
-    <t>#14 — Verify set as default for a grading scale</t>
-  </si>
-  <si>
-    <t>A custom (non-default) grading scale exists.</t>
-  </si>
-  <si>
-    <t>1. Open the custom scale's Open drop down -&gt; Set as default. 2. Click Yes, set as default.</t>
-  </si>
-  <si>
-    <t>Confirmation Set as default for the school? All newly created classes will be associated with this grading scale. Existing classes will not be affected; after Yes the scale becomes default (badge moves to it).</t>
-  </si>
-  <si>
-    <t>Only non-default scales offer Set as default.</t>
-  </si>
-  <si>
-    <t>As expected. The confirmation read 'Set as default for the school? All newly created classes will be associated with this grading scale. Existing classes will not be affected', and after 'Yes, set as default' the default badge moved to the new scale.</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>TST_GSCL_TC_9</t>
-  </si>
-  <si>
-    <t>Verify a grading scale is deleted after confirmation</t>
-  </si>
-  <si>
-    <t>#15 — Verify deleting a grading scale</t>
-  </si>
-  <si>
-    <t>A deletable (non-default) grading scale exists.</t>
-  </si>
-  <si>
-    <t>1. Open the scale's Open drop down -&gt; Delete. 2. Click Yes, delete.</t>
-  </si>
-  <si>
-    <t>Confirmation Are you sure? Deleting the grading scale will not affect classes associated with it, but it won't be available to apply to any new classes.; after Yes, delete the scale is removed from the list.</t>
-  </si>
-  <si>
-    <t>As expected. The confirmation read 'Are you sure? Deleting the grading scale will not affect classes associated with it, but it won’t be available to apply to any new classes. Delete this grading scale from your school?', and after 'Yes, delete' the scale left the list.</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>TST_GSCL_TC_10</t>
-  </si>
-  <si>
-    <t>Verify deleting a grading scale can be cancelled</t>
-  </si>
-  <si>
-    <t>A deletable grading scale exists.</t>
-  </si>
-  <si>
-    <t>1. Open drop down -&gt; Delete. 2. Click No, go back.</t>
-  </si>
-  <si>
-    <t>Confirmation closes; scale remains in the list (not deleted).</t>
-  </si>
-  <si>
-    <t>As expected. 'No, go back' closed the confirmation and the scale remained in the list.</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>TST_GSCL_TC_11</t>
-  </si>
-  <si>
-    <t>Verify the default grading scale cannot be deleted</t>
-  </si>
-  <si>
-    <t>On the Grading scales page (Cambridge One grading scale is default).</t>
-  </si>
-  <si>
-    <t>1. Open the Open drop down on the default scale.</t>
-  </si>
-  <si>
-    <t>Default scale: Cambridge One grading scale</t>
-  </si>
-  <si>
-    <t>The default scale's menu offers only View details - no Delete (nor Set as default) - so the default scale cannot be deleted.</t>
-  </si>
-  <si>
-    <t>The default scale's Delete / Set as default options are omitted from the DOM, not hidden - so their absence is genuinely assertable.</t>
-  </si>
-  <si>
-    <t>As expected. The default scale's menu offered only View details - Delete and Set as default are absent from the DOM entirely (element count 0), not merely hidden.</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>TST_GSCL_TC_12</t>
-  </si>
-  <si>
-    <t>Verify expanding the grading scale bands shows the bands</t>
-  </si>
-  <si>
-    <t>#16 — Verify expanding grading scale bands</t>
-  </si>
-  <si>
-    <t>On a grading scale's View details page.</t>
-  </si>
-  <si>
-    <t>1. Click Grading scale bands.</t>
-  </si>
-  <si>
-    <t>Section expands to list bands as Grade name / Band (e.g. A -&gt; 50% - 100% with Target score: 50%, F -&gt; 0% - 49%).</t>
-  </si>
-  <si>
-    <t>As expected. Clicking 'Grading scale bands' expanded the section to show Grade name / Band rows: A 50% - 100% with 'Target score: 50%', and F 0% - 49%.</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>TST_CMGT_TC_1</t>
-  </si>
-  <si>
-    <t>Verify an existing label can be added to a class</t>
-  </si>
-  <si>
-    <t>#21 — Add label in class</t>
-  </si>
-  <si>
-    <t>A class is open (Classes tab -&gt; launch a class -&gt; /view/classdata).</t>
-  </si>
-  <si>
-    <t>1. Click + Add labels. 2. Select an existing label.</t>
-  </si>
-  <si>
-    <t>The selected label is applied to the class and shown on it.</t>
-  </si>
-  <si>
-    <t>Same label list as bulk-create form (TST_BCCF_TC_5).</t>
   </si>
   <si>
     <t>61</t>
@@ -3747,8 +3753,11 @@
       <c r="K30" t="s">
         <v>271</v>
       </c>
+      <c r="L30" t="s">
+        <v>272</v>
+      </c>
       <c r="M30" t="s">
-        <v>272</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -4790,22 +4799,25 @@
       <c r="K55" t="s">
         <v>487</v>
       </c>
+      <c r="L55" t="s">
+        <v>488</v>
+      </c>
       <c r="M55" t="s">
-        <v>272</v>
+        <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B56" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C56" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D56" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E56" t="s">
         <v>18</v>
@@ -4814,22 +4826,22 @@
         <v>19</v>
       </c>
       <c r="G56" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H56" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="I56" t="s">
         <v>476</v>
       </c>
       <c r="J56" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="K56" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L56" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M56" t="s">
         <v>26</v>
@@ -4837,16 +4849,16 @@
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B57" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C57" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D57" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E57" t="s">
         <v>18</v>
@@ -4855,19 +4867,19 @@
         <v>19</v>
       </c>
       <c r="G57" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H57" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="I57" t="s">
         <v>476</v>
       </c>
       <c r="J57" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L57" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M57" t="s">
         <v>26</v>
@@ -4875,16 +4887,16 @@
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B58" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C58" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D58" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E58" t="s">
         <v>60</v>
@@ -4893,19 +4905,19 @@
         <v>61</v>
       </c>
       <c r="G58" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H58" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="I58" t="s">
         <v>22</v>
       </c>
       <c r="J58" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L58" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M58" t="s">
         <v>26</v>
@@ -4913,16 +4925,16 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B59" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C59" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D59" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E59" t="s">
         <v>69</v>
@@ -4931,22 +4943,22 @@
         <v>50</v>
       </c>
       <c r="G59" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H59" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="I59" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="J59" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="K59" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L59" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M59" t="s">
         <v>26</v>
@@ -4954,16 +4966,16 @@
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B60" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C60" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D60" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E60" t="s">
         <v>18</v>
@@ -4972,19 +4984,19 @@
         <v>50</v>
       </c>
       <c r="G60" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H60" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I60" t="s">
         <v>476</v>
       </c>
       <c r="J60" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L60" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M60" t="s">
         <v>26</v>
@@ -4992,16 +5004,16 @@
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B61" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C61" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D61" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E61" t="s">
         <v>18</v>
@@ -5010,36 +5022,36 @@
         <v>50</v>
       </c>
       <c r="G61" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H61" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="I61" t="s">
         <v>331</v>
       </c>
       <c r="J61" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="K61" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M61" t="s">
-        <v>272</v>
+        <v>538</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B62" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C62" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D62" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E62" t="s">
         <v>18</v>
@@ -5048,33 +5060,33 @@
         <v>61</v>
       </c>
       <c r="G62" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H62" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="I62" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="J62" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="M62" t="s">
-        <v>272</v>
+        <v>538</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B63" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C63" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D63" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E63" t="s">
         <v>18</v>
@@ -5083,36 +5095,36 @@
         <v>19</v>
       </c>
       <c r="G63" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="H63" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="I63" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="J63" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="K63" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="M63" t="s">
-        <v>272</v>
+        <v>538</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B64" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C64" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="D64" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E64" t="s">
         <v>18</v>
@@ -5121,33 +5133,33 @@
         <v>19</v>
       </c>
       <c r="G64" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="H64" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="I64" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="J64" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="M64" t="s">
-        <v>272</v>
+        <v>538</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B65" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C65" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D65" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E65" t="s">
         <v>18</v>
@@ -5156,36 +5168,36 @@
         <v>50</v>
       </c>
       <c r="G65" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="H65" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="I65" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="J65" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="K65" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="M65" t="s">
-        <v>272</v>
+        <v>538</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B66" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C66" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="D66" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E66" t="s">
         <v>60</v>
@@ -5194,36 +5206,36 @@
         <v>50</v>
       </c>
       <c r="G66" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="H66" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="I66" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="J66" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="K66" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="M66" t="s">
-        <v>272</v>
+        <v>538</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B67" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C67" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D67" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E67" t="s">
         <v>60</v>
@@ -5232,33 +5244,33 @@
         <v>61</v>
       </c>
       <c r="G67" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="H67" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="I67" t="s">
         <v>22</v>
       </c>
       <c r="J67" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M67" t="s">
-        <v>272</v>
+        <v>538</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B68" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C68" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="D68" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E68" t="s">
         <v>69</v>
@@ -5267,33 +5279,33 @@
         <v>50</v>
       </c>
       <c r="G68" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="H68" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="I68" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="J68" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="M68" t="s">
-        <v>272</v>
+        <v>538</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B69" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C69" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D69" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E69" t="s">
         <v>18</v>
@@ -5305,33 +5317,33 @@
         <v>32</v>
       </c>
       <c r="H69" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="I69" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="J69" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K69" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="M69" t="s">
-        <v>272</v>
+        <v>538</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B70" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C70" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="D70" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E70" t="s">
         <v>18</v>
@@ -5340,19 +5352,19 @@
         <v>19</v>
       </c>
       <c r="G70" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="H70" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="I70" t="s">
         <v>22</v>
       </c>
       <c r="J70" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="K70" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="M70" t="s">
         <v>26</v>
@@ -5360,16 +5372,16 @@
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B71" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C71" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D71" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E71" t="s">
         <v>18</v>
@@ -5378,19 +5390,19 @@
         <v>19</v>
       </c>
       <c r="G71" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="H71" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="I71" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="J71" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="K71" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="M71" t="s">
         <v>26</v>
@@ -5398,16 +5410,16 @@
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B72" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C72" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="D72" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E72" t="s">
         <v>18</v>
@@ -5416,19 +5428,19 @@
         <v>19</v>
       </c>
       <c r="G72" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="H72" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="I72" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="J72" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="K72" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="M72" t="s">
         <v>26</v>
@@ -5436,16 +5448,16 @@
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B73" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C73" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="D73" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E73" t="s">
         <v>18</v>
@@ -5454,16 +5466,16 @@
         <v>50</v>
       </c>
       <c r="G73" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="H73" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="I73" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="J73" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="M73" t="s">
         <v>26</v>
@@ -5471,16 +5483,16 @@
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B74" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C74" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="D74" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E74" t="s">
         <v>18</v>
@@ -5489,16 +5501,16 @@
         <v>61</v>
       </c>
       <c r="G74" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="H74" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="I74" t="s">
         <v>22</v>
       </c>
       <c r="J74" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="M74" t="s">
         <v>26</v>
@@ -5506,16 +5518,16 @@
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B75" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C75" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="D75" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E75" t="s">
         <v>60</v>
@@ -5524,19 +5536,19 @@
         <v>50</v>
       </c>
       <c r="G75" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="H75" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="I75" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="J75" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="K75" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="M75" t="s">
         <v>26</v>
@@ -5544,16 +5556,16 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B76" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C76" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D76" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E76" t="s">
         <v>18</v>
@@ -5562,36 +5574,36 @@
         <v>19</v>
       </c>
       <c r="G76" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="H76" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="I76" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="J76" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="K76" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="M76" t="s">
-        <v>272</v>
+        <v>538</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B77" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C77" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="D77" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E77" t="s">
         <v>18</v>
@@ -5600,36 +5612,36 @@
         <v>19</v>
       </c>
       <c r="G77" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="H77" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="I77" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="J77" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="K77" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="M77" t="s">
-        <v>272</v>
+        <v>538</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B78" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C78" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="D78" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E78" t="s">
         <v>60</v>
@@ -5638,36 +5650,36 @@
         <v>50</v>
       </c>
       <c r="G78" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="H78" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="I78" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="J78" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="K78" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="M78" t="s">
-        <v>272</v>
+        <v>538</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B79" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="C79" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="D79" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="E79" t="s">
         <v>18</v>
@@ -5676,36 +5688,36 @@
         <v>50</v>
       </c>
       <c r="G79" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="H79" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="I79" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="J79" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="K79" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="M79" t="s">
-        <v>272</v>
+        <v>538</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B80" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C80" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="D80" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="E80" t="s">
         <v>18</v>
@@ -5714,33 +5726,33 @@
         <v>50</v>
       </c>
       <c r="G80" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="H80" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="I80" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="J80" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="M80" t="s">
-        <v>272</v>
+        <v>538</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B81" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C81" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D81" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="E81" t="s">
         <v>18</v>
@@ -5749,36 +5761,36 @@
         <v>50</v>
       </c>
       <c r="G81" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="H81" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="I81" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="J81" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="K81" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="M81" t="s">
-        <v>272</v>
+        <v>538</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B82" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C82" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="D82" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="E82" t="s">
         <v>18</v>
@@ -5787,22 +5799,22 @@
         <v>50</v>
       </c>
       <c r="G82" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="H82" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="I82" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="J82" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="K82" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="M82" t="s">
-        <v>272</v>
+        <v>538</v>
       </c>
     </row>
   </sheetData>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="706">
   <si>
     <t>S.No.</t>
   </si>
@@ -118,13 +118,13 @@
     <t>Filter modal opens with Class status (Not started, Active, Ended, Expired, Deleted), Class labels (Find a label), Clear all and Apply.</t>
   </si>
   <si>
-    <t>Filter is a modal dialog.</t>
+    <t>Filter is a modal dialog. Open only - closing via X is TST_CLST_TC_23 (split 2026-08-21 so this TC's end-of-test screenshot shows the panel OPEN with its options, which is what the expected result describes).</t>
   </si>
   <si>
     <t>PASS. Filter modal opened showing all five Class status options (Not started / Active / Ended / Expired / Deleted), the 'Find a label' input, and the Clear all and Apply buttons.</t>
   </si>
   <si>
-    <t>Automated - adminClassesTab.test.js (npm run P1AdminClassesTab_Thor, thor). Last run 2026-08-17: 12/12 passing. PRODUCT NOTE: the panel's X close button is unreliable - a click reports success but the panel can stay open. Automation carries an authorised retry marked // WORKAROUND. App-side fix reported landed 2026-08-17; retry retained pending removal.</t>
+    <t>Automated - adminClassesTab.test.js (npm run P1AdminClassesTab_Thor, thor). Last run 2026-08-21: 23/23 passing. X-CLOSE HISTORY CORRECTED 2026-08-21: the 3x re-click // WORKAROUND was removed and the behaviour re-investigated live. It is NOT a product bug - 10/10 manual single clicks close the panel, and 8/8 automated closes succeed when the panel is given time to settle after opening (locator.click, real mouse, dispatchEvent, focus+Enter all work). The panel is visible and geometrically stable before its close handler is bound, which Playwright cannot detect, so automation was simply clicking too early. Closing now lives in TST_CLST_TC_23.</t>
   </si>
   <si>
     <t>3</t>
@@ -2102,6 +2102,33 @@
   </si>
   <si>
     <t>The context class is visible and behaves correctly for the student role. [ASSUMED] needs a student test account.</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>TST_CLST_TC_23</t>
+  </si>
+  <si>
+    <t>Verify the X button closes the Filter modal without applying a filter</t>
+  </si>
+  <si>
+    <t>On the Classes tab, with no filter applied.</t>
+  </si>
+  <si>
+    <t>1. Click Filter and confirm the modal is open. 2. Click the X close button once. 3. Observe the modal and the class list.</t>
+  </si>
+  <si>
+    <t>The modal closes on a single click. No filter is applied - the page-level Clear link does not appear - and the class list is unchanged.</t>
+  </si>
+  <si>
+    <t>Split out of TST_CLST_TC_2 on 2026-08-21: one TC that both opened and closed the modal was photographed at end of test with the panel already closed, so its screenshot could not evidence the open panel. TC_2 now ends with the modal open; this TC owns the close. Listed immediately after TC_2 in the execution file so the report shows the open panel one row above this result. Asserting that no filter was applied is what distinguishes closing from applying - Apply also closes the panel.</t>
+  </si>
+  <si>
+    <t>PASS. The modal closed on a single X click; no Clear link appeared and the Active class count was unchanged.</t>
+  </si>
+  <si>
+    <t>Automated - adminClassesTab.test.js (npm run P1AdminClassesTab_Thor, thor). Last run 2026-08-21: 23/23 passing. See TC_2 Comments for the X-close history - the 2026-08-15 product defect was re-diagnosed on 2026-08-21 as an automation timing issue, not a product bug.</t>
   </si>
 </sst>
 </file>
@@ -2458,7 +2485,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:N82"/>
+  <dimension ref="A1:N83"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -5817,6 +5844,50 @@
         <v>538</v>
       </c>
     </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>697</v>
+      </c>
+      <c r="B83" t="s">
+        <v>698</v>
+      </c>
+      <c r="C83" t="s">
+        <v>699</v>
+      </c>
+      <c r="D83" t="s">
+        <v>31</v>
+      </c>
+      <c r="E83" t="s">
+        <v>18</v>
+      </c>
+      <c r="F83" t="s">
+        <v>50</v>
+      </c>
+      <c r="G83" t="s">
+        <v>700</v>
+      </c>
+      <c r="H83" t="s">
+        <v>701</v>
+      </c>
+      <c r="I83" t="s">
+        <v>22</v>
+      </c>
+      <c r="J83" t="s">
+        <v>702</v>
+      </c>
+      <c r="K83" t="s">
+        <v>703</v>
+      </c>
+      <c r="L83" t="s">
+        <v>704</v>
+      </c>
+      <c r="M83" t="s">
+        <v>26</v>
+      </c>
+      <c r="N83" t="s">
+        <v>705</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="785">
   <si>
     <t>S.No.</t>
   </si>
@@ -208,6 +208,9 @@
     <t>All filter selections clear back to default within the modal.</t>
   </si>
   <si>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase.</t>
+  </si>
+  <si>
     <t>PASS. Clear all cleared the selections and closed the panel, and the page-level 'Clear' link disappeared, confirming the applied filter was reset. NOTE: during the panel's ~3.6s close it still holds its pre-clear markup, so the reset must be verified at page level, not from the panel's own chips.</t>
   </si>
   <si>
@@ -712,7 +715,7 @@
     <t>Name accepted (maxlength 50) and category created. [ASSUMED] confirm truncation at 50.</t>
   </si>
   <si>
-    <t>Automated as TST_GCAT_TC_3. The test asserts the generated name is exactly 50 characters before using it, so a helper bug cannot quietly turn this into a short-name test that never exercises the boundary.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Automated as TST_GCAT_TC_3. The test asserts the generated name is exactly 50 characters before using it, so a helper bug cannot quietly turn this into a short-name test that never exercises the boundary.</t>
   </si>
   <si>
     <t>PASS. A 50-character name was accepted and the category appeared in the list. Confirmed live that #gradingCategoryNameInput carries maxlength=50, so longer input cannot be typed - the [ASSUMED] on this TC is resolved.</t>
@@ -736,7 +739,7 @@
     <t>Modal: You have reached the maximum number of grading categories for your school. Please remove at least one category to add a new one; no category created. [ASSUMED] exact max count.</t>
   </si>
   <si>
-    <t>NOT AUTOMATED - BLOCKED. Deliberately absent from the test file, the TC repository and the execution file (not merely skipped), so it cannot run by accident.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. NOT AUTOMATED - BLOCKED. Deliberately absent from the test file, the TC repository and the execution file (not merely skipped), so it cannot run by accident.</t>
   </si>
   <si>
     <t>- (not executed)</t>
@@ -766,7 +769,7 @@
     <t>Save is disabled while empty; empty-named category cannot be created.</t>
   </si>
   <si>
-    <t>Automated as TST_GCAT_TC_5. Checked both ways - disabled when empty, enabled once a character is typed, disabled again when cleared. A one-way check would still pass against a permanently disabled Save, which is itself a defect worth catching.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Automated as TST_GCAT_TC_5. Checked both ways - disabled when empty, enabled once a character is typed, disabled again when cleared. A one-way check would still pass against a permanently disabled Save, which is itself a defect worth catching.</t>
   </si>
   <si>
     <t>PASS. Save was disabled with an empty name, became enabled on input, and returned to disabled when the field was cleared. The test ends with the modal open so the end-of-test screenshot shows the disabled Save; nothing is saved.</t>
@@ -898,7 +901,7 @@
     <t>Create new classes form opens (/class/create) with subtitle in &lt;school&gt;, Upload file, Get CSV template, How to use this form, bulk-action toolbar (Start date, End date, Add teacher, Add labels, Add Material, Copy an Existing Class, Duplicate, Show student progress, Remove), and a class row (Class name, Start date, End date, Add teachers, Add materials, Add label). Create N class is disabled.</t>
   </si>
   <si>
-    <t>Form auto-saves a draft.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Form auto-saves a draft.</t>
   </si>
   <si>
     <t>Form opened at /class/create with all components present: Upload file, Get CSV template, How to use this form, all 9 bulk-toolbar actions, and row 1 (name, dates, teachers, materials, label). Create button disabled on an empty row.</t>
@@ -1189,7 +1192,7 @@
     <t>Back to dashboard returns to the school Classes page; Create more classes returns to a fresh Create form. [ASSUMED] confirm form reset.</t>
   </si>
   <si>
-    <t>Back to dashboard covered by automation TST_CCLS_TC_8.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Back to dashboard covered by automation TST_CCLS_TC_8.</t>
   </si>
   <si>
     <t>"Back to dashboard" returned to the school Classes page. "Create more classes" returned a COMPLETELY EMPTY create form (name and both dates blank).</t>
@@ -1399,7 +1402,7 @@
     <t>Modal: You have reached the maximum number of grading scales for this school. Please remove at least one grading scale to add a new one; no scale created. [ASSUMED] exact maximum.</t>
   </si>
   <si>
-    <t>The expected modal copy is now VERIFIED word for word - the modal is pre-rendered in the DOM, so it was captured without filling the school to its cap. Only triggering it is blocked (shared school).</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. The expected modal copy is now VERIFIED word for word - the modal is pre-rendered in the DOM, so it was captured without filling the school to its cap. Only triggering it is blocked (shared school).</t>
   </si>
   <si>
     <t>52</t>
@@ -1744,7 +1747,7 @@
     <t>Up to 50 classes can be selected and deleted in one action. [ASSUMED] confirm the 50-class maximum.</t>
   </si>
   <si>
-    <t>Scenario title references 50 classes.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Scenario title references 50 classes.</t>
   </si>
   <si>
     <t>66</t>
@@ -2008,7 +2011,7 @@
     <t>Components with a count of 0 are disabled/unselectable (e.g. Teachers [0] disabled; Class grade settings - Not available).</t>
   </si>
   <si>
-    <t>Observed live.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Observed live.</t>
   </si>
   <si>
     <t>78</t>
@@ -2056,7 +2059,10 @@
     <t>The created context class</t>
   </si>
   <si>
-    <t>The context class is listed and behaves as expected in the admin view. [ASSUMED] confirm admin-specific behaviour.</t>
+    <t>The context class is listed on the Classes tab and its Student progress column reads "Progress reset". [ASSUMED] - the string is corroborated by the bulk-create CSV template, whose sample row carries Progress reset in its Student progress data column (see TST_BCCF_TC_10), but has not been read off a live class row.</t>
+  </si>
+  <si>
+    <t>Expected result strengthened 2026-09-01 from the other team's TC_CLS_030, which gives the concrete assertion this case previously lacked - ours read only "behaves as expected", which nothing could fail. Allow a few minutes after creation: class creation is asynchronous. Depends on TST_BCCF_TC_20 (the bulk Show student progress toolbar action) for the class that produces this state.</t>
   </si>
   <si>
     <t>80</t>
@@ -2080,7 +2086,7 @@
     <t>The context class is visible and behaves correctly for the teacher role. [ASSUMED] needs a teacher test account.</t>
   </si>
   <si>
-    <t>Cross-role verification.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Cross-role verification.</t>
   </si>
   <si>
     <t>81</t>
@@ -2129,6 +2135,237 @@
   </si>
   <si>
     <t>Automated - adminClassesTab.test.js (npm run P1AdminClassesTab_Thor, thor). Last run 2026-08-21: 23/23 passing. See TC_2 Comments for the X-close history - the 2026-08-15 product defect was re-diagnosed on 2026-08-21 as an automation timing issue, not a product bug.</t>
+  </si>
+  <si>
+    <t>TST_CLST_TC_24</t>
+  </si>
+  <si>
+    <t>Verify a Class status and Class label filter applied together return only classes matching both</t>
+  </si>
+  <si>
+    <t>#2 - Verify filter functionality is working fine</t>
+  </si>
+  <si>
+    <t>On the Classes tab. At least one Active class carries a known label, and at least one class carrying that same label is not Active.</t>
+  </si>
+  <si>
+    <t>1. Open Filter. 2. Select Class status Active. 3. In Class labels, type the label into "Find a label" and select it. 4. Click Apply. 5. Expand each returned row and read its label and status.</t>
+  </si>
+  <si>
+    <t>Status: Active + Label: &lt;LABEL_ON_AN_ACTIVE_CLASS&gt; - must be a label confirmed to sit on at least one Active class.</t>
+  </si>
+  <si>
+    <t>Only classes that are both Active and carry the selected label are listed. Every returned row satisfies both conditions, and classes carrying the label but not Active are absent. The Active classes (n) heading updates to the filtered total and the page-level Clear link appears. [ASSUMED] - not yet run against a populated combination.</t>
+  </si>
+  <si>
+    <t>Positive counterpart to TST_CLST_TC_22, which pairs a status and a label that match zero classes. TC_22 cannot distinguish AND from OR: if the filters were ORed, a zero-match pair would still return zero and TC_22 would still pass. This case is the only one that proves the AND. Added 2026-09-01 from the other team's TC_CLS_002, whose expected result states "Combined filters apply as an AND condition".</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Blocked</t>
+  </si>
+  <si>
+    <t>Blocked at design time (skill rule 4). TST_CLST_TC_4's Actual Result records that label VM1 matches no ACTIVE class on 3 July Test School 1. Unblock by applying an existing label to a known Active class on the target school, or by identifying a label/Active-class pair live; then ground the expected result and clear the [ASSUMED].</t>
+  </si>
+  <si>
+    <t>TST_GCAT_TC_10</t>
+  </si>
+  <si>
+    <t>Verify a grading category cannot be created with a name that already exists</t>
+  </si>
+  <si>
+    <t>#5 - Verify create grading category</t>
+  </si>
+  <si>
+    <t>On the Manage grading categories page, with at least one existing category whose name is known.</t>
+  </si>
+  <si>
+    <t>1. Note an existing category name and the current category count. 2. Click Create a grading category. 3. Enter the exact existing name. 4. Click Save. 5. Return to the list and re-count.</t>
+  </si>
+  <si>
+    <t>The name of a category already present in the school.</t>
+  </si>
+  <si>
+    <t>The duplicate name is not accepted: creation is blocked or warned per business rule, and the category count is unchanged. [ASSUMED] - the rule itself is unconfirmed; the other team's sheet also leaves it open ("handled per business rule").</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from the other team's TC_CLS_005. We cover the empty name (TST_GCAT_TC_5) and the 50-character boundary (TST_GCAT_TC_3) but never re-use an existing name. Automation note: the GCAT suite deliberately generates names as AutoCat_create_&lt;epoch-ms&gt; to avoid collisions, so this case needs a fixed name plus a housekeeping step to remove it. Confirm the rule with the product owner before finalising the expected result - "blocked" and "warned but allowed" are different products.</t>
+  </si>
+  <si>
+    <t>TST_GSCL_TC_13</t>
+  </si>
+  <si>
+    <t>Verify the Cambridge One default grading scale details page shows its classes list and notice but no bands section</t>
+  </si>
+  <si>
+    <t>#12 - Verify view details page of grading scale</t>
+  </si>
+  <si>
+    <t>On the Grading scales page. The system scale "Cambridge One grading scale" carries the default badge.</t>
+  </si>
+  <si>
+    <t>1. Open the Open drop down menu on "Cambridge One grading scale". 2. Click View details. 3. Read the page: heading, classes list, any notice, and whether a bands section is present.</t>
+  </si>
+  <si>
+    <t>The system scale "Cambridge One grading scale".</t>
+  </si>
+  <si>
+    <t>The details page shows the scale name, the linked Classes (n) list (or "No classes yet") and the pre-27-July-2023 notice. No "Grading scale bands" section is rendered, because the default scale's target varies by material. [ASSUMED] - the notice wording is not captured verbatim.</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from the other team's TC_CLS_012, which opens both a custom scale and the default scale for comparison. Our TST_GSCL_TC_6 opens a custom scale only, and the default scale renders differently. The asymmetry is already recorded in this document's product reference and in TST_GSCL_TC_12's note - the case simply did not exist. Capture the notice text verbatim on the first live pass and clear the [ASSUMED].</t>
+  </si>
+  <si>
+    <t>TST_GSCL_TC_14</t>
+  </si>
+  <si>
+    <t>Verify a grading scale that is applied to a class cannot be deleted without warning</t>
+  </si>
+  <si>
+    <t>#15 - Verify deleting a grading scale</t>
+  </si>
+  <si>
+    <t>A non-default grading scale exists and is currently applied to at least one live class.</t>
+  </si>
+  <si>
+    <t>1. Apply a non-default scale to a class via Class grade settings. 2. Open the Grading scales page and that scale's Open drop down menu. 3. Click Delete. 4. Read the resulting dialog. 5. Cancel and confirm the scale is still listed and still applied to the class.</t>
+  </si>
+  <si>
+    <t>A non-default scale applied to &lt;CLASS_WITH_CUSTOM_SCALE&gt;.</t>
+  </si>
+  <si>
+    <t>Deletion of an in-use scale is prevented, or warns about the impact on the classes using it before proceeding, per business rule. The affected class(es) are identified to the admin. Cancelling leaves both the scale and the class assignment untouched. [ASSUMED] - behaviour and copy unconfirmed.</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from the other team's TC_CLS_015_N1, which bundles two rules: the default scale and a scale in active use. Our TST_GSCL_TC_11 implements only the first. Suite placement: the precondition is a scale applied to a live class - the state the CGST suite already builds - so this case should run inside the CGST suite rather than the GSCL suite, exactly as TST_GSCL_TC_7 does.</t>
+  </si>
+  <si>
+    <t>TST_CGST_TC_7</t>
+  </si>
+  <si>
+    <t>Verify a grading category can be removed from the class weighting with the delete icon</t>
+  </si>
+  <si>
+    <t>#22 - Launch class grade setting page from a class page</t>
+  </si>
+  <si>
+    <t>On the Class grade settings page of a class that already has at least one grading category carrying a weightage.</t>
+  </si>
+  <si>
+    <t>1. Note the categories listed under grade weighting and the current Total grade %. 2. Click the delete (bin) icon against one grading category. 3. Observe the live total. 4. Click Save changes. 5. Refresh the page and re-read the weighting.</t>
+  </si>
+  <si>
+    <t>A class with a weighted grading category (the CGST suite creates one via TST_CGST_TC_3).</t>
+  </si>
+  <si>
+    <t>The category is removed from the class weighting, the live Total grade % recalculates immediately, and the removal persists after Save changes and a refresh. [ASSUMED] - the removal control has not been exercised live.</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from the other team's TC_CLS_034, which covers weights, add and remove, and the 100% rule. Our TST_CGST_TC_3 only adds a category and TST_CGST_TC_6 only checks the 100% total, so removal was untested. Fits the existing CGST suite, which already creates and tears down its own class - no new fixture needed. Creates and mutates real data on that throwaway class.</t>
+  </si>
+  <si>
+    <t>TST_BCCF_TC_17</t>
+  </si>
+  <si>
+    <t>Verify the bulk Add teacher toolbar action applies the teacher to every selected class row</t>
+  </si>
+  <si>
+    <t>#3 - Verify bulk class creation form is working fine</t>
+  </si>
+  <si>
+    <t>On the "Create new classes" form (/class/create) with at least 2 class rows filled.</t>
+  </si>
+  <si>
+    <t>1. Fill 2+ class rows. 2. Tick the checkbox on each row. 3. Click Add teacher in the bulk toolbar. 4. Enter a valid teacher email in the "Edit teachers" modal and click Apply changes. 5. Read every selected row and the row checkboxes.</t>
+  </si>
+  <si>
+    <t>Teacher email &lt;EXISTING_THOR_TEACHER_EMAIL&gt;; 2+ draft class rows.</t>
+  </si>
+  <si>
+    <t>The teacher is added to every selected row, not only the first. The rows deselect after the action is applied, and the Saved auto-save indicator updates. [ASSUMED] - the deselect-after-apply behaviour is recorded in TST_BCCF_TC_9's Remarks but has not been asserted by a case of its own.</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from the other team's TC_CLS_036, which exercises the whole bulk toolbar. TST_BCCF_TC_9 covers bulk Start/End date only; its Remarks claim "the same pattern applies to bulk Add teacher / Add labels / Add Material" - a prose claim, not coverage. This case and TC_18-TC_21 turn that sentence into tests. Side-effect free - the form is not submitted.</t>
+  </si>
+  <si>
+    <t>TST_BCCF_TC_18</t>
+  </si>
+  <si>
+    <t>Verify the bulk Add Material toolbar action applies the material to every selected class row</t>
+  </si>
+  <si>
+    <t>On the "Create new classes" form with at least 2 class rows filled.</t>
+  </si>
+  <si>
+    <t>1. Fill 2+ class rows. 2. Tick the checkbox on each row. 3. Click Add Material in the bulk toolbar. 4. Select a course material and apply. 5. Read every selected row and the row checkboxes.</t>
+  </si>
+  <si>
+    <t>Material/component &lt;VALID_THOR_MATERIAL&gt;; 2+ draft class rows.</t>
+  </si>
+  <si>
+    <t>The material is added to every selected row, the rows deselect after apply, and the Saved indicator updates. [ASSUMED]</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from TC_CLS_036 - see TST_BCCF_TC_17 Remarks. Side-effect free.</t>
+  </si>
+  <si>
+    <t>TST_BCCF_TC_19</t>
+  </si>
+  <si>
+    <t>Verify the bulk Add labels toolbar action applies the label to every selected class row</t>
+  </si>
+  <si>
+    <t>1. Fill 2+ class rows. 2. Tick the checkbox on each row. 3. Click Add labels in the bulk toolbar. 4. Select or create a label and apply. 5. Read every selected row and the row checkboxes.</t>
+  </si>
+  <si>
+    <t>Label &lt;EXISTING_THOR_CLASS_LABEL&gt;; 2+ draft class rows.</t>
+  </si>
+  <si>
+    <t>The label is added to every selected row, the rows deselect after apply, and the Saved indicator updates. [ASSUMED]</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from TC_CLS_036 - see TST_BCCF_TC_17 Remarks. Note TST_BCCF_TC_7 records that labels behave specially on Duplicate (an "Apply the labels to new classes too?" dialog); check whether the bulk label action raises anything similar. Side-effect free.</t>
+  </si>
+  <si>
+    <t>TST_BCCF_TC_20</t>
+  </si>
+  <si>
+    <t>Verify the bulk Show student progress toolbar action applies to every selected class row</t>
+  </si>
+  <si>
+    <t>1. Fill 2+ class rows. 2. Tick the checkbox on each row. 3. Click Show student progress in the bulk toolbar. 4. Apply the setting. 5. Read every selected row.</t>
+  </si>
+  <si>
+    <t>2+ draft class rows.</t>
+  </si>
+  <si>
+    <t>The "show student progress" setting is applied to every selected row, the rows deselect after apply, and the Saved indicator updates. [ASSUMED]</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from TC_CLS_036. This is the toolbar control that produces a context class - the classes created this way are the subject of TST_CTXC_TC_1 and TST_CTXC_TC_2, so the two areas should be grounded in the same live pass. Side-effect free while the form is not submitted.</t>
+  </si>
+  <si>
+    <t>TST_BCCF_TC_21</t>
+  </si>
+  <si>
+    <t>Verify the bulk Remove toolbar action deletes exactly the selected class rows</t>
+  </si>
+  <si>
+    <t>On the "Create new classes" form with at least 3 class rows filled and distinguishable by name.</t>
+  </si>
+  <si>
+    <t>1. Fill 3+ distinguishable class rows. 2. Tick the checkbox on 2 of them, leaving one unticked. 3. Click Remove in the bulk toolbar. 4. Confirm if prompted. 5. Read the remaining rows.</t>
+  </si>
+  <si>
+    <t>3+ draft class rows with distinct names.</t>
+  </si>
+  <si>
+    <t>Exactly the selected rows are removed and the unselected row survives, unchanged. The Create N class(es) button count drops to match the remaining valid rows, and the Saved indicator updates. [ASSUMED] - whether Remove raises its own confirmation is unconfirmed.</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from TC_CLS_036. Deliberately leaves one row unselected: an action that removed all rows would still pass a case that only counted deletions. Side-effect free - the form is not submitted.</t>
   </si>
 </sst>
 </file>
@@ -2175,10 +2412,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2485,7 +2725,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:N83"/>
+  <dimension ref="A1:N93"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -2754,8 +2994,11 @@
       <c r="J6" t="s">
         <v>64</v>
       </c>
+      <c r="K6" s="2" t="s">
+        <v>65</v>
+      </c>
       <c r="L6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M6" t="s">
         <v>26</v>
@@ -2766,19 +3009,19 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
         <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F7" t="s">
         <v>61</v>
@@ -2787,16 +3030,19 @@
         <v>32</v>
       </c>
       <c r="H7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J7" t="s">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="L7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M7" t="s">
         <v>26</v>
@@ -2807,16 +3053,16 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E8" t="s">
         <v>18</v>
@@ -2825,22 +3071,22 @@
         <v>19</v>
       </c>
       <c r="G8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M8" t="s">
         <v>26</v>
@@ -2851,16 +3097,16 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E9" t="s">
         <v>18</v>
@@ -2869,22 +3115,22 @@
         <v>19</v>
       </c>
       <c r="G9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M9" t="s">
         <v>26</v>
@@ -2895,16 +3141,16 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E10" t="s">
         <v>60</v>
@@ -2913,22 +3159,22 @@
         <v>50</v>
       </c>
       <c r="G10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M10" t="s">
         <v>26</v>
@@ -2939,19 +3185,19 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F11" t="s">
         <v>50</v>
@@ -2960,19 +3206,19 @@
         <v>32</v>
       </c>
       <c r="H11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M11" t="s">
         <v>26</v>
@@ -2983,16 +3229,16 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E12" t="s">
         <v>18</v>
@@ -3001,19 +3247,19 @@
         <v>50</v>
       </c>
       <c r="G12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I12" t="s">
         <v>22</v>
       </c>
       <c r="J12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M12" t="s">
         <v>26</v>
@@ -3024,16 +3270,16 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E13" t="s">
         <v>18</v>
@@ -3042,22 +3288,22 @@
         <v>50</v>
       </c>
       <c r="G13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I13" t="s">
         <v>22</v>
       </c>
       <c r="J13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M13" t="s">
         <v>26</v>
@@ -3068,16 +3314,16 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D14" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E14" t="s">
         <v>18</v>
@@ -3086,19 +3332,19 @@
         <v>50</v>
       </c>
       <c r="G14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I14" t="s">
         <v>22</v>
       </c>
       <c r="J14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L14" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M14" t="s">
         <v>26</v>
@@ -3109,16 +3355,16 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D15" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E15" t="s">
         <v>18</v>
@@ -3127,19 +3373,19 @@
         <v>61</v>
       </c>
       <c r="G15" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I15" t="s">
         <v>22</v>
       </c>
       <c r="J15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M15" t="s">
         <v>26</v>
@@ -3150,16 +3396,16 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B16" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C16" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D16" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E16" t="s">
         <v>18</v>
@@ -3168,19 +3414,19 @@
         <v>61</v>
       </c>
       <c r="G16" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I16" t="s">
         <v>22</v>
       </c>
       <c r="J16" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L16" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M16" t="s">
         <v>26</v>
@@ -3191,16 +3437,16 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D17" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E17" t="s">
         <v>18</v>
@@ -3209,19 +3455,19 @@
         <v>61</v>
       </c>
       <c r="G17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H17" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I17" t="s">
         <v>22</v>
       </c>
       <c r="J17" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M17" t="s">
         <v>26</v>
@@ -3232,16 +3478,16 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B18" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C18" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E18" t="s">
         <v>18</v>
@@ -3250,22 +3496,22 @@
         <v>19</v>
       </c>
       <c r="G18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H18" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I18" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J18" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L18" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M18" t="s">
         <v>26</v>
@@ -3276,16 +3522,16 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D19" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E19" t="s">
         <v>18</v>
@@ -3294,22 +3540,22 @@
         <v>50</v>
       </c>
       <c r="G19" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I19" t="s">
         <v>22</v>
       </c>
       <c r="J19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L19" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M19" t="s">
         <v>26</v>
@@ -3320,16 +3566,16 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B20" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C20" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D20" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E20" t="s">
         <v>18</v>
@@ -3338,19 +3584,19 @@
         <v>50</v>
       </c>
       <c r="G20" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H20" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I20" t="s">
         <v>22</v>
       </c>
       <c r="J20" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L20" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M20" t="s">
         <v>26</v>
@@ -3361,16 +3607,16 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D21" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E21" t="s">
         <v>18</v>
@@ -3379,22 +3625,22 @@
         <v>50</v>
       </c>
       <c r="G21" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H21" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I21" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K21" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L21" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M21" t="s">
         <v>26</v>
@@ -3405,16 +3651,16 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C22" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E22" t="s">
         <v>18</v>
@@ -3423,22 +3669,22 @@
         <v>50</v>
       </c>
       <c r="G22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H22" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I22" t="s">
         <v>22</v>
       </c>
       <c r="J22" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K22" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L22" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M22" t="s">
         <v>26</v>
@@ -3449,16 +3695,16 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B23" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C23" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D23" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E23" t="s">
         <v>60</v>
@@ -3467,19 +3713,22 @@
         <v>61</v>
       </c>
       <c r="G23" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H23" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I23" t="s">
         <v>22</v>
       </c>
       <c r="J23" t="s">
-        <v>204</v>
+        <v>205</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="L23" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M23" t="s">
         <v>26</v>
@@ -3490,16 +3739,16 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B24" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C24" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D24" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E24" t="s">
         <v>18</v>
@@ -3508,22 +3757,22 @@
         <v>19</v>
       </c>
       <c r="G24" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H24" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I24" t="s">
         <v>22</v>
       </c>
       <c r="J24" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K24" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L24" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M24" t="s">
         <v>26</v>
@@ -3531,16 +3780,16 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B25" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C25" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D25" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E25" t="s">
         <v>18</v>
@@ -3549,42 +3798,42 @@
         <v>19</v>
       </c>
       <c r="G25" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H25" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I25" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J25" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K25" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L25" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M25" t="s">
         <v>26</v>
       </c>
       <c r="N25" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B26" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C26" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D26" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E26" t="s">
         <v>60</v>
@@ -3593,42 +3842,42 @@
         <v>61</v>
       </c>
       <c r="G26" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H26" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I26" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J26" t="s">
-        <v>232</v>
-      </c>
-      <c r="K26" t="s">
         <v>233</v>
       </c>
+      <c r="K26" s="2" t="s">
+        <v>234</v>
+      </c>
       <c r="L26" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M26" t="s">
         <v>26</v>
       </c>
       <c r="N26" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B27" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C27" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D27" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E27" t="s">
         <v>60</v>
@@ -3637,86 +3886,86 @@
         <v>50</v>
       </c>
       <c r="G27" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H27" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I27" t="s">
         <v>22</v>
       </c>
       <c r="J27" t="s">
-        <v>240</v>
-      </c>
-      <c r="K27" t="s">
         <v>241</v>
       </c>
+      <c r="K27" s="2" t="s">
+        <v>242</v>
+      </c>
       <c r="L27" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M27" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N27" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B28" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C28" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D28" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F28" t="s">
         <v>50</v>
       </c>
       <c r="G28" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H28" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I28" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J28" t="s">
-        <v>250</v>
-      </c>
-      <c r="K28" t="s">
         <v>251</v>
       </c>
+      <c r="K28" s="2" t="s">
+        <v>252</v>
+      </c>
       <c r="L28" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M28" t="s">
         <v>26</v>
       </c>
       <c r="N28" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B29" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C29" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D29" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E29" t="s">
         <v>18</v>
@@ -3725,22 +3974,22 @@
         <v>50</v>
       </c>
       <c r="G29" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H29" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I29" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J29" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K29" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L29" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M29" t="s">
         <v>26</v>
@@ -3748,16 +3997,16 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B30" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C30" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E30" t="s">
         <v>18</v>
@@ -3766,22 +4015,22 @@
         <v>50</v>
       </c>
       <c r="G30" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H30" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I30" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J30" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K30" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L30" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M30" t="s">
         <v>26</v>
@@ -3789,16 +4038,16 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B31" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C31" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D31" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E31" t="s">
         <v>18</v>
@@ -3807,42 +4056,42 @@
         <v>19</v>
       </c>
       <c r="G31" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H31" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I31" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J31" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K31" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L31" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M31" t="s">
         <v>26</v>
       </c>
       <c r="N31" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B32" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C32" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D32" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E32" t="s">
         <v>60</v>
@@ -3851,42 +4100,42 @@
         <v>61</v>
       </c>
       <c r="G32" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H32" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I32" t="s">
         <v>22</v>
       </c>
       <c r="J32" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K32" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L32" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M32" t="s">
         <v>26</v>
       </c>
       <c r="N32" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B33" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C33" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D33" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E33" t="s">
         <v>18</v>
@@ -3898,39 +4147,39 @@
         <v>32</v>
       </c>
       <c r="H33" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I33" t="s">
         <v>22</v>
       </c>
       <c r="J33" t="s">
-        <v>294</v>
-      </c>
-      <c r="K33" t="s">
         <v>295</v>
       </c>
+      <c r="K33" s="2" t="s">
+        <v>296</v>
+      </c>
       <c r="L33" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M33" t="s">
         <v>26</v>
       </c>
       <c r="N33" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B34" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C34" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D34" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E34" t="s">
         <v>18</v>
@@ -3939,42 +4188,42 @@
         <v>19</v>
       </c>
       <c r="G34" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H34" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I34" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J34" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K34" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L34" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M34" t="s">
         <v>26</v>
       </c>
       <c r="N34" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B35" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C35" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D35" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E35" t="s">
         <v>18</v>
@@ -3983,42 +4232,42 @@
         <v>50</v>
       </c>
       <c r="G35" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H35" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I35" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J35" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K35" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L35" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M35" t="s">
         <v>26</v>
       </c>
       <c r="N35" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B36" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C36" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D36" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E36" t="s">
         <v>18</v>
@@ -4027,42 +4276,42 @@
         <v>50</v>
       </c>
       <c r="G36" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H36" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I36" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J36" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K36" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L36" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M36" t="s">
         <v>26</v>
       </c>
       <c r="N36" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B37" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C37" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D37" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E37" t="s">
         <v>18</v>
@@ -4071,39 +4320,39 @@
         <v>50</v>
       </c>
       <c r="G37" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H37" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I37" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J37" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L37" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M37" t="s">
         <v>26</v>
       </c>
       <c r="N37" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B38" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C38" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D38" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E38" t="s">
         <v>18</v>
@@ -4112,39 +4361,39 @@
         <v>19</v>
       </c>
       <c r="G38" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H38" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I38" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J38" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L38" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M38" t="s">
         <v>26</v>
       </c>
       <c r="N38" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B39" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C39" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D39" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E39" t="s">
         <v>18</v>
@@ -4153,39 +4402,42 @@
         <v>50</v>
       </c>
       <c r="G39" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H39" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="I39" t="s">
         <v>22</v>
       </c>
       <c r="J39" t="s">
-        <v>348</v>
+        <v>349</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="L39" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M39" t="s">
         <v>26</v>
       </c>
       <c r="N39" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B40" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C40" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D40" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E40" t="s">
         <v>18</v>
@@ -4194,42 +4446,42 @@
         <v>50</v>
       </c>
       <c r="G40" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H40" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I40" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J40" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K40" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L40" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M40" t="s">
         <v>26</v>
       </c>
       <c r="N40" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B41" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C41" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D41" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E41" t="s">
         <v>18</v>
@@ -4238,42 +4490,42 @@
         <v>50</v>
       </c>
       <c r="G41" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H41" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I41" t="s">
         <v>22</v>
       </c>
       <c r="J41" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K41" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L41" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M41" t="s">
         <v>26</v>
       </c>
       <c r="N41" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B42" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C42" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D42" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E42" t="s">
         <v>18</v>
@@ -4282,39 +4534,39 @@
         <v>61</v>
       </c>
       <c r="G42" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H42" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="I42" t="s">
         <v>22</v>
       </c>
       <c r="J42" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L42" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M42" t="s">
         <v>26</v>
       </c>
       <c r="N42" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B43" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C43" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D43" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E43" t="s">
         <v>18</v>
@@ -4323,39 +4575,39 @@
         <v>50</v>
       </c>
       <c r="G43" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H43" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I43" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J43" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L43" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M43" t="s">
         <v>26</v>
       </c>
       <c r="N43" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B44" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C44" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D44" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E44" t="s">
         <v>18</v>
@@ -4364,42 +4616,42 @@
         <v>50</v>
       </c>
       <c r="G44" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H44" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I44" t="s">
         <v>22</v>
       </c>
       <c r="J44" t="s">
-        <v>391</v>
-      </c>
-      <c r="K44" t="s">
         <v>392</v>
       </c>
+      <c r="K44" s="2" t="s">
+        <v>393</v>
+      </c>
       <c r="L44" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M44" t="s">
         <v>26</v>
       </c>
       <c r="N44" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B45" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C45" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D45" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E45" t="s">
         <v>60</v>
@@ -4408,39 +4660,42 @@
         <v>61</v>
       </c>
       <c r="G45" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H45" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="I45" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J45" t="s">
-        <v>400</v>
+        <v>401</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="L45" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M45" t="s">
         <v>26</v>
       </c>
       <c r="N45" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B46" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C46" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D46" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E46" t="s">
         <v>60</v>
@@ -4449,124 +4704,130 @@
         <v>50</v>
       </c>
       <c r="G46" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H46" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="I46" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J46" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K46" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L46" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M46" t="s">
         <v>26</v>
       </c>
       <c r="N46" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B47" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C47" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D47" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E47" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F47" t="s">
         <v>19</v>
       </c>
       <c r="G47" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H47" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I47" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="J47" t="s">
-        <v>418</v>
+        <v>419</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="L47" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M47" t="s">
         <v>26</v>
       </c>
       <c r="N47" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B48" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C48" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D48" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E48" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F48" t="s">
         <v>50</v>
       </c>
       <c r="G48" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H48" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I48" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J48" t="s">
-        <v>426</v>
+        <v>427</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="L48" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M48" t="s">
         <v>26</v>
       </c>
       <c r="N48" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B49" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C49" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D49" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E49" t="s">
         <v>18</v>
@@ -4575,22 +4836,22 @@
         <v>19</v>
       </c>
       <c r="G49" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H49" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="I49" t="s">
         <v>22</v>
       </c>
       <c r="J49" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K49" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L49" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M49" t="s">
         <v>26</v>
@@ -4598,16 +4859,16 @@
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B50" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C50" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D50" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E50" t="s">
         <v>18</v>
@@ -4616,22 +4877,22 @@
         <v>19</v>
       </c>
       <c r="G50" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H50" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="I50" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J50" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K50" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L50" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M50" t="s">
         <v>26</v>
@@ -4639,16 +4900,16 @@
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B51" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C51" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D51" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E51" t="s">
         <v>18</v>
@@ -4657,22 +4918,22 @@
         <v>50</v>
       </c>
       <c r="G51" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H51" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I51" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J51" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K51" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L51" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M51" t="s">
         <v>26</v>
@@ -4680,16 +4941,16 @@
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B52" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C52" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D52" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E52" t="s">
         <v>60</v>
@@ -4698,57 +4959,57 @@
         <v>50</v>
       </c>
       <c r="G52" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H52" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="I52" t="s">
         <v>22</v>
       </c>
       <c r="J52" t="s">
-        <v>461</v>
-      </c>
-      <c r="K52" t="s">
         <v>462</v>
       </c>
+      <c r="K52" s="2" t="s">
+        <v>463</v>
+      </c>
       <c r="M52" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B53" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C53" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D53" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E53" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F53" t="s">
         <v>19</v>
       </c>
       <c r="G53" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H53" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="I53" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="J53" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L53" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M53" t="s">
         <v>26</v>
@@ -4756,16 +5017,16 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B54" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C54" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D54" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E54" t="s">
         <v>18</v>
@@ -4774,19 +5035,19 @@
         <v>50</v>
       </c>
       <c r="G54" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H54" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I54" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J54" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L54" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M54" t="s">
         <v>26</v>
@@ -4794,16 +5055,16 @@
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B55" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C55" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D55" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E55" t="s">
         <v>18</v>
@@ -4812,22 +5073,22 @@
         <v>50</v>
       </c>
       <c r="G55" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H55" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="I55" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="J55" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K55" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L55" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M55" t="s">
         <v>26</v>
@@ -4835,16 +5096,16 @@
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B56" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C56" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D56" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E56" t="s">
         <v>18</v>
@@ -4853,22 +5114,22 @@
         <v>19</v>
       </c>
       <c r="G56" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H56" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="I56" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J56" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K56" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L56" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M56" t="s">
         <v>26</v>
@@ -4876,16 +5137,16 @@
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B57" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C57" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D57" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E57" t="s">
         <v>18</v>
@@ -4894,19 +5155,19 @@
         <v>19</v>
       </c>
       <c r="G57" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H57" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I57" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J57" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L57" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M57" t="s">
         <v>26</v>
@@ -4914,16 +5175,16 @@
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B58" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C58" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D58" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E58" t="s">
         <v>60</v>
@@ -4932,19 +5193,19 @@
         <v>61</v>
       </c>
       <c r="G58" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H58" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="I58" t="s">
         <v>22</v>
       </c>
       <c r="J58" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L58" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M58" t="s">
         <v>26</v>
@@ -4952,40 +5213,40 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B59" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C59" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D59" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E59" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F59" t="s">
         <v>50</v>
       </c>
       <c r="G59" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H59" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="I59" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="J59" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="K59" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L59" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M59" t="s">
         <v>26</v>
@@ -4993,16 +5254,16 @@
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B60" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C60" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D60" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E60" t="s">
         <v>18</v>
@@ -5011,19 +5272,19 @@
         <v>50</v>
       </c>
       <c r="G60" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H60" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I60" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J60" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="L60" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M60" t="s">
         <v>26</v>
@@ -5031,16 +5292,16 @@
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B61" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C61" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D61" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E61" t="s">
         <v>18</v>
@@ -5049,36 +5310,36 @@
         <v>50</v>
       </c>
       <c r="G61" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H61" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="I61" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J61" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="K61" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M61" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B62" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C62" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D62" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E62" t="s">
         <v>18</v>
@@ -5087,33 +5348,33 @@
         <v>61</v>
       </c>
       <c r="G62" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H62" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I62" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J62" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M62" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B63" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C63" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D63" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E63" t="s">
         <v>18</v>
@@ -5122,36 +5383,36 @@
         <v>19</v>
       </c>
       <c r="G63" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H63" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="I63" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="J63" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="K63" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M63" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B64" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C64" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D64" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E64" t="s">
         <v>18</v>
@@ -5160,33 +5421,36 @@
         <v>19</v>
       </c>
       <c r="G64" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H64" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="I64" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="J64" t="s">
-        <v>561</v>
+        <v>562</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="M64" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B65" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C65" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D65" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E65" t="s">
         <v>18</v>
@@ -5195,36 +5459,36 @@
         <v>50</v>
       </c>
       <c r="G65" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H65" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="I65" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J65" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="K65" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M65" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B66" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C66" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D66" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E66" t="s">
         <v>60</v>
@@ -5233,36 +5497,36 @@
         <v>50</v>
       </c>
       <c r="G66" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H66" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="I66" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="J66" t="s">
-        <v>576</v>
-      </c>
-      <c r="K66" t="s">
         <v>577</v>
       </c>
+      <c r="K66" s="2" t="s">
+        <v>578</v>
+      </c>
       <c r="M66" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B67" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C67" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D67" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E67" t="s">
         <v>60</v>
@@ -5271,68 +5535,68 @@
         <v>61</v>
       </c>
       <c r="G67" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H67" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="I67" t="s">
         <v>22</v>
       </c>
       <c r="J67" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M67" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B68" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C68" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D68" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E68" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F68" t="s">
         <v>50</v>
       </c>
       <c r="G68" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H68" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="I68" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="J68" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M68" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B69" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C69" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D69" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E69" t="s">
         <v>18</v>
@@ -5344,33 +5608,33 @@
         <v>32</v>
       </c>
       <c r="H69" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="I69" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="J69" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="K69" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M69" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B70" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C70" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D70" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E70" t="s">
         <v>18</v>
@@ -5379,19 +5643,19 @@
         <v>19</v>
       </c>
       <c r="G70" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H70" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="I70" t="s">
         <v>22</v>
       </c>
       <c r="J70" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="K70" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M70" t="s">
         <v>26</v>
@@ -5399,16 +5663,16 @@
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B71" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C71" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D71" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E71" t="s">
         <v>18</v>
@@ -5417,19 +5681,19 @@
         <v>19</v>
       </c>
       <c r="G71" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H71" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="I71" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="J71" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="K71" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M71" t="s">
         <v>26</v>
@@ -5437,16 +5701,16 @@
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B72" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C72" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D72" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E72" t="s">
         <v>18</v>
@@ -5455,19 +5719,19 @@
         <v>19</v>
       </c>
       <c r="G72" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H72" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="I72" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="J72" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="K72" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M72" t="s">
         <v>26</v>
@@ -5475,16 +5739,16 @@
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B73" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C73" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D73" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E73" t="s">
         <v>18</v>
@@ -5493,16 +5757,16 @@
         <v>50</v>
       </c>
       <c r="G73" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H73" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="I73" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="J73" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M73" t="s">
         <v>26</v>
@@ -5510,16 +5774,16 @@
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B74" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C74" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D74" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E74" t="s">
         <v>18</v>
@@ -5528,16 +5792,16 @@
         <v>61</v>
       </c>
       <c r="G74" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H74" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="I74" t="s">
         <v>22</v>
       </c>
       <c r="J74" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="M74" t="s">
         <v>26</v>
@@ -5545,16 +5809,16 @@
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B75" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C75" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D75" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E75" t="s">
         <v>60</v>
@@ -5563,19 +5827,19 @@
         <v>50</v>
       </c>
       <c r="G75" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H75" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="I75" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="J75" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="K75" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M75" t="s">
         <v>26</v>
@@ -5583,16 +5847,16 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B76" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C76" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D76" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E76" t="s">
         <v>18</v>
@@ -5601,36 +5865,36 @@
         <v>19</v>
       </c>
       <c r="G76" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H76" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="I76" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="J76" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="K76" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="M76" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B77" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C77" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D77" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E77" t="s">
         <v>18</v>
@@ -5639,36 +5903,36 @@
         <v>19</v>
       </c>
       <c r="G77" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H77" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="I77" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="J77" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="K77" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="M77" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B78" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C78" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D78" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E78" t="s">
         <v>60</v>
@@ -5677,36 +5941,36 @@
         <v>50</v>
       </c>
       <c r="G78" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H78" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="I78" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="J78" t="s">
-        <v>664</v>
-      </c>
-      <c r="K78" t="s">
         <v>665</v>
       </c>
+      <c r="K78" s="2" t="s">
+        <v>666</v>
+      </c>
       <c r="M78" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B79" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C79" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D79" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E79" t="s">
         <v>18</v>
@@ -5715,36 +5979,36 @@
         <v>50</v>
       </c>
       <c r="G79" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H79" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="I79" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="J79" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="K79" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M79" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B80" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C80" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D80" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E80" t="s">
         <v>18</v>
@@ -5753,33 +6017,36 @@
         <v>50</v>
       </c>
       <c r="G80" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H80" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="I80" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="J80" t="s">
-        <v>681</v>
+        <v>682</v>
+      </c>
+      <c r="K80" t="s">
+        <v>683</v>
       </c>
       <c r="M80" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="B81" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="C81" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="D81" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E81" t="s">
         <v>18</v>
@@ -5788,36 +6055,36 @@
         <v>50</v>
       </c>
       <c r="G81" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="H81" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="I81" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="J81" t="s">
-        <v>688</v>
-      </c>
-      <c r="K81" t="s">
-        <v>689</v>
+        <v>690</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>691</v>
       </c>
       <c r="M81" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B82" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C82" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="D82" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E82" t="s">
         <v>18</v>
@@ -5826,33 +6093,33 @@
         <v>50</v>
       </c>
       <c r="G82" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="H82" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="I82" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="J82" t="s">
-        <v>696</v>
-      </c>
-      <c r="K82" t="s">
-        <v>689</v>
+        <v>698</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>691</v>
       </c>
       <c r="M82" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B83" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C83" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D83" t="s">
         <v>31</v>
@@ -5864,28 +6131,468 @@
         <v>50</v>
       </c>
       <c r="G83" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="H83" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="I83" t="s">
         <v>22</v>
       </c>
       <c r="J83" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="K83" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="L83" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="M83" t="s">
         <v>26</v>
       </c>
       <c r="N83" t="s">
-        <v>705</v>
+        <v>707</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="2">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="M84" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="N84" s="2" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="2">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="M85" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="N85" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="2">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="M86" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="N86" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="2">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="M87" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="N87" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="2">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="M88" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="N88" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="2">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="K89" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="L89" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="M89" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="N89" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="2">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="K90" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="L90" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="M90" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="N90" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="2">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="K91" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="L91" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="M91" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="N91" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="2">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="K92" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="L92" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="M92" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="N92" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="2">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="J93" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="K93" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="L93" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="M93" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="N93" s="2" t="s">
+        <v>716</v>
       </c>
     </row>
   </sheetData>
